--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887613962645255</v>
+        <v>0.7887505226803012</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921939267721968</v>
+        <v>0.7921730288600494</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915575134920257</v>
+        <v>0.7915367464308581</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7930830194867502</v>
+        <v>0.7930497980016152</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7917687880545308</v>
+        <v>0.7917345661227293</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7903225404314581</v>
+        <v>0.7902877580398808</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7887430990214878</v>
+        <v>0.7887084687422008</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7876530164354137</v>
+        <v>0.7876190241163002</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.78973045370596</v>
+        <v>0.7896907922666045</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7947301499187952</v>
+        <v>0.7947114542967293</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971608625367816</v>
+        <v>0.7971409683474195</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995945244683198</v>
+        <v>0.7995741192967333</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002850720105318</v>
+        <v>0.8002761745130124</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7985821077140567</v>
+        <v>0.7985895630372042</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991094151373813</v>
+        <v>0.7991224577120816</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040434464999739</v>
+        <v>0.8040379034345808</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8099254321993267</v>
+        <v>0.8099013647870139</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161944867107962</v>
+        <v>0.8161638493180483</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224991100312368</v>
+        <v>0.8224758986201463</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229786627041125</v>
+        <v>0.8229785094385016</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8183819222896753</v>
+        <v>0.8184187578847282</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.814789340808065</v>
+        <v>0.8148375353488484</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8130123746273339</v>
+        <v>0.8130942915105256</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8108367507924246</v>
+        <v>0.8109647065821544</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8103008536167449</v>
+        <v>0.8104613042040048</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8150925966124539</v>
+        <v>0.8152871248437543</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8205389130446272</v>
+        <v>0.8207530037182603</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8271503014827557</v>
+        <v>0.8273855772996468</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8316382974317342</v>
+        <v>0.8318819543666147</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.816258480973677</v>
+        <v>0.8165504689448012</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8181030084654918</v>
+        <v>0.8183921907657745</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8051960909713143</v>
+        <v>0.805515097296027</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7973207051316856</v>
+        <v>0.7976185786297507</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7895956914142754</v>
+        <v>0.7899337407853912</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7797825510601828</v>
+        <v>0.7801336180783887</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7670419109559033</v>
+        <v>0.7671669261273992</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7654125215591328</v>
+        <v>0.7654835125806659</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758547471789327</v>
+        <v>0.758512738363371</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7496665258280732</v>
+        <v>0.7494850954795605</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7418388840863838</v>
+        <v>0.7415660384347471</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.73337712496983</v>
+        <v>0.7330145494552642</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7397959552688921</v>
+        <v>0.7392612308776411</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7455448935350306</v>
+        <v>0.7449873846452405</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7543860952103962</v>
+        <v>0.7538971857286036</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7604555609042867</v>
+        <v>0.7623867390759077</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731413442870514</v>
+        <v>0.7753640446016428</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7765938500909189</v>
+        <v>0.7783894957735069</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7756469113159186</v>
+        <v>0.7777669863075782</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7809019265299907</v>
+        <v>0.7822449963954728</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7867797689151901</v>
+        <v>0.7868740940949812</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.790875662957539</v>
+        <v>0.7899064197600066</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7850927088623291</v>
+        <v>0.7852892894516197</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7848131089938716</v>
+        <v>0.7851214001847577</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7826172721356406</v>
+        <v>0.7840020412927335</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.781518029619703</v>
+        <v>0.7835342772688458</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7822413639283945</v>
+        <v>0.7842584367343224</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7815961785097524</v>
+        <v>0.7841469334789465</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7816405063307794</v>
+        <v>0.7835225246110904</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,15 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7867</v>
+        <v>0.783620976803987</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B66">
+        <v>0.7763708062392134</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887505226803012</v>
+        <v>0.788745493383735</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921730288600494</v>
+        <v>0.7921633592589075</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915367464308581</v>
+        <v>0.7915271249992355</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7930497980016152</v>
+        <v>0.7930344156390369</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7917345661227293</v>
+        <v>0.791718721280114</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902877580398808</v>
+        <v>0.7902716548359171</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7887084687422008</v>
+        <v>0.7886924365862852</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7876190241163002</v>
+        <v>0.7876032873115453</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7896907922666045</v>
+        <v>0.789672422275376</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7947114542967293</v>
+        <v>0.794702805509635</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971409683474195</v>
+        <v>0.7971317666439466</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995741192967333</v>
+        <v>0.799564682720625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002761745130124</v>
+        <v>0.8002720362900637</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7985895630372042</v>
+        <v>0.7985929854461019</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991224577120816</v>
+        <v>0.7991284833891028</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040379034345808</v>
+        <v>0.8040353136184524</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8099013647870139</v>
+        <v>0.8098901623603477</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161638493180483</v>
+        <v>0.8161495068004327</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224758986201463</v>
+        <v>0.8224649868774425</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229785094385016</v>
+        <v>0.8229782580460023</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8184187578847282</v>
+        <v>0.8184355872345028</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8148375353488484</v>
+        <v>0.8148596250141833</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8130942915105256</v>
+        <v>0.8131320201804402</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8109647065821544</v>
+        <v>0.8110237391980113</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8104613042040048</v>
+        <v>0.8105354259875147</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8152871248437543</v>
+        <v>0.8153770695263394</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8207530037182603</v>
+        <v>0.8208520918389726</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8273855772996468</v>
+        <v>0.8274945554182616</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8318819543666147</v>
+        <v>0.8319952047934859</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8165504689448012</v>
+        <v>0.8166858226365665</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8183921907657745</v>
+        <v>0.8185263056566311</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.805515097296027</v>
+        <v>0.8056629788493246</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7976185786297507</v>
+        <v>0.7977567570825872</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7899337407853912</v>
+        <v>0.7900907357563991</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7801336180783887</v>
+        <v>0.7802970349380596</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7671669261273992</v>
+        <v>0.7672255376757505</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7654835125806659</v>
+        <v>0.7655173542701849</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758512738363371</v>
+        <v>0.7584977544989142</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7494850954795605</v>
+        <v>0.7494020683937686</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7415660384347471</v>
+        <v>0.7414407621733239</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7330145494552642</v>
+        <v>0.7328474769505526</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7392612308776411</v>
+        <v>0.7390131736744912</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7449873846452405</v>
+        <v>0.7447283678120021</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7538971857286036</v>
+        <v>0.7536694916671881</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7623867390759077</v>
+        <v>0.7621745517473236</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7753640446016428</v>
+        <v>0.7752720117392844</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7783894957735069</v>
+        <v>0.7785724996352883</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777669863075782</v>
+        <v>0.777949199065722</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7822449963954728</v>
+        <v>0.7819526912609125</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7868740940949812</v>
+        <v>0.7858324448158597</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7899064197600066</v>
+        <v>0.7880901140437196</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7852892894516197</v>
+        <v>0.7833737188012696</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7851214001847577</v>
+        <v>0.7825977246989343</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7840020412927335</v>
+        <v>0.7810344233115107</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7835342772688458</v>
+        <v>0.7801287231321925</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7842584367343224</v>
+        <v>0.7797381286772038</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7841469334789465</v>
+        <v>0.7792804663550152</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7835225246110904</v>
+        <v>0.7782807267362647</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.783620976803987</v>
+        <v>0.777548475229968</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,15 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7763708062392134</v>
+        <v>0.7673233730861333</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B67">
+        <v>0.7560792300615582</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777949199065722</v>
+        <v>0.7779447310867256</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7819526912609125</v>
+        <v>0.7819412535565509</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7858324448158597</v>
+        <v>0.7857987549059349</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7880901140437196</v>
+        <v>0.7880319676929566</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7833737188012696</v>
+        <v>0.783288746871446</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7825977246989343</v>
+        <v>0.7824546625522105</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7810344233115107</v>
+        <v>0.7808375390742802</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7801287231321925</v>
+        <v>0.7798671141180151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7797381286772038</v>
+        <v>0.7793613370600159</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7792804663550152</v>
+        <v>0.7788483637337529</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7782807267362647</v>
+        <v>0.777930248834319</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.777548475229968</v>
+        <v>0.7763014972844489</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7673233730861333</v>
+        <v>0.7658801623427678</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7560792300615582</v>
+        <v>0.7538150718947446</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779447310867256</v>
+        <v>0.7779439103140771</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7819412535565509</v>
+        <v>0.7819384126258266</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7857987549059349</v>
+        <v>0.7857855559049693</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7880319676929566</v>
+        <v>0.7880055370789142</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.783288746871446</v>
+        <v>0.7832465972396727</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7824546625522105</v>
+        <v>0.7823970286185677</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7808375390742802</v>
+        <v>0.7807674778050563</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7798671141180151</v>
+        <v>0.779783686366506</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7793613370600159</v>
+        <v>0.7792405709452499</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7788483637337529</v>
+        <v>0.7787053610571453</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.777930248834319</v>
+        <v>0.7777571906820416</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7763014972844489</v>
+        <v>0.7760886689739211</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7658801623427678</v>
+        <v>0.7655183269541947</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,15 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7538150718947446</v>
+        <v>0.7531701358661154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B68">
+        <v>0.7532458906709762</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788745493383735</v>
+        <v>0.7887407092690824</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921633592589075</v>
+        <v>0.7921541588316721</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915271249992355</v>
+        <v>0.7915179631548285</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7930344156390369</v>
+        <v>0.7930197734698926</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791718721280114</v>
+        <v>0.7917036393280145</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902716548359171</v>
+        <v>0.7902563276276379</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886924365862852</v>
+        <v>0.7886771773688208</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7876032873115453</v>
+        <v>0.7875883092092374</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789672422275376</v>
+        <v>0.7896549328995252</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794702805509635</v>
+        <v>0.7946945774504645</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971317666439466</v>
+        <v>0.7971230134769227</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799564682720625</v>
+        <v>0.7995557069945869</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002720362900637</v>
+        <v>0.8002680864065594</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7985929854461019</v>
+        <v>0.7985962257610162</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991284833891028</v>
+        <v>0.7991342112182926</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040353136184524</v>
+        <v>0.8040328348612712</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098901623603477</v>
+        <v>0.8098794648160241</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161495068004327</v>
+        <v>0.8161357628810169</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224649868774425</v>
+        <v>0.8224545040414147</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229782580460023</v>
+        <v>0.822977912918595</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8184355872345028</v>
+        <v>0.8184514732313917</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8148596250141833</v>
+        <v>0.8148805181982163</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8131320201804402</v>
+        <v>0.8131678136696863</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8110237391980113</v>
+        <v>0.8110798026938452</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8105354259875147</v>
+        <v>0.8106058768749551</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8153770695263394</v>
+        <v>0.8154626066432646</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8208520918389726</v>
+        <v>0.8209463815490742</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8274945554182616</v>
+        <v>0.8275983056619813</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8319952047934859</v>
+        <v>0.8321032566933106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8166858226365665</v>
+        <v>0.8168147517468038</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8185263056566311</v>
+        <v>0.8186540909605485</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8056629788493246</v>
+        <v>0.8058038416864468</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7977567570825872</v>
+        <v>0.7978884316317013</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7900907357563991</v>
+        <v>0.7902404454110364</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7802970349380596</v>
+        <v>0.7804530874931883</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7672255376757505</v>
+        <v>0.7672817523410693</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7655173542701849</v>
+        <v>0.7655501360299154</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584977544989142</v>
+        <v>0.7584841381192871</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7494020683937686</v>
+        <v>0.7493236167592287</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7414407621733239</v>
+        <v>0.7413221441288462</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7328474769505526</v>
+        <v>0.7326889278376558</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7390131736744912</v>
+        <v>0.7387767893124112</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7447283678120021</v>
+        <v>0.7444813122516883</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7536694916671881</v>
+        <v>0.7534519896327021</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7621745517473236</v>
+        <v>0.7619715135625973</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7752720117392844</v>
+        <v>0.7751839119272119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7785724996352883</v>
+        <v>0.7787331818861181</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779439103140771</v>
+        <v>0.7780589975796028</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7819384126258266</v>
+        <v>0.7816205888880332</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7857855559049693</v>
+        <v>0.7848801735739752</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7880055370789142</v>
+        <v>0.7866409051107457</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7832465972396727</v>
+        <v>0.7820699691043367</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7823970286185677</v>
+        <v>0.7809632119390515</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7807674778050563</v>
+        <v>0.7791195962194504</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.779783686366506</v>
+        <v>0.7778651767579586</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7792405709452499</v>
+        <v>0.7766754755760847</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7787053610571453</v>
+        <v>0.775964342195166</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7777571906820416</v>
+        <v>0.7751037430190897</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7760886689739211</v>
+        <v>0.7727552695792186</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7655183269541947</v>
+        <v>0.763282048830551</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7531701358661154</v>
+        <v>0.75459436531201</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,15 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.7532458906709762</v>
+        <v>0.7538743825600142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B69">
+        <v>0.753995920393483</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887407092690824</v>
+        <v>0.7887361528370885</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921541588316721</v>
+        <v>0.7921453942536874</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915179631548285</v>
+        <v>0.7915092287695836</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7930197734698926</v>
+        <v>0.7930058193714602</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7917036393280145</v>
+        <v>0.7916892665155162</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902563276276379</v>
+        <v>0.7902417216945996</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886771773688208</v>
+        <v>0.7886626365592087</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875883092092374</v>
+        <v>0.7875740362827173</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7896549328995252</v>
+        <v>0.7896382623913224</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946945774504645</v>
+        <v>0.7946867401774395</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971230134769227</v>
+        <v>0.7971146768617245</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995557069945869</v>
+        <v>0.7995471591956307</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002680864065594</v>
+        <v>0.8002643123853254</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7985962257610162</v>
+        <v>0.7985992979978154</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991342112182926</v>
+        <v>0.7991396626912382</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040328348612712</v>
+        <v>0.8040304603423181</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098794648160241</v>
+        <v>0.8098692391439911</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161357628810169</v>
+        <v>0.8161225820690774</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224545040414147</v>
+        <v>0.8224444268158682</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822977912918595</v>
+        <v>0.8229774881149994</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8184514732313917</v>
+        <v>0.818466491266872</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8148805181982163</v>
+        <v>0.8149003078029129</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8131678136696863</v>
+        <v>0.813201815499659</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8110798026938452</v>
+        <v>0.8111331133486994</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8106058768749551</v>
+        <v>0.8106729201663323</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8154626066432646</v>
+        <v>0.8155440488933045</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8209463815490742</v>
+        <v>0.8210362089392778</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8275983056619813</v>
+        <v>0.8276971904927355</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8321032566933106</v>
+        <v>0.8322064572019583</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8168147517468038</v>
+        <v>0.8169377005491008</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8186540909605485</v>
+        <v>0.8187759817778851</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8058038416864468</v>
+        <v>0.8059381702368648</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7978884316317013</v>
+        <v>0.7980140469874921</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7902404454110364</v>
+        <v>0.7903833597461879</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7804530874931883</v>
+        <v>0.7806022542346652</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7672817523410693</v>
+        <v>0.7673357073659931</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7655501360299154</v>
+        <v>0.7655818916853039</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584841381192871</v>
+        <v>0.7584717486321615</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7493236167592287</v>
+        <v>0.7492493810006353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7413221441288462</v>
+        <v>0.7412096769444279</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7326889278376558</v>
+        <v>0.7325382737790165</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7387767893124112</v>
+        <v>0.7385512808467898</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7444813122516883</v>
+        <v>0.7442454185046958</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7534519896327021</v>
+        <v>0.7532440209230489</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7619715135625973</v>
+        <v>0.7617770571901863</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7751839119272119</v>
+        <v>0.775099503387028</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7787331818861181</v>
+        <v>0.7786810133834543</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7780589975796028</v>
+        <v>0.7795266604560713</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7816205888880332</v>
+        <v>0.7830639692508452</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7848801735739752</v>
+        <v>0.7861142316405985</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7866409051107457</v>
+        <v>0.7880156578621837</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7820699691043367</v>
+        <v>0.78425640357541</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7809632119390515</v>
+        <v>0.7836946324173797</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7791195962194504</v>
+        <v>0.782611466827962</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7778651767579586</v>
+        <v>0.7819388937428493</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7766754755760847</v>
+        <v>0.7812400781064472</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.775964342195166</v>
+        <v>0.7810006347485601</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7751037430190897</v>
+        <v>0.7807979818226085</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7727552695792186</v>
+        <v>0.7796704230726087</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.763282048830551</v>
+        <v>0.7757922940212324</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.75459436531201</v>
+        <v>0.7735938890362589</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.7538743825600142</v>
+        <v>0.7732784604765247</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.753995920393483</v>
+        <v>0.783126213415769</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887361528370885</v>
+        <v>0.7887318082147945</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921453942536874</v>
+        <v>0.7921370352821069</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915092287695836</v>
+        <v>0.7915008926388478</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7930058193714602</v>
+        <v>0.7929925059982574</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916892665155162</v>
+        <v>0.7916755540208077</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902417216945996</v>
+        <v>0.7902277873385467</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886626365592087</v>
+        <v>0.7886487646339706</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875740362827173</v>
+        <v>0.7875604199203142</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7896382623913224</v>
+        <v>0.7896223546358621</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946867401774395</v>
+        <v>0.7946792665214825</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971146768617245</v>
+        <v>0.7971067277814274</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995471591956307</v>
+        <v>0.7995390094610141</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002643123853254</v>
+        <v>0.8002607028184796</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7985992979978154</v>
+        <v>0.7986022147813436</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991396626912382</v>
+        <v>0.7991448572856171</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040304603423181</v>
+        <v>0.8040281837703201</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098692391439911</v>
+        <v>0.8098594551148188</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161225820690774</v>
+        <v>0.8161099314986121</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224444268158682</v>
+        <v>0.8224347333956978</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229774881149994</v>
+        <v>0.8229769957215792</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818466491266872</v>
+        <v>0.8184807090414734</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149003078029129</v>
+        <v>0.8149190774912953</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813201815499659</v>
+        <v>0.813234155476227</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8111331133486994</v>
+        <v>0.8111838671203061</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8106729201663323</v>
+        <v>0.8107367948079767</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8155440488933045</v>
+        <v>0.815621680381619</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8210362089392778</v>
+        <v>0.821121879794698</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8276971904927355</v>
+        <v>0.8277915400502187</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8322064572019583</v>
+        <v>0.8323051234719657</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8169377005491008</v>
+        <v>0.8170550735020277</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8187759817778851</v>
+        <v>0.8188923744605485</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8059381702368648</v>
+        <v>0.8060664056776976</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7980140469874921</v>
+        <v>0.7981340085750087</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7903833597461879</v>
+        <v>0.7905199262921118</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7806022542346652</v>
+        <v>0.7807449738614587</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7673357073659931</v>
+        <v>0.7673875304315658</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7655818916853039</v>
+        <v>0.7656126557328359</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584717486321615</v>
+        <v>0.7584604622446488</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7492493810006353</v>
+        <v>0.7491790375965957</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7412096769444279</v>
+        <v>0.741102902751279</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7325382737790165</v>
+        <v>0.7323949460702974</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7385512808467898</v>
+        <v>0.7383359215399321</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7442454185046958</v>
+        <v>0.7440199558558169</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7532440209230489</v>
+        <v>0.7530449814096141</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7617770571901863</v>
+        <v>0.7615906601335705</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.775099503387028</v>
+        <v>0.7750185632830334</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7786810133834543</v>
+        <v>0.7786308674218961</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7795266604560713</v>
+        <v>0.7794645385444234</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7830639692508452</v>
+        <v>0.7841876575226622</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7861142316405985</v>
+        <v>0.7871751910808512</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7880156578621837</v>
+        <v>0.7889803089880387</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.78425640357541</v>
+        <v>0.7856750794285939</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7836946324173797</v>
+        <v>0.7851561759581772</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.782611466827962</v>
+        <v>0.7842018960222149</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7819388937428493</v>
+        <v>0.7835815504138298</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7812400781064472</v>
+        <v>0.7827450124939221</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7810006347485601</v>
+        <v>0.7819927959022149</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7807979818226085</v>
+        <v>0.7806978407628398</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7796704230726087</v>
+        <v>0.7816231121949708</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7757922940212324</v>
+        <v>0.7791827111576135</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7735938890362589</v>
+        <v>0.7781645104907821</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.7732784604765247</v>
+        <v>0.7779228498427531</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.783126213415769</v>
+        <v>0.7858827727582587</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>45814</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>45821</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>45828</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>45835</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>45842</v>
       </c>
       <c r="B6">
@@ -412,507 +438,515 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887318082147945</v>
+        <v>0.7887276609709339</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921370352821069</v>
+        <v>0.7921290544078231</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7915008926388478</v>
+        <v>0.7914929281565878</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929925059982574</v>
+        <v>0.7929797902474617</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916755540208077</v>
+        <v>0.7916624573993227</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902277873385467</v>
+        <v>0.7902144793206699</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886487646339706</v>
+        <v>0.7886355165154313</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875604199203142</v>
+        <v>0.7875474158743496</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7896223546358621</v>
+        <v>0.7896071585239796</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946792665214825</v>
+        <v>0.7946721317728123</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7971067277814274</v>
+        <v>0.7970991398507095</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995390094610141</v>
+        <v>0.7995312306410549</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002607028184796</v>
+        <v>0.8002572472563492</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986022147813436</v>
+        <v>0.7986049875126621</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991448572856171</v>
+        <v>0.7991498126951376</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040281837703201</v>
+        <v>0.804025999335367</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098594551148188</v>
+        <v>0.8098500849972048</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8161099314986121</v>
+        <v>0.8160977807066894</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224347333956978</v>
+        <v>0.8224254033732231</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229769957215792</v>
+        <v>0.8229764461495794</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8184807090414734</v>
+        <v>0.8184941875082865</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149190774912953</v>
+        <v>0.8149369027947464</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813234155476227</v>
+        <v>0.8132649512762771</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8111838671203061</v>
+        <v>0.8112322419576634</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8107367948079767</v>
+        <v>0.8107977181194335</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.815621680381619</v>
+        <v>0.815695759782853</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.821121879794698</v>
+        <v>0.8212036728960935</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8277915400502187</v>
+        <v>0.8278816556299228</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8323051234719657</v>
+        <v>0.832399545813476</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8170550735020277</v>
+        <v>0.817167239587081</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8188923744605485</v>
+        <v>0.8190036308056428</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8060664056776976</v>
+        <v>0.8061889506201019</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7981340085750087</v>
+        <v>0.7982486867388914</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7905199262921118</v>
+        <v>0.7906505545579532</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7807449738614587</v>
+        <v>0.7808816492418083</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7673875304315658</v>
+        <v>0.7674373403786627</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7656126557328359</v>
+        <v>0.7656424628436307</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584604622446488</v>
+        <v>0.7584501696651327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7491790375965957</v>
+        <v>0.7491122947360622</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.741102902751279</v>
+        <v>0.7410014073572145</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7323949460702974</v>
+        <v>0.7322584287972078</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7383359215399321</v>
+        <v>0.7381300473772087</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7440199558558169</v>
+        <v>0.7438042552075905</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7530449814096141</v>
+        <v>0.7528543161146137</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7615906601335705</v>
+        <v>0.7614118405191302</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7750185632830334</v>
+        <v>0.7749408859584478</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7786308674218961</v>
+        <v>0.778582632371182</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7794645385444234</v>
+        <v>0.7794048500969177</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7841876575226622</v>
+        <v>0.7841533393327861</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7871751910808512</v>
+        <v>0.7888120555597116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7889803089880387</v>
+        <v>0.7907975251201442</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7856750794285939</v>
+        <v>0.7878994687213512</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7851561759581772</v>
+        <v>0.7878514680982271</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7842018960222149</v>
+        <v>0.7871123032367833</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7835815504138298</v>
+        <v>0.7866358722166878</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7827450124939221</v>
+        <v>0.78605583411237</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7819927959022149</v>
+        <v>0.7855015739461603</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7806978407628398</v>
+        <v>0.7845228668008043</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7816231121949708</v>
+        <v>0.7846940677442233</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7791827111576135</v>
+        <v>0.7860166471548677</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7781645104907821</v>
+        <v>0.7865217543138608</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.7779228498427531</v>
+        <v>0.786800736620222</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.7858827727582587</v>
+        <v>0.7952536179891544</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B70">
+        <v>0.8099911179891544</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887276609709339</v>
+        <v>0.7887236979559136</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921290544078231</v>
+        <v>0.7921214265535131</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914929281565878</v>
+        <v>0.7914853110329239</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929797902474617</v>
+        <v>0.792967632794479</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916624573993227</v>
+        <v>0.7916499361043371</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902144793206699</v>
+        <v>0.7902017563728073</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886355165154313</v>
+        <v>0.7886228510841924</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875474158743496</v>
+        <v>0.7875349837825766</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7896071585239796</v>
+        <v>0.7895926274070019</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946721317728123</v>
+        <v>0.7946653134090708</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970991398507095</v>
+        <v>0.7970918890243792</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995312306410549</v>
+        <v>0.7995237979981207</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002572472563492</v>
+        <v>0.8002539361098026</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986049875126621</v>
+        <v>0.7986076265128653</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991498126951376</v>
+        <v>0.7991545450287489</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.804025999335367</v>
+        <v>0.804023901665609</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098500849972048</v>
+        <v>0.8098411033086308</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160977807066894</v>
+        <v>0.8160861014312168</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224254033732231</v>
+        <v>0.8224164176470782</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229764461495794</v>
+        <v>0.8229758483833174</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8184941875082865</v>
+        <v>0.8185069816823723</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149369027947464</v>
+        <v>0.8149538520663474</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8132649512762771</v>
+        <v>0.8132943098206526</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8112322419576634</v>
+        <v>0.8112783998072195</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8107977181194335</v>
+        <v>0.8108558881651384</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.815695759782853</v>
+        <v>0.8157665230974933</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8212036728960935</v>
+        <v>0.8212818429038092</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8278816556299228</v>
+        <v>0.8279678127274842</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.832399545813476</v>
+        <v>0.8324899904520922</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.817167239587081</v>
+        <v>0.817274536094706</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8190036308056428</v>
+        <v>0.8191100817193468</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8061889506201019</v>
+        <v>0.8063061732038229</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7982486867388914</v>
+        <v>0.7983584204247073</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7906505545579532</v>
+        <v>0.7907756199379281</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7808816492418083</v>
+        <v>0.7810126509231037</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7674373403786627</v>
+        <v>0.7674852478815182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7656424628436307</v>
+        <v>0.7656713474868876</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584501696651327</v>
+        <v>0.7584407741586288</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7491122947360622</v>
+        <v>0.7490488885803445</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7410014073572145</v>
+        <v>0.7409048152258406</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7322584287972078</v>
+        <v>0.7321282529051982</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7381300473772087</v>
+        <v>0.7379330505099106</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7438042552075905</v>
+        <v>0.7435977028078993</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7528543161146137</v>
+        <v>0.7526715144066758</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7614118405191302</v>
+        <v>0.7612401533317636</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7749408859584478</v>
+        <v>0.7748662813572953</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.778582632371182</v>
+        <v>0.7785362043178089</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7794048500969177</v>
+        <v>0.7793474577273067</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7841533393327861</v>
+        <v>0.784120385789457</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7888120555597116</v>
+        <v>0.7888008425249345</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7907975251201442</v>
+        <v>0.7923461733518888</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7878994687213512</v>
+        <v>0.7900054747407118</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7878514680982271</v>
+        <v>0.7900866509331304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7871123032367833</v>
+        <v>0.7899271588153218</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7866358722166878</v>
+        <v>0.7901409983401122</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.78605583411237</v>
+        <v>0.790183874828392</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7855015739461603</v>
+        <v>0.7905105487307631</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7845228668008043</v>
+        <v>0.7908000570162583</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7846940677442233</v>
+        <v>0.7921780193167307</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7860166471548677</v>
+        <v>0.7963637823900197</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.7865217543138608</v>
+        <v>0.798501801902897</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.786800736620222</v>
+        <v>0.7999016000012253</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.7952536179891544</v>
+        <v>0.8109663315186854</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,15 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8099911179891544</v>
+        <v>0.8257038315186853</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B71">
+        <v>0.8404413315186853</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887236979559136</v>
+        <v>0.7887199071626405</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921214265535131</v>
+        <v>0.7921141288108277</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914853110329239</v>
+        <v>0.7914780190476889</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.792967632794479</v>
+        <v>0.7929559976881657</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916499361043371</v>
+        <v>0.7916379530691675</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7902017563728073</v>
+        <v>0.7901895807715072</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886228510841924</v>
+        <v>0.7886107307543324</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875349837825766</v>
+        <v>0.7875230867511918</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895926274070019</v>
+        <v>0.789578718621155</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946653134090708</v>
+        <v>0.7946587908587093</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970918890243792</v>
+        <v>0.7970849533437773</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995237979981207</v>
+        <v>0.7995166889447957</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002539361098026</v>
+        <v>0.8002507605641743</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986076265128653</v>
+        <v>0.7986101411471971</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991545450287489</v>
+        <v>0.7991590689837966</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.804023901665609</v>
+        <v>0.8040218857882664</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098411033086308</v>
+        <v>0.8098324865948185</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160861014312168</v>
+        <v>0.8160748674267028</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224164176470782</v>
+        <v>0.8224077583347499</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229758483833174</v>
+        <v>0.8229752101881694</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185069816823723</v>
+        <v>0.8185191413375965</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149538520663474</v>
+        <v>0.8149699873044475</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8132943098206526</v>
+        <v>0.8133223284660767</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8112783998072195</v>
+        <v>0.8113224883586606</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8108558881651384</v>
+        <v>0.8109114858232506</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8157665230974933</v>
+        <v>0.8158341860606304</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8212818429038092</v>
+        <v>0.8213566228839403</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8279678127274842</v>
+        <v>0.8280502637102621</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8324899904520922</v>
+        <v>0.8325767019565179</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.817274536094706</v>
+        <v>0.8173772719381585</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8191100817193468</v>
+        <v>0.8192120304269993</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8063061732038229</v>
+        <v>0.8064184106846343</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7983584204247073</v>
+        <v>0.7984635204104165</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7907756199379281</v>
+        <v>0.7908954671518265</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7810126509231037</v>
+        <v>0.7811383202472799</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7674852478815182</v>
+        <v>0.7675313560734254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7656713474868876</v>
+        <v>0.7656993436472056</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584407741586288</v>
+        <v>0.7584321898954666</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7490488885803445</v>
+        <v>0.7489885800354688</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7409048152258406</v>
+        <v>0.740812785125019</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7321282529051982</v>
+        <v>0.7320039910442291</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7379330505099106</v>
+        <v>0.7377443734952532</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7435977028078993</v>
+        <v>0.743399734716909</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7526715144066758</v>
+        <v>0.7524961057364765</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7612401533317636</v>
+        <v>0.7610751870466987</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7748662813572953</v>
+        <v>0.7747945736108279</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7785362043178089</v>
+        <v>0.7784914864506136</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7793474577273067</v>
+        <v>0.7792922339543916</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.784120385789457</v>
+        <v>0.7840887175575666</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7888008425249345</v>
+        <v>0.7887902068088848</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923461733518888</v>
+        <v>0.7923429411573818</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7900054747407118</v>
+        <v>0.7899778498445871</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7900866509331304</v>
+        <v>0.7916145210154729</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7899271588153218</v>
+        <v>0.7916278726471838</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7901409983401122</v>
+        <v>0.7919536284661213</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.790183874828392</v>
+        <v>0.7923593834661466</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7905105487307631</v>
+        <v>0.7931642859986627</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7908000570162583</v>
+        <v>0.7939778919976496</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7921780193167307</v>
+        <v>0.7958204827356361</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7963637823900197</v>
+        <v>0.8001645475040013</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.798501801902897</v>
+        <v>0.8024911081728119</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.7999016000012253</v>
+        <v>0.8047722630242963</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8109663315186854</v>
+        <v>0.8157558996685654</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8257038315186853</v>
+        <v>0.8482641362738955</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,15 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8404413315186853</v>
+        <v>0.8627766362738956</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B72">
+        <v>0.8507387429940685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7916278726471838</v>
+        <v>0.7915825745098388</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7919536284661213</v>
+        <v>0.7918904495232482</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7923593834661466</v>
+        <v>0.7922556814687597</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7931642859986627</v>
+        <v>0.793098933257802</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7939778919976496</v>
+        <v>0.7939335733360933</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7958204827356361</v>
+        <v>0.7956982373768597</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8001645475040013</v>
+        <v>0.7998319313173975</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8024911081728119</v>
+        <v>0.8017951322292678</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8047722630242963</v>
+        <v>0.8035311564810884</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8157558996685654</v>
+        <v>0.8141010008229248</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8482641362738955</v>
+        <v>0.845127435675925</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8627766362738956</v>
+        <v>0.859639935675925</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8507387429940685</v>
+        <v>0.845127435675925</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887199071626405</v>
+        <v>0.7887162776050953</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921141288108277</v>
+        <v>0.7921071402109316</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914780190476889</v>
+        <v>0.7914710318347709</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929559976881657</v>
+        <v>0.7929448519969594</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916379530691675</v>
+        <v>0.7916264743419449</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901895807715072</v>
+        <v>0.7901779179657297</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7886107307543324</v>
+        <v>0.7885991211021255</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875230867511918</v>
+        <v>0.787511690990384</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789578718621155</v>
+        <v>0.7895653930714726</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946587908587093</v>
+        <v>0.7946525452944124</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970849533437773</v>
+        <v>0.7970783127154261</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995166889447957</v>
+        <v>0.7995098828154013</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002507605641743</v>
+        <v>0.8002477125032198</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986101411471971</v>
+        <v>0.7986125399325222</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991590689837966</v>
+        <v>0.7991633979970074</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040218857882664</v>
+        <v>0.8040199470945026</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098324865948185</v>
+        <v>0.8098242132342538</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160748674267028</v>
+        <v>0.8160640542965614</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8224077583347499</v>
+        <v>0.8223994086894231</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229752101881694</v>
+        <v>0.8229745382854681</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185191413375965</v>
+        <v>0.8185307116085838</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149699873044475</v>
+        <v>0.8149853648664438</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8133223284660767</v>
+        <v>0.8133490960431151</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8113224883586606</v>
+        <v>0.8113646425686276</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8109114858232506</v>
+        <v>0.8109646765954627</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8158341860606304</v>
+        <v>0.8158989462527441</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8213566228839403</v>
+        <v>0.8214282265268655</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8280502637102621</v>
+        <v>0.8281292401676341</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8325767019565179</v>
+        <v>0.8326599053807762</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8173772719381585</v>
+        <v>0.8174757305621394</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8192120304269993</v>
+        <v>0.8193097552932458</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8064184106846343</v>
+        <v>0.806525972585924</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7984635204104165</v>
+        <v>0.7985642721502129</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7908954671518265</v>
+        <v>0.7910104132824105</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7811383202472799</v>
+        <v>0.7812589721208933</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7675313560734254</v>
+        <v>0.7675757611258566</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7656993436472056</v>
+        <v>0.7657264846154539</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584321898954666</v>
+        <v>0.758424340544287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7489885800354688</v>
+        <v>0.7489311519562369</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.740812785125019</v>
+        <v>0.7407250063438464</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7320039910442291</v>
+        <v>0.7318852530739014</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7377443734952532</v>
+        <v>0.7375635042239849</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.743399734716909</v>
+        <v>0.7432098319153897</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7524961057364765</v>
+        <v>0.7523276558448928</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7610751870466987</v>
+        <v>0.7609165606120565</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7747945736108279</v>
+        <v>0.774725599769821</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7784914864506136</v>
+        <v>0.7784483884982452</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7792922339543916</v>
+        <v>0.7792390603514552</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7840887175575666</v>
+        <v>0.7840582613015808</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887902068088848</v>
+        <v>0.7887801059168362</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923429411573818</v>
+        <v>0.7923400904866167</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7899778498445871</v>
+        <v>0.7899515190416101</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7916145210154729</v>
+        <v>0.7929406191096096</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7915825745098388</v>
+        <v>0.7930091639263949</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7918904495232482</v>
+        <v>0.7933853547387351</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7922556814687597</v>
+        <v>0.7940078589755218</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.793098933257802</v>
+        <v>0.7952616888981452</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7939335733360933</v>
+        <v>0.796514472360788</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.7956982373768597</v>
+        <v>0.798547811318607</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.7998319313173975</v>
+        <v>0.8025073682986008</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8017951322292678</v>
+        <v>0.8042478873351407</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8035311564810884</v>
+        <v>0.8062342142461387</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8141010008229248</v>
+        <v>0.8163267479063527</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.845127435675925</v>
+        <v>0.8425267850120873</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.859639935675925</v>
+        <v>0.8532325267768197</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.845127435675925</v>
+        <v>0.8419333838944558</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887162776050953</v>
+        <v>0.7887127992120685</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921071402109316</v>
+        <v>0.7921004415235626</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914710318347709</v>
+        <v>0.7914643306928452</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929448519969594</v>
+        <v>0.7929341654986032</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916264743419449</v>
+        <v>0.7916154687654009</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901779179657297</v>
+        <v>0.7901667362504654</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885991211021255</v>
+        <v>0.7885879905405738</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.787511690990384</v>
+        <v>0.7875007654948535</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895653930714726</v>
+        <v>0.7895526148667145</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946525452944124</v>
+        <v>0.7946465594522084</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970783127154261</v>
+        <v>0.797071948717257</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995098828154013</v>
+        <v>0.7995033606660253</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002477125032198</v>
+        <v>0.8002447844417835</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986125399325222</v>
+        <v>0.7986148306306955</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991633979970074</v>
+        <v>0.7991675443765384</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040199470945026</v>
+        <v>0.8040180813077662</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098242132342538</v>
+        <v>0.8098162632645796</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160640542965614</v>
+        <v>0.8160536393405611</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223994086894231</v>
+        <v>0.8223913530214908</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229745382854681</v>
+        <v>0.8229738385000607</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185307116085838</v>
+        <v>0.8185417335124042</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8149853648664438</v>
+        <v>0.815000036089343</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8133490960431151</v>
+        <v>0.81337469376275</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8113646425686276</v>
+        <v>0.8114049859944165</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8109646765954627</v>
+        <v>0.8110156121945552</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8158989462527441</v>
+        <v>0.8159609849542642</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8214282265268655</v>
+        <v>0.821496850100512</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8281292401676341</v>
+        <v>0.8282049549836314</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8326599053807762</v>
+        <v>0.8327398081590537</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8174757305621394</v>
+        <v>0.8175701725025664</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8193097552932458</v>
+        <v>0.8194035123060996</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.806525972585924</v>
+        <v>0.8066291434745503</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7985642721502129</v>
+        <v>0.7986609382834254</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7910104132824105</v>
+        <v>0.7911207504630138</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7812589721208933</v>
+        <v>0.7813748974824655</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7675757611258566</v>
+        <v>0.7676185527830095</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7657264846154539</v>
+        <v>0.7657528028372562</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758424340544287</v>
+        <v>0.7584171580693088</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7489311519562369</v>
+        <v>0.7488764067167559</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7407250063438464</v>
+        <v>0.740641195394193</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7318852530739014</v>
+        <v>0.7317716821330875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7375635042239849</v>
+        <v>0.7373899714427234</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7432098319153897</v>
+        <v>0.7430275159707114</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7523276558448928</v>
+        <v>0.7521657633852554</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7609165606120565</v>
+        <v>0.7607639207421417</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.774725599769821</v>
+        <v>0.7746592086662696</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7784483884982452</v>
+        <v>0.7784068262145121</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7792390603514552</v>
+        <v>0.7791878267785007</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7840582613015808</v>
+        <v>0.784028949131652</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887801059168362</v>
+        <v>0.7887705013514916</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923400904866167</v>
+        <v>0.7923375832964032</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7899515190416101</v>
+        <v>0.7899263948064439</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7929406191096096</v>
+        <v>0.7929016037600667</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7930091639263949</v>
+        <v>0.7947129645213549</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7933853547387351</v>
+        <v>0.7952232455607671</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7940078589755218</v>
+        <v>0.7959224354957501</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7952616888981452</v>
+        <v>0.7974249240110276</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.796514472360788</v>
+        <v>0.7990003477025552</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.798547811318607</v>
+        <v>0.8012567107186985</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8025073682986008</v>
+        <v>0.8053234220875394</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8042478873351407</v>
+        <v>0.8071228651758861</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8062342142461387</v>
+        <v>0.808851736448516</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8163267479063527</v>
+        <v>0.8184377032300605</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8425267850120873</v>
+        <v>0.8410559514733293</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8532325267768197</v>
+        <v>0.8500759579629984</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,15 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8419333838944558</v>
+        <v>0.8422849731757143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B73">
+        <v>0.8465030792520766</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887127992120685</v>
+        <v>0.7887094627338944</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7921004415235626</v>
+        <v>0.7920940150805567</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914643306928452</v>
+        <v>0.7914578984188091</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929341654986032</v>
+        <v>0.7929239104073321</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916154687654009</v>
+        <v>0.7916049076953341</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901667362504654</v>
+        <v>0.7901560064798124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885879905405738</v>
+        <v>0.7885773100333017</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7875007654948535</v>
+        <v>0.7874902817629695</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895526148667145</v>
+        <v>0.7895403509981497</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946465594522084</v>
+        <v>0.7946408174726173</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.797071948717257</v>
+        <v>0.7970658444284825</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7995033606660253</v>
+        <v>0.7994971050989923</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002447844417835</v>
+        <v>0.8002419694660434</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986148306306955</v>
+        <v>0.798617020329927</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991675443765384</v>
+        <v>0.7991715194177997</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040180813077662</v>
+        <v>0.8040162844552323</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098162632645796</v>
+        <v>0.8098086182280984</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160536393405611</v>
+        <v>0.8160436014160672</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223913530214908</v>
+        <v>0.8223835766248626</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229738385000607</v>
+        <v>0.8229731158851835</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185417335124042</v>
+        <v>0.818552244402098</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815000036089343</v>
+        <v>0.8150140478308892</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.81337469376275</v>
+        <v>0.813399196010441</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8114049859944165</v>
+        <v>0.8114436319645689</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8110156121945552</v>
+        <v>0.8110644319406646</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8159609849542642</v>
+        <v>0.8160204687791783</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.821496850100512</v>
+        <v>0.8215626741742539</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8282049549836314</v>
+        <v>0.8282776041689988</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8327398081590537</v>
+        <v>0.8328166017855909</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8175701725025664</v>
+        <v>0.8176608376451071</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8194035123060996</v>
+        <v>0.8194935372704865</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8066291434745503</v>
+        <v>0.8067281854118651</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7986609382834254</v>
+        <v>0.798753760853226</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7911207504630138</v>
+        <v>0.7912267482608637</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7813748974824655</v>
+        <v>0.7814863655039936</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7676185527830095</v>
+        <v>0.7676598148542126</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7657528028372562</v>
+        <v>0.7657783298065544</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584171580693088</v>
+        <v>0.7584105816989926</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7488764067167559</v>
+        <v>0.7488241640931459</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.740641195394193</v>
+        <v>0.7405610931265928</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7317716821330875</v>
+        <v>0.7316629511936574</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7373899714427234</v>
+        <v>0.7372233407920376</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7430275159707114</v>
+        <v>0.742852345188833</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7521657633852554</v>
+        <v>0.7520100569091335</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7607639207421417</v>
+        <v>0.7606169394862404</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7746592086662696</v>
+        <v>0.7745952598899626</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7784068262145121</v>
+        <v>0.7783667209077199</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7791878267785007</v>
+        <v>0.7791384306885478</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.784028949131652</v>
+        <v>0.7840007181097354</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887705013514916</v>
+        <v>0.7887613581605827</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923375832964032</v>
+        <v>0.7923353857159326</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7899263948064439</v>
+        <v>0.7899023972370526</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7929016037600667</v>
+        <v>0.7928642615129139</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7947129645213549</v>
+        <v>0.7957654732386342</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7952232455607671</v>
+        <v>0.7962915639031647</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7959224354957501</v>
+        <v>0.7970163299430411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7974249240110276</v>
+        <v>0.7986055000982824</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.7990003477025552</v>
+        <v>0.8003714901850425</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8012567107186985</v>
+        <v>0.8026946999054446</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8053234220875394</v>
+        <v>0.806573471467315</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8071228651758861</v>
+        <v>0.8082055648277717</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.808851736448516</v>
+        <v>0.8096056645327385</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8184377032300605</v>
+        <v>0.8184819060920733</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8410559514733293</v>
+        <v>0.8370470605869542</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8500759579629984</v>
+        <v>0.8438936473645589</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8422849731757143</v>
+        <v>0.8376274396668453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8465030792520766</v>
+        <v>0.8368449595256862</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887094627338944</v>
+        <v>0.788706259660366</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920940150805567</v>
+        <v>0.7920878446204357</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914578984188091</v>
+        <v>0.7914517191608077</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929239104073321</v>
+        <v>0.7929140611333534</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7916049076953341</v>
+        <v>0.7915947647524164</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901560064798124</v>
+        <v>0.7901457018140529</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885773100333017</v>
+        <v>0.7885670528423693</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874902817629695</v>
+        <v>0.7874802135492245</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895403509981497</v>
+        <v>0.7895285710561861</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946408174726173</v>
+        <v>0.7946353047607686</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970658444284825</v>
+        <v>0.7970599842798223</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994971050989923</v>
+        <v>0.7994911001083668</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002419694660434</v>
+        <v>0.8002392611803716</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.798617020329927</v>
+        <v>0.7986191155158997</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991715194177997</v>
+        <v>0.7991753335053255</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040162844552323</v>
+        <v>0.8040145528420271</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8098086182280984</v>
+        <v>0.809801261034015</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160436014160672</v>
+        <v>0.8160339208118392</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223835766248626</v>
+        <v>0.8223760657080659</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229731158851835</v>
+        <v>0.8229723748284619</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818552244402098</v>
+        <v>0.818562278362129</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150140478308892</v>
+        <v>0.8150274429427844</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813399196010441</v>
+        <v>0.8134226710435438</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8114436319645689</v>
+        <v>0.8114806846090185</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8110644319406646</v>
+        <v>0.811111263992438</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8160204687791783</v>
+        <v>0.8160775511175462</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8215626741742539</v>
+        <v>0.8216258651439601</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8282776041689988</v>
+        <v>0.8283473684842713</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8328166017855909</v>
+        <v>0.8328904633073166</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8176608376451071</v>
+        <v>0.8177479472228462</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8194935372704865</v>
+        <v>0.8195800477499475</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8067281854118651</v>
+        <v>0.8068233401231276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.798753760853226</v>
+        <v>0.7988429632732447</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7912267482608637</v>
+        <v>0.791328655795101</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7814863655039936</v>
+        <v>0.7815936255586593</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7676598148542126</v>
+        <v>0.7676996256668613</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7657783298065544</v>
+        <v>0.7658030959943779</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584105816989926</v>
+        <v>0.7584045570390266</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7488241640931459</v>
+        <v>0.7487742594130486</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7405610931265928</v>
+        <v>0.7404844622015657</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7316629511936574</v>
+        <v>0.7315587600306405</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7372233407920376</v>
+        <v>0.7370632112929236</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.742852345188833</v>
+        <v>0.7426839111907638</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7520100569091335</v>
+        <v>0.7518601921717996</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7606169394862404</v>
+        <v>0.7604753120419324</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7745952598899626</v>
+        <v>0.7745336228671358</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7783667209077199</v>
+        <v>0.7783279990103065</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7791384306885478</v>
+        <v>0.7790907765001847</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7840007181097354</v>
+        <v>0.7839735098082827</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887613581605827</v>
+        <v>0.7887526445437899</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923353857159326</v>
+        <v>0.7923334675325333</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7899023972370526</v>
+        <v>0.7898794532510012</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7928642615129139</v>
+        <v>0.7928284882875026</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7957654732386342</v>
+        <v>0.7964104122318525</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7962915639031647</v>
+        <v>0.7969189293666952</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7970163299430411</v>
+        <v>0.7976548314187228</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7986055000982824</v>
+        <v>0.7992650635542438</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8003714901850425</v>
+        <v>0.8011223050804768</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8026946999054446</v>
+        <v>0.803431573213365</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.806573471467315</v>
+        <v>0.8070017556953937</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8082055648277717</v>
+        <v>0.8083898216577916</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8096056645327385</v>
+        <v>0.8094551759159834</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8184819060920733</v>
+        <v>0.8176085444203991</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8370470605869542</v>
+        <v>0.8329155483319834</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8438936473645589</v>
+        <v>0.8382432635755841</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8376274396668453</v>
+        <v>0.8329077190330448</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8368449595256862</v>
+        <v>0.8301546649208382</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788706259660366</v>
+        <v>0.7887002229574406</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920878446204357</v>
+        <v>0.7920762128287642</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914517191608077</v>
+        <v>0.7914400622763342</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7929140611333534</v>
+        <v>0.7928954874065763</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915947647524164</v>
+        <v>0.7915756377638636</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901457018140529</v>
+        <v>0.7901262706535858</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885670528423693</v>
+        <v>0.7885477116381713</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874802135492245</v>
+        <v>0.7874612286870986</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895285710561861</v>
+        <v>0.7895063528340783</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946353047607686</v>
+        <v>0.7946249143570466</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970599842798223</v>
+        <v>0.7970489401052276</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994911001083668</v>
+        <v>0.7994797839889124</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002392611803716</v>
+        <v>0.8002341414085747</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986191155158997</v>
+        <v>0.7986230456446498</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991753335053255</v>
+        <v>0.7991825163315585</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040145528420271</v>
+        <v>0.8040112718063385</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809801261034015</v>
+        <v>0.8097873479189124</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160339208118392</v>
+        <v>0.8160155591975479</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223760657080659</v>
+        <v>0.822361789340375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229723748284619</v>
+        <v>0.8229708521400956</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818562278362129</v>
+        <v>0.8185810375204012</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150274429427844</v>
+        <v>0.815052537093972</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8134226710435438</v>
+        <v>0.8134667854677767</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8114806846090185</v>
+        <v>0.8115503857956203</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.811111263992438</v>
+        <v>0.8111994282454105</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8160775511175462</v>
+        <v>0.8161850662920143</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8216258651439601</v>
+        <v>0.8217449504498122</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8283473684842713</v>
+        <v>0.8284788977833282</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8328904633073166</v>
+        <v>0.8330300338189414</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8177479472228462</v>
+        <v>0.8179123017829022</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8195800477499475</v>
+        <v>0.8197433144473478</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8068233401231276</v>
+        <v>0.8070028644224235</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7988429632732447</v>
+        <v>0.7990113184614343</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.791328655795101</v>
+        <v>0.7915211054227186</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7815936255586593</v>
+        <v>0.781796430654623</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7676996256668613</v>
+        <v>0.7677751818796683</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7658030959943779</v>
+        <v>0.7658504625534921</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7584045570390266</v>
+        <v>0.7583939726718201</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7487742594130486</v>
+        <v>0.7486808734178422</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7404844622015657</v>
+        <v>0.7403407609979492</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7315587600306405</v>
+        <v>0.7313629144373274</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7370632112929236</v>
+        <v>0.7367610003407482</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7426839111907638</v>
+        <v>0.7423657686192908</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7518601921717996</v>
+        <v>0.751576732724078</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7604753120419324</v>
+        <v>0.7602070034964707</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7745336228671358</v>
+        <v>0.7744168060666619</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7783279990103065</v>
+        <v>0.7782544344663754</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7790907765001847</v>
+        <v>0.7790003429747794</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7839735098082827</v>
+        <v>0.7839219478789583</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887526445437899</v>
+        <v>0.7887363925789572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923334675325333</v>
+        <v>0.7923303641959294</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7898794532510012</v>
+        <v>0.7898364636518738</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7928284882875026</v>
+        <v>0.792761273592459</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7964104122318525</v>
+        <v>0.7979397470309396</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7969189293666952</v>
+        <v>0.7984482950299363</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7976548314187228</v>
+        <v>0.7991839142683426</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.7992650635542438</v>
+        <v>0.8008424644628181</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8011223050804768</v>
+        <v>0.8028724813265236</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.803431573213365</v>
+        <v>0.805159237754565</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8070017556953937</v>
+        <v>0.8083396548631792</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8083898216577916</v>
+        <v>0.8094731259321516</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8094551759159834</v>
+        <v>0.8100076217733848</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8176085444203991</v>
+        <v>0.8165917183689031</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8329155483319834</v>
+        <v>0.8281103868594198</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8382432635755841</v>
+        <v>0.8321317098846712</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8329077190330448</v>
+        <v>0.8285763757232516</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8301546649208382</v>
+        <v>0.8265577275866988</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7887002229574406</v>
+        <v>0.788697375393639</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920762128287642</v>
+        <v>0.7920707248493516</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914400622763342</v>
+        <v>0.791434558603907</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928954874065763</v>
+        <v>0.7928867209585715</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915756377638636</v>
+        <v>0.7915666104313402</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901262706535858</v>
+        <v>0.7901171001227307</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885477116381713</v>
+        <v>0.7885385837592112</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874612286870986</v>
+        <v>0.7874522689809534</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7895063528340783</v>
+        <v>0.7894958646132656</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946249143570466</v>
+        <v>0.7946200127560397</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970489401052276</v>
+        <v>0.797043730582461</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994797839889124</v>
+        <v>0.7994744466562592</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002341414085747</v>
+        <v>0.8002317193206167</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986230456446498</v>
+        <v>0.7986248910705134</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991825163315585</v>
+        <v>0.7991859020428412</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040112718063385</v>
+        <v>0.8040097161851366</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097873479189124</v>
+        <v>0.8097807636062988</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160155591975479</v>
+        <v>0.8160068449391421</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822361789340375</v>
+        <v>0.8223550003239892</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229708521400956</v>
+        <v>0.8229700767037437</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185810375204012</v>
+        <v>0.8185898174499295</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815052537093972</v>
+        <v>0.8150643052975659</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8134667854677767</v>
+        <v>0.8134875359101451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8115503857956203</v>
+        <v>0.8115832042729452</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8111994282454105</v>
+        <v>0.8112409701462622</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8161850662920143</v>
+        <v>0.8162357505779552</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8217449504498122</v>
+        <v>0.8218011181459659</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8284788977833282</v>
+        <v>0.8285409602325586</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8330300338189414</v>
+        <v>0.8330960359298394</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8179123017829022</v>
+        <v>0.8179899109475195</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8197433144473478</v>
+        <v>0.8198204291608386</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8070028644224235</v>
+        <v>0.8070876320622657</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7990113184614343</v>
+        <v>0.7990908396982085</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7915211054227186</v>
+        <v>0.7916120594987308</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.781796430654623</v>
+        <v>0.7818923904159509</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7677751818796683</v>
+        <v>0.7678110601034935</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7658504625534921</v>
+        <v>0.7658731184592869</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583939726718201</v>
+        <v>0.7583893296774527</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7486808734178422</v>
+        <v>0.7486371268765226</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7403407609979492</v>
+        <v>0.7402733063684832</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7313629144373274</v>
+        <v>0.7312707710511646</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7367610003407482</v>
+        <v>0.7366182573922775</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7423657686192908</v>
+        <v>0.7422153839853873</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.751576732724078</v>
+        <v>0.7514425650401593</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7602070034964707</v>
+        <v>0.7600798117520153</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7744168060666619</v>
+        <v>0.7743614072442734</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7782544344663754</v>
+        <v>0.7782194669285294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7790003429747794</v>
+        <v>0.7789574024497827</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7839219478789583</v>
+        <v>0.7838974965908416</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887363925789572</v>
+        <v>0.788728803516954</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923303641959294</v>
+        <v>0.7923291332075659</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7898364636518738</v>
+        <v>0.7898163000396057</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792761273592459</v>
+        <v>0.7927296626199879</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7979397470309396</v>
+        <v>0.7985897258148771</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7984482950299363</v>
+        <v>0.7991043517185161</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7991839142683426</v>
+        <v>0.7998405598105833</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8008424644628181</v>
+        <v>0.8015240800879956</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8028724813265236</v>
+        <v>0.8036017464773459</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.805159237754565</v>
+        <v>0.8058576742631851</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8083396548631792</v>
+        <v>0.8088664033846771</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094731259321516</v>
+        <v>0.8099203068157792</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8100076217733848</v>
+        <v>0.8102284117911298</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8165917183689031</v>
+        <v>0.8162597150515214</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8281103868594198</v>
+        <v>0.8265595195057471</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8321317098846712</v>
+        <v>0.8301999537820104</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285763757232516</v>
+        <v>0.8272766841313304</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8265577275866988</v>
+        <v>0.8257150548480585</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788697375393639</v>
+        <v>0.7886946332583087</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920707248493516</v>
+        <v>0.7920654393534372</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791434558603907</v>
+        <v>0.7914292556618091</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928867209585715</v>
+        <v>0.792878276021158</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915666104313402</v>
+        <v>0.791557914325874</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901171001227307</v>
+        <v>0.7901082662920438</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885385837592112</v>
+        <v>0.788529791133797</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874522689809534</v>
+        <v>0.7874436383521118</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894958646132656</v>
+        <v>0.7894857600643701</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946200127560397</v>
+        <v>0.7946152924212575</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.797043730582461</v>
+        <v>0.797038714010077</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994744466562592</v>
+        <v>0.7994693072902483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002317193206167</v>
+        <v>0.8002293826472849</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986248910705134</v>
+        <v>0.7986266630402374</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991859020428412</v>
+        <v>0.7991891608784808</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040097161851366</v>
+        <v>0.8040082133694688</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097807636062988</v>
+        <v>0.8097744101654241</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8160068449391421</v>
+        <v>0.8159984213224203</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223550003239892</v>
+        <v>0.8223484295496577</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229700767037437</v>
+        <v>0.822969295338574</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185898174499295</v>
+        <v>0.8185982304139187</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150643052975659</v>
+        <v>0.8150755958059454</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8134875359101451</v>
+        <v>0.8135074821458168</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8115832042729452</v>
+        <v>0.8116147706406641</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8112409701462622</v>
+        <v>0.8112809453702515</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8162357505779552</v>
+        <v>0.8162845381815437</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8218011181459659</v>
+        <v>0.8218552014829482</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8285409602325586</v>
+        <v>0.8286007349071932</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8330960359298394</v>
+        <v>0.8331596941881692</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8179899109475195</v>
+        <v>0.8180646955646564</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8198204291608386</v>
+        <v>0.8198947489651814</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8070876320622657</v>
+        <v>0.8071693114661342</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7990908396982085</v>
+        <v>0.7991674803504747</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7916120594987308</v>
+        <v>0.791699750129139</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7818923904159509</v>
+        <v>0.7819849743467416</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7678110601034935</v>
+        <v>0.7678457533889946</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7658731184592869</v>
+        <v>0.7658951246527541</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583893296774527</v>
+        <v>0.7583850707462734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7486371268765226</v>
+        <v>0.7485951854623912</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7402733063684832</v>
+        <v>0.7402085511167651</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7312707710511646</v>
+        <v>0.7311821855844514</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7366182573922775</v>
+        <v>0.7364806879025441</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7422153839853873</v>
+        <v>0.7420703793875013</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7514425650401593</v>
+        <v>0.75131308945301</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7600798117520153</v>
+        <v>0.7599569494777816</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7743614072442734</v>
+        <v>0.7743078807949875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7782194669285294</v>
+        <v>0.7781856323866294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7789574024497827</v>
+        <v>0.7789158805585314</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7838974965908416</v>
+        <v>0.783873872097233</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788728803516954</v>
+        <v>0.7887215421083671</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923291332075659</v>
+        <v>0.7923280893245601</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7898163000396057</v>
+        <v>0.7897969529821898</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7927296626199879</v>
+        <v>0.7926992802983005</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7985897258148771</v>
+        <v>0.7985406440531932</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7991043517185161</v>
+        <v>0.7997806219991624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.7998405598105833</v>
+        <v>0.8005259845770867</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8015240800879956</v>
+        <v>0.8022090569193125</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8036017464773459</v>
+        <v>0.8044027972073845</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8058576742631851</v>
+        <v>0.8066648766301996</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088664033846771</v>
+        <v>0.8096649289583677</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8099203068157792</v>
+        <v>0.8107283111037774</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8102284117911298</v>
+        <v>0.8111656259510951</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8162597150515214</v>
+        <v>0.8168526768457702</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8265595195057471</v>
+        <v>0.8268324238805451</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8301999537820104</v>
+        <v>0.8304652157575256</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8272766841313304</v>
+        <v>0.8285191387709745</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,15 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8257150548480585</v>
+        <v>0.8281596853591007</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B74">
+        <v>0.8312558458092298</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886946332583087</v>
+        <v>0.7886919908034127</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920654393534372</v>
+        <v>0.7920603453403783</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914292556618091</v>
+        <v>0.7914241426715301</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.792878276021158</v>
+        <v>0.7928701352350555</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791557914325874</v>
+        <v>0.7915495315557924</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7901082662920438</v>
+        <v>0.7900997509625352</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788529791133797</v>
+        <v>0.7885213156347022</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874436383521118</v>
+        <v>0.7874353190072393</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894857600643701</v>
+        <v>0.7894760185304204</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946152924212575</v>
+        <v>0.7946107434857332</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.797038714010077</v>
+        <v>0.7970338798691518</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994693072902483</v>
+        <v>0.799464355083366</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002293826472849</v>
+        <v>0.8002271269660592</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986266630402374</v>
+        <v>0.7986283658256934</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991891608784808</v>
+        <v>0.7991922998275158</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040082133694688</v>
+        <v>0.8040067607460269</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097744101654241</v>
+        <v>0.8097682757305789</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159984213224203</v>
+        <v>0.8159902742628951</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223484295496577</v>
+        <v>0.8223420669224862</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822969295338574</v>
+        <v>0.8229685102227629</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8185982304139187</v>
+        <v>0.8186062985731194</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150755958059454</v>
+        <v>0.8150864367599753</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8135074821458168</v>
+        <v>0.8135266697000609</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8116147706406641</v>
+        <v>0.8116451547631536</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8112809453702515</v>
+        <v>0.8113194403384596</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8162845381815437</v>
+        <v>0.8163315329055575</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8218552014829482</v>
+        <v>0.8219073135299197</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8286007349071932</v>
+        <v>0.8286583450378303</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8331596941881692</v>
+        <v>0.8332211307270037</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8180646955646564</v>
+        <v>0.8181368065816854</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8198947489651814</v>
+        <v>0.8199664225849215</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8071693114661342</v>
+        <v>0.8072480676630417</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7991674803504747</v>
+        <v>0.7992413933957863</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.791699750129139</v>
+        <v>0.7917843487756886</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7819849743467416</v>
+        <v>0.7820743559171345</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7678457533889946</v>
+        <v>0.7678793182560367</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7658951246527541</v>
+        <v>0.7659165061908707</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583850707462734</v>
+        <v>0.7583811637429447</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7485951854623912</v>
+        <v>0.748554941487507</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7402085511167651</v>
+        <v>0.7401463383862069</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7311821855844514</v>
+        <v>0.7310969574055367</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7364806879025441</v>
+        <v>0.736348017180952</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7420703793875013</v>
+        <v>0.7419304731999907</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.75131308945301</v>
+        <v>0.7511880661018261</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7599569494777816</v>
+        <v>0.7598382016334981</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7743078807949875</v>
+        <v>0.7742561343605581</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7781856323866294</v>
+        <v>0.778152877619334</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7789158805585314</v>
+        <v>0.7788757090094358</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.783873872097233</v>
+        <v>0.7838510333412751</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887215421083671</v>
+        <v>0.7887145879516727</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923280893245601</v>
+        <v>0.7923272150464427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897969529821898</v>
+        <v>0.7897783744543424</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7926992802983005</v>
+        <v>0.7926700570871338</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7985406440531932</v>
+        <v>0.798493272913912</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.7997806219991624</v>
+        <v>0.8005627696707572</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8005259845770867</v>
+        <v>0.8013549049095865</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8022090569193125</v>
+        <v>0.8030516778271294</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8044027972073845</v>
+        <v>0.8053906631123521</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8066648766301996</v>
+        <v>0.807690061972997</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8096649289583677</v>
+        <v>0.8107146902646445</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8107283111037774</v>
+        <v>0.8118261488629654</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8111656259510951</v>
+        <v>0.8124081571932662</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8168526768457702</v>
+        <v>0.8178282478906778</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8268324238805451</v>
+        <v>0.8276904743064669</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8304652157575256</v>
+        <v>0.8314114959321526</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285191387709745</v>
+        <v>0.8302987583659861</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8281596853591007</v>
+        <v>0.8309857547851691</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8312558458092298</v>
+        <v>0.8420918400412694</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8013549049095865</v>
+        <v>0.8013556886482296</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8030516778271294</v>
+        <v>0.8030536290109564</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8053906631123521</v>
+        <v>0.8053884661811368</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.807690061972997</v>
+        <v>0.8076995019019136</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8107146902646445</v>
+        <v>0.8107225524700906</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8118261488629654</v>
+        <v>0.8118374711299556</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8124081571932662</v>
+        <v>0.8124263845861883</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8178282478906778</v>
+        <v>0.8180434410249199</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8276904743064669</v>
+        <v>0.8279269648383828</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8314114959321526</v>
+        <v>0.8316346243376691</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8302987583659861</v>
+        <v>0.8304487531950534</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8309857547851691</v>
+        <v>0.8311323102976365</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8420918400412694</v>
+        <v>0.8422351239107665</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8013556886482296</v>
+        <v>0.8013551596585822</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8030536290109564</v>
+        <v>0.803049357289338</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8053884661811368</v>
+        <v>0.8053703382512936</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8076995019019136</v>
+        <v>0.8076657973160609</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8107225524700906</v>
+        <v>0.8106958040847756</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8118374711299556</v>
+        <v>0.8118155373496361</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8124263845861883</v>
+        <v>0.8122274184471265</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8180434410249199</v>
+        <v>0.8178910986224265</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8279269648383828</v>
+        <v>0.8277743133671812</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8316346243376691</v>
+        <v>0.8315529274517626</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8304487531950534</v>
+        <v>0.8303548761225154</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8311323102976365</v>
+        <v>0.8310468251805483</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8422351239107665</v>
+        <v>0.841995567293481</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886919908034127</v>
+        <v>0.7886894426912614</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920603453403783</v>
+        <v>0.7920554325920459</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914241426715301</v>
+        <v>0.7914192096122351</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928701352350555</v>
+        <v>0.7928622824679449</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915495315557924</v>
+        <v>0.7915414454945474</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900997509625352</v>
+        <v>0.7900915372228858</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885213156347022</v>
+        <v>0.7885131404177478</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874353190072393</v>
+        <v>0.7874272944124217</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894760185304204</v>
+        <v>0.7894666208099788</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946107434857332</v>
+        <v>0.7946063567854778</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970338798691518</v>
+        <v>0.7970292183913112</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799464355083366</v>
+        <v>0.7994595800002994</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002271269660592</v>
+        <v>0.8002249481532885</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986283658256934</v>
+        <v>0.7986300033756261</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7991922998275158</v>
+        <v>0.799195325375698</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040067607460269</v>
+        <v>0.8040053558688085</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097682757305789</v>
+        <v>0.8097623492305135</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159902742628951</v>
+        <v>0.815982390554991</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223420669224862</v>
+        <v>0.8223359029398774</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229685102227629</v>
+        <v>0.8229677232490706</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186062985731194</v>
+        <v>0.8186140423617565</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150864367599753</v>
+        <v>0.8150968541553697</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8135266697000609</v>
+        <v>0.8135451407472827</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8116451547631536</v>
+        <v>0.8116744214315539</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8113194403384596</v>
+        <v>0.8113565352679386</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8163315329055575</v>
+        <v>0.8163768311609743</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8219073135299197</v>
+        <v>0.8219575593797258</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8286583450378303</v>
+        <v>0.8287139052269177</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8332211307270037</v>
+        <v>0.8332804593765561</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8181368065816854</v>
+        <v>0.8182063844125582</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8199664225849215</v>
+        <v>0.8200355884122574</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8072480676630417</v>
+        <v>0.8073240541786828</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7992413933957863</v>
+        <v>0.7993127212207949</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7917843487756886</v>
+        <v>0.7918660151712655</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7820743559171345</v>
+        <v>0.7821606970259075</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7678793182560367</v>
+        <v>0.7679118077808189</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659165061908707</v>
+        <v>0.7659372870800873</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583811637429447</v>
+        <v>0.7583775795946353</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.748554941487507</v>
+        <v>0.7485162955529696</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7401463383862069</v>
+        <v>0.7400865231155065</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7310969574055367</v>
+        <v>0.7310149005881883</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.736348017180952</v>
+        <v>0.7362199895370847</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7419304731999907</v>
+        <v>0.7417954029754253</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7511880661018261</v>
+        <v>0.7510672710551716</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7598382016334981</v>
+        <v>0.7597233670219552</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7742561343605581</v>
+        <v>0.774206081487932</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.778152877619334</v>
+        <v>0.7781211526160967</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7788757090094358</v>
+        <v>0.7788368237635823</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7838510333412751</v>
+        <v>0.7838289419289814</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887145879516727</v>
+        <v>0.7887079222804214</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923272150464427</v>
+        <v>0.7923264946110531</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897783744543424</v>
+        <v>0.7897605200866828</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7926700570871338</v>
+        <v>0.7926419285492809</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.798493272913912</v>
+        <v>0.7984475258180792</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8005627696707572</v>
+        <v>0.8013472847710745</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8013551596585822</v>
+        <v>0.8021968037595031</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.803049357289338</v>
+        <v>0.803906163000994</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8053703382512936</v>
+        <v>0.806360264279643</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8076657973160609</v>
+        <v>0.8086829014718684</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8106958040847756</v>
+        <v>0.8117420864769636</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8118155373496361</v>
+        <v>0.8129147025380571</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8122274184471265</v>
+        <v>0.8133094064724768</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8178910986224265</v>
+        <v>0.8187718953620322</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8277743133671812</v>
+        <v>0.8285874676642468</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8315529274517626</v>
+        <v>0.8325178140845659</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8303548761225154</v>
+        <v>0.8320203630029976</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8310468251805483</v>
+        <v>0.8335406506700309</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.841995567293481</v>
+        <v>0.8466129148980073</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886894426912614</v>
+        <v>0.7886869839585411</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920554325920459</v>
+        <v>0.7920506916044792</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914192096122351</v>
+        <v>0.7914144471553776</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928622824679449</v>
+        <v>0.7928547027080032</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915414454945474</v>
+        <v>0.791533640670893</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900915372228858</v>
+        <v>0.7900836093375987</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885131404177478</v>
+        <v>0.7885052498103138</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874272944124217</v>
+        <v>0.7874195491837304</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894666208099788</v>
+        <v>0.7894575490312642</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946063567854778</v>
+        <v>0.7946021237980018</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970292183913112</v>
+        <v>0.7970247204929947</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994595800002994</v>
+        <v>0.7994549727102153</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002249481532885</v>
+        <v>0.8002228423594783</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986300033756261</v>
+        <v>0.7986315793454929</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799195325375698</v>
+        <v>0.799198243549928</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040053558688085</v>
+        <v>0.8040039964461607</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097623492305135</v>
+        <v>0.8097566203234896</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815982390554991</v>
+        <v>0.8159747578061303</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223359029398774</v>
+        <v>0.8223299286508018</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229677232490706</v>
+        <v>0.8229669360610217</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186140423617565</v>
+        <v>0.8186214806507455</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8150968541553697</v>
+        <v>0.8151068720415271</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8135451407472827</v>
+        <v>0.8135629344120254</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8116744214315539</v>
+        <v>0.8117026308136577</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8113565352679386</v>
+        <v>0.8113923047155467</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8163768311609743</v>
+        <v>0.8164205226095316</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8219575593797258</v>
+        <v>0.8220060368353452</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8287139052269177</v>
+        <v>0.8287675221853671</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8332804593765561</v>
+        <v>0.8333377863547018</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8182063844125582</v>
+        <v>0.8182735598379615</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8200355884122574</v>
+        <v>0.8201023753859482</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8073240541786828</v>
+        <v>0.8073974140163824</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7993127212207949</v>
+        <v>0.7993815965176535</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7918660151712655</v>
+        <v>0.7919448982993558</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7821606970259075</v>
+        <v>0.7822441489394283</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7679118077808189</v>
+        <v>0.7679432718450722</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659372870800873</v>
+        <v>0.7659574903043092</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583775795946353</v>
+        <v>0.7583742919582257</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7485162955529696</v>
+        <v>0.7484791557748918</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7400865231155065</v>
+        <v>0.74002897096039</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7310149005881883</v>
+        <v>0.730935842596775</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7362199895370847</v>
+        <v>0.7360963666751397</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7417954029754253</v>
+        <v>0.7416649238516151</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7510672710551716</v>
+        <v>0.7509504950230521</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7597233670219552</v>
+        <v>0.7596122572074806</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.774206081487932</v>
+        <v>0.7741576411710109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7781211526160967</v>
+        <v>0.7780904103451665</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7788368237635823</v>
+        <v>0.7787991647141614</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7838289419289814</v>
+        <v>0.7838075619176361</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7887079222804214</v>
+        <v>0.788701527804623</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923264946110531</v>
+        <v>0.7923259138022705</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897605200866828</v>
+        <v>0.7897433488273531</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7926419285492809</v>
+        <v>0.7926148348948076</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7984475258180792</v>
+        <v>0.7984033218414082</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8013472847710745</v>
+        <v>0.8022101384626514</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8021968037595031</v>
+        <v>0.8031482738804561</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.803906163000994</v>
+        <v>0.8048752438113119</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.806360264279643</v>
+        <v>0.8074551451105809</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8086829014718684</v>
+        <v>0.8097957300432783</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8117420864769636</v>
+        <v>0.8128900805365828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8129147025380571</v>
+        <v>0.8139702098678636</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8133094064724768</v>
+        <v>0.8145600566260747</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8187718953620322</v>
+        <v>0.819668842388074</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8285874676642468</v>
+        <v>0.8293857150439727</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8325178140845659</v>
+        <v>0.8334212391992668</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8320203630029976</v>
+        <v>0.8335784444954069</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8335406506700309</v>
+        <v>0.8357410651856398</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8466129148980073</v>
+        <v>0.8495871105424313</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8031482738804561</v>
+        <v>0.80314849658587</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8048752438113119</v>
+        <v>0.8048732318859558</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8074551451105809</v>
+        <v>0.8074375662668115</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8097957300432783</v>
+        <v>0.8097748424322954</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8128900805365828</v>
+        <v>0.8128739809055286</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8139702098678636</v>
+        <v>0.8139612241898495</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8145600566260747</v>
+        <v>0.8144068205965468</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.819668842388074</v>
+        <v>0.8197220139168555</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8293857150439727</v>
+        <v>0.8294547160626191</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8334212391992668</v>
+        <v>0.8335360523579605</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8335784444954069</v>
+        <v>0.8336234071329234</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8357410651856398</v>
+        <v>0.8357880951430054</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8495871105424313</v>
+        <v>0.8495407797690471</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886869839585411</v>
+        <v>0.7886846099840594</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920506916044792</v>
+        <v>0.7920461135265742</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914144471553776</v>
+        <v>0.7914098466059641</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928547027080032</v>
+        <v>0.7928473819683297</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791533640670893</v>
+        <v>0.7915261026703024</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900836093375987</v>
+        <v>0.790075952646603</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7885052498103138</v>
+        <v>0.7884976292112748</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874195491837304</v>
+        <v>0.7874120689889984</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894575490312642</v>
+        <v>0.7894487865391052</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7946021237980018</v>
+        <v>0.7945980365871765</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970247204929947</v>
+        <v>0.7970203777165077</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994549727102153</v>
+        <v>0.7994505245260376</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002228423594783</v>
+        <v>0.800220805986975</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986315793454929</v>
+        <v>0.7986330971240725</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799198243549928</v>
+        <v>0.7992010599580713</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040039964461607</v>
+        <v>0.8040026803289855</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097566203234896</v>
+        <v>0.8097510793385525</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159747578061303</v>
+        <v>0.8159673643764808</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223299286508018</v>
+        <v>0.8223241356181321</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229669360610217</v>
+        <v>0.8229661500842179</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186214806507455</v>
+        <v>0.8186286308928927</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151068720415271</v>
+        <v>0.8151165126988118</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8135629344120254</v>
+        <v>0.813580087038263</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117026308136577</v>
+        <v>0.8117298388569936</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8113923047155467</v>
+        <v>0.8114268180658638</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8164205226095316</v>
+        <v>0.8164626907407868</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8220060368353452</v>
+        <v>0.8220528370271094</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8287675221853671</v>
+        <v>0.8288192953955186</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8333377863547018</v>
+        <v>0.8333932108900434</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8182735598379615</v>
+        <v>0.8183384548150063</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8201023753859482</v>
+        <v>0.8201669037823158</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8073974140163824</v>
+        <v>0.8074682805397642</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7993815965176535</v>
+        <v>0.799448143091352</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7919448982993558</v>
+        <v>0.7920211372776406</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7822441489394283</v>
+        <v>0.7823248531416936</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7679432718450722</v>
+        <v>0.7679737573649947</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659574903043092</v>
+        <v>0.7659771378565046</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583742919582257</v>
+        <v>0.7583712769282257</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7484791557748918</v>
+        <v>0.7484434370947353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.74002897096039</v>
+        <v>0.7399735573305685</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.730935842596775</v>
+        <v>0.7308596231092437</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7360963666751397</v>
+        <v>0.73597692624752</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7416649238516151</v>
+        <v>0.7415388071135651</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7509504950230521</v>
+        <v>0.7508375421906122</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7596122572074806</v>
+        <v>0.7595046955326882</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7741576411710109</v>
+        <v>0.7741107374337667</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780904103451665</v>
+        <v>0.7780606065407001</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7787991647141614</v>
+        <v>0.7787626753939039</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7838075619176361</v>
+        <v>0.783786859623983</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788701527804623</v>
+        <v>0.7886953885700547</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923259138022705</v>
+        <v>0.7923254597814214</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897433488273531</v>
+        <v>0.7897268226402533</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7926148348948076</v>
+        <v>0.7925887205728845</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7984033218414082</v>
+        <v>0.7983605852678777</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022101384626514</v>
+        <v>0.8029949172112471</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.80314849658587</v>
+        <v>0.8039941372758463</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8048732318859558</v>
+        <v>0.8057180348697777</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8074375662668115</v>
+        <v>0.8083235807600667</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8097748424322954</v>
+        <v>0.8106199984390573</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8128739809055286</v>
+        <v>0.8135329303952337</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8139612241898495</v>
+        <v>0.814525082131567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8144068205965468</v>
+        <v>0.8149931823632045</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8197220139168555</v>
+        <v>0.8201400173086703</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8294547160626191</v>
+        <v>0.8295816482420159</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8335360523579605</v>
+        <v>0.8338113549944319</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8336234071329234</v>
+        <v>0.8344502631688868</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8357880951430054</v>
+        <v>0.8371733921933594</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8495407797690471</v>
+        <v>0.8507264779541697</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886846099840594</v>
+        <v>0.7886800993646919</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920461135265742</v>
+        <v>0.7920374136345063</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914098466059641</v>
+        <v>0.7914010993053081</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928473819683297</v>
+        <v>0.79283346621953</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915261026703024</v>
+        <v>0.7915117742406023</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.790075952646603</v>
+        <v>0.7900613990515527</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884976292112748</v>
+        <v>0.7884831444603371</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874120689889984</v>
+        <v>0.7873978511103178</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894487865391052</v>
+        <v>0.7894321282765695</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945980365871765</v>
+        <v>0.7945902703904054</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970203777165077</v>
+        <v>0.7970121265150782</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994505245260376</v>
+        <v>0.7994420736240421</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800220805986975</v>
+        <v>0.8002169282553153</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986330971240725</v>
+        <v>0.7986359704692452</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992010599580713</v>
+        <v>0.7992064080232694</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040026803289855</v>
+        <v>0.8040001700638646</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097510793385525</v>
+        <v>0.8097405254908877</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159673643764808</v>
+        <v>0.8159532523531148</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223241356181321</v>
+        <v>0.8223130619366353</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229661500842179</v>
+        <v>0.8229645865364806</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186286308928927</v>
+        <v>0.8186421307202014</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151165126988118</v>
+        <v>0.8151347435367954</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813580087038263</v>
+        <v>0.8136126020720307</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117298388569936</v>
+        <v>0.8117814557506883</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8114268180658638</v>
+        <v>0.8114923307392214</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8164626907407868</v>
+        <v>0.8165427632125153</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8220528370271094</v>
+        <v>0.8221417400585527</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8288192953955186</v>
+        <v>0.8289176758857351</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8333932108900434</v>
+        <v>0.8334987179258283</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8183384548150063</v>
+        <v>0.8184618514412911</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8201669037823158</v>
+        <v>0.8202896268459677</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8074682805397642</v>
+        <v>0.8076030235961942</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.799448143091352</v>
+        <v>0.7995747051534899</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7920211372776406</v>
+        <v>0.7921661946412063</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7823248531416936</v>
+        <v>0.7824785399896619</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7679737573649947</v>
+        <v>0.7680319668545839</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659771378565046</v>
+        <v>0.7660148491678436</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583712769282257</v>
+        <v>0.758365979742684</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7484434370947353</v>
+        <v>0.7483759532911581</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7399735573305685</v>
+        <v>0.7398686909736528</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7308596231092437</v>
+        <v>0.730715113198364</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.73597692624752</v>
+        <v>0.735749775339845</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7415388071135651</v>
+        <v>0.7412988189918915</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7508375421906122</v>
+        <v>0.7506223839919326</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7595046955326882</v>
+        <v>0.7592995635730345</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7741107374337667</v>
+        <v>0.7740212586995211</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780606065407001</v>
+        <v>0.7780036499401526</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7787626753939039</v>
+        <v>0.7786929966884681</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.783786859623983</v>
+        <v>0.7837473637249928</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886953885700547</v>
+        <v>0.7886838179498037</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923254597814214</v>
+        <v>0.7923248867649864</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897268226402533</v>
+        <v>0.7896955668274106</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7925887205728845</v>
+        <v>0.7925392267586696</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7983605852678777</v>
+        <v>0.7982792351106462</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8029949172112471</v>
+        <v>0.8036276032299818</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8039941372758463</v>
+        <v>0.8054716952785178</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8057180348697777</v>
+        <v>0.8072219647629149</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8083235807600667</v>
+        <v>0.8097911149564818</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8106199984390573</v>
+        <v>0.8120563719536367</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8135329303952337</v>
+        <v>0.8147091841297438</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.814525082131567</v>
+        <v>0.8155844227229977</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8149931823632045</v>
+        <v>0.8161364729441167</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8201400173086703</v>
+        <v>0.821090196921779</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8295816482420159</v>
+        <v>0.8299789936382058</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8338113549944319</v>
+        <v>0.8346311571061779</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8344502631688868</v>
+        <v>0.8362841129666063</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8371733921933594</v>
+        <v>0.8400481417390906</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,15 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8507264779541697</v>
+        <v>0.853712441569515</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B75">
+        <v>0.866274941569515</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886800993646919</v>
+        <v>0.7886846099840594</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920374136345063</v>
+        <v>0.7920461135265742</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914010993053081</v>
+        <v>0.7914098466059641</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.79283346621953</v>
+        <v>0.7928473819683297</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915117742406023</v>
+        <v>0.7915261026703024</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900613990515527</v>
+        <v>0.790075952646603</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884831444603371</v>
+        <v>0.7884976292112748</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873978511103178</v>
+        <v>0.7874120689889984</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894321282765695</v>
+        <v>0.7894487865391052</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945902703904054</v>
+        <v>0.7945980365871765</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970121265150782</v>
+        <v>0.7970203777165077</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994420736240421</v>
+        <v>0.7994505245260376</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002169282553153</v>
+        <v>0.800220805986975</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986359704692452</v>
+        <v>0.7986330971240725</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992064080232694</v>
+        <v>0.7992010599580713</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040001700638646</v>
+        <v>0.8040026803289855</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097405254908877</v>
+        <v>0.8097510793385525</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159532523531148</v>
+        <v>0.8159673643764808</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223130619366353</v>
+        <v>0.8223241356181321</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229645865364806</v>
+        <v>0.8229661500842179</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186421307202014</v>
+        <v>0.8186286308928927</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151347435367954</v>
+        <v>0.8151165126988118</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136126020720307</v>
+        <v>0.813580087038263</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117814557506883</v>
+        <v>0.8117298388569936</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8114923307392214</v>
+        <v>0.8114268180658638</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8165427632125153</v>
+        <v>0.8164626907407868</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8221417400585527</v>
+        <v>0.8220528370271094</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8289176758857351</v>
+        <v>0.8288192953955186</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8334987179258283</v>
+        <v>0.8333932108900434</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8184618514412911</v>
+        <v>0.8183384548150063</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8202896268459677</v>
+        <v>0.8201669037823158</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8076030235961942</v>
+        <v>0.8074682805397642</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7995747051534899</v>
+        <v>0.799448143091352</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7921661946412063</v>
+        <v>0.7920211372776406</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7824785399896619</v>
+        <v>0.7823248531416936</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7680319668545839</v>
+        <v>0.7679737573649947</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660148491678436</v>
+        <v>0.7659771378565046</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758365979742684</v>
+        <v>0.7583712769282257</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7483759532911581</v>
+        <v>0.7484434370947353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7398686909736528</v>
+        <v>0.7399735573305685</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.730715113198364</v>
+        <v>0.7308596231092437</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.735749775339845</v>
+        <v>0.73597692624752</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7412988189918915</v>
+        <v>0.7415388071135651</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7506223839919326</v>
+        <v>0.7508375421906122</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7592995635730345</v>
+        <v>0.7595046955326882</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7740212586995211</v>
+        <v>0.7741107374337667</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780036499401526</v>
+        <v>0.7780606065407001</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7786929966884681</v>
+        <v>0.7787626753939039</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7837473637249928</v>
+        <v>0.783786859623983</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886838179498037</v>
+        <v>0.7886953885700547</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923248867649864</v>
+        <v>0.7923254597814214</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896955668274106</v>
+        <v>0.7897268226402533</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7925392267586696</v>
+        <v>0.7925887205728845</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7982792351106462</v>
+        <v>0.7983605852678777</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8036276032299818</v>
+        <v>0.8021592745151018</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8054716952785178</v>
+        <v>0.8040396907342877</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8072219647629149</v>
+        <v>0.80585118334797</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097911149564818</v>
+        <v>0.8084162034774726</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8120563719536367</v>
+        <v>0.810925472430452</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8147091841297438</v>
+        <v>0.814041225295425</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8155844227229977</v>
+        <v>0.8152406668515255</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8161364729441167</v>
+        <v>0.8159354434520527</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.821090196921779</v>
+        <v>0.8210552762172214</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8299789936382058</v>
+        <v>0.8306471908472501</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8346311571061779</v>
+        <v>0.835320138754011</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8362841129666063</v>
+        <v>0.8362996999554021</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8400481417390906</v>
+        <v>0.839428453876649</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.853712441569515</v>
+        <v>0.8555334036487812</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.866274941569515</v>
+        <v>0.8680959036487812</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.80585118334797</v>
+        <v>0.8058547789375337</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8084162034774726</v>
+        <v>0.8084184160543082</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.810925472430452</v>
+        <v>0.8109221130756188</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.814041225295425</v>
+        <v>0.8139933695940301</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8152406668515255</v>
+        <v>0.8151251158333324</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8159354434520527</v>
+        <v>0.8158540516697678</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8210552762172214</v>
+        <v>0.8210023665276054</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8306471908472501</v>
+        <v>0.8306087775909985</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.835320138754011</v>
+        <v>0.8353021605872242</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8362996999554021</v>
+        <v>0.8362746098912627</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.839428453876649</v>
+        <v>0.8394122739120973</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8555334036487812</v>
+        <v>0.8555196738014359</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8680959036487812</v>
+        <v>0.8680821738014359</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886846099840594</v>
+        <v>0.7886823164597699</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920461135265742</v>
+        <v>0.7920416901049845</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914098466059641</v>
+        <v>0.7914053998496946</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928473819683297</v>
+        <v>0.7928403072009834</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915261026703024</v>
+        <v>0.7915188180463055</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.790075952646603</v>
+        <v>0.7900685534749667</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884976292112748</v>
+        <v>0.7884902650010108</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874120689889984</v>
+        <v>0.7874048404594891</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894487865391052</v>
+        <v>0.7894403177932282</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945980365871765</v>
+        <v>0.7945940877536845</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970203777165077</v>
+        <v>0.7970161821770586</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994505245260376</v>
+        <v>0.7994462273498991</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800220805986975</v>
+        <v>0.8002188356697892</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986330971240725</v>
+        <v>0.7986345598572389</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992010599580713</v>
+        <v>0.7992037798247046</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040026803289855</v>
+        <v>0.8040014054999877</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097510793385525</v>
+        <v>0.8097457172223486</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159673643764808</v>
+        <v>0.8159601993238319</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223241356181321</v>
+        <v>0.8223185158838111</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229661500842179</v>
+        <v>0.8229653665534894</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186286308928927</v>
+        <v>0.8186355092523403</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151165126988118</v>
+        <v>0.8151257967969453</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813580087038263</v>
+        <v>0.8135966324307925</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117298388569936</v>
+        <v>0.8117560976506519</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8114268180658638</v>
+        <v>0.8114601399697456</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8164626907407868</v>
+        <v>0.8165034133912927</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8220528370271094</v>
+        <v>0.822098044968657</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8288192953955186</v>
+        <v>0.8288693177088485</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8333932108900434</v>
+        <v>0.8334468257850459</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8183384548150063</v>
+        <v>0.8184011832068468</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8201669037823158</v>
+        <v>0.82022928592839</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8074682805397642</v>
+        <v>0.8075367782683924</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.799448143091352</v>
+        <v>0.7995124765880877</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7920211372776406</v>
+        <v>0.7920948621564173</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7823248531416936</v>
+        <v>0.7824029421050021</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7679737573649947</v>
+        <v>0.768003308501672</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659771378565046</v>
+        <v>0.7659962507727597</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583712769282257</v>
+        <v>0.7583685127798698</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7484434370947353</v>
+        <v>0.7484090606635567</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7399735573305685</v>
+        <v>0.7399201665279007</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7308596231092437</v>
+        <v>0.7307860929614201</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.73597692624752</v>
+        <v>0.7358614605495855</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7415388071135651</v>
+        <v>0.7414168388932101</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7508375421906122</v>
+        <v>0.7507282291604305</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7595046955326882</v>
+        <v>0.7594005162234326</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7741107374337667</v>
+        <v>0.7740652989505026</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780606065407001</v>
+        <v>0.7780316995072607</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7787626753939039</v>
+        <v>0.778727302707773</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.783786859623983</v>
+        <v>0.7837668034500861</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886953885700547</v>
+        <v>0.7886894898331935</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923254597814214</v>
+        <v>0.7923251209391464</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897268226402533</v>
+        <v>0.7897109062353851</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7925887205728845</v>
+        <v>0.7925635339055758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7983605852678777</v>
+        <v>0.7983192451841539</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021592745151018</v>
+        <v>0.8021100253575383</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8040396907342877</v>
+        <v>0.804883237061403</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8058547789375337</v>
+        <v>0.806781776263086</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8084184160543082</v>
+        <v>0.8093361985230614</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8109221130756188</v>
+        <v>0.811990543832096</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8139933695940301</v>
+        <v>0.8150390109688433</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8151251158333324</v>
+        <v>0.8162167806041409</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8158540516697678</v>
+        <v>0.8170725133290982</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8210023665276054</v>
+        <v>0.8222543219072583</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8306087775909985</v>
+        <v>0.8317537467917047</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8353021605872242</v>
+        <v>0.837003007667538</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8362746098912627</v>
+        <v>0.8386559825921027</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8394122739120973</v>
+        <v>0.8425509078515401</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8555196738014359</v>
+        <v>0.8596497325403156</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8680821738014359</v>
+        <v>0.8722122325403157</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886823164597699</v>
+        <v>0.7886779549413925</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920416901049845</v>
+        <v>0.7920332769133251</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914053998496946</v>
+        <v>0.7913969378815398</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928403072009834</v>
+        <v>0.7928268476291239</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915188180463055</v>
+        <v>0.7915049595109545</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900685534749667</v>
+        <v>0.7900544774355986</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884902650010108</v>
+        <v>0.7884762556973324</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7874048404594891</v>
+        <v>0.7873910892686276</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894403177932282</v>
+        <v>0.789424204412487</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945940877536845</v>
+        <v>0.79458657804218</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970161821770586</v>
+        <v>0.7970082038532253</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994462273498991</v>
+        <v>0.7994380562865472</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002188356697892</v>
+        <v>0.8002150807877506</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986345598572389</v>
+        <v>0.7986373316818196</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992037798247046</v>
+        <v>0.7992089491050455</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040014054999877</v>
+        <v>0.8039989722383433</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097457172223486</v>
+        <v>0.8097354961857264</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159601993238319</v>
+        <v>0.8159465137701338</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223185158838111</v>
+        <v>0.8223077666824559</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229653665534894</v>
+        <v>0.8229638109541749</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186355092523403</v>
+        <v>0.8186485092180622</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151257967969453</v>
+        <v>0.8151433707775504</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8135966324307925</v>
+        <v>0.8136280253170741</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117560976506519</v>
+        <v>0.811805958473282</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8114601399697456</v>
+        <v>0.8115234467036956</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8165034133912927</v>
+        <v>0.816580808093271</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.822098044968657</v>
+        <v>0.8221839965336328</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8288693177088485</v>
+        <v>0.8289644510836878</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8334468257850459</v>
+        <v>0.833548968744387</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8184011832068468</v>
+        <v>0.8185205591063121</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.82022928592839</v>
+        <v>0.8203480248342414</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8075367782683924</v>
+        <v>0.8076671254412329</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7995124765880877</v>
+        <v>0.7996349300284228</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7920948621564173</v>
+        <v>0.7922352487477582</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7824029421050021</v>
+        <v>0.7825517632801549</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.768003308501672</v>
+        <v>0.7680597716396678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7659962507727597</v>
+        <v>0.7660329522715621</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583685127798698</v>
+        <v>0.7583636598005126</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7484090606635567</v>
+        <v>0.7483440469523568</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7399201665279007</v>
+        <v>0.7398190305143668</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7307860929614201</v>
+        <v>0.7306465542203907</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7358614605495855</v>
+        <v>0.7356416887718206</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7414168388932101</v>
+        <v>0.7411845598123766</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7507282291604305</v>
+        <v>0.7505198453277844</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7594005162234326</v>
+        <v>0.759201691197833</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7740652989505026</v>
+        <v>0.7739785536468804</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780316995072607</v>
+        <v>0.7779764207601751</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778727302707773</v>
+        <v>0.7786597102725442</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7837668034500861</v>
+        <v>0.7837285125605626</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886894898331935</v>
+        <v>0.7886783602754849</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923251209391464</v>
+        <v>0.7923247477323482</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7897109062353851</v>
+        <v>0.7896807739190651</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7925635339055758</v>
+        <v>0.792515754245285</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7983192451841539</v>
+        <v>0.798240492665471</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021100253575383</v>
+        <v>0.803577389422474</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.804883237061403</v>
+        <v>0.806187473700184</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.806781776263086</v>
+        <v>0.8079713928273621</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8093361985230614</v>
+        <v>0.8105112569078801</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.811990543832096</v>
+        <v>0.8127886675713046</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8150390109688433</v>
+        <v>0.8153670045545428</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8162167806041409</v>
+        <v>0.8162289609907096</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8170725133290982</v>
+        <v>0.8168527055653499</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8222543219072583</v>
+        <v>0.82176522059295</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8317537467917047</v>
+        <v>0.8304695949073411</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.837003007667538</v>
+        <v>0.8354316086503719</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8386559825921027</v>
+        <v>0.8376087705994509</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8425509078515401</v>
+        <v>0.8419566126498803</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8596497325403156</v>
+        <v>0.8561643081103343</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8722122325403157</v>
+        <v>0.8687268081103343</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886779549413925</v>
+        <v>0.7886800993646919</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920332769133251</v>
+        <v>0.7920374136345063</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913969378815398</v>
+        <v>0.7914010993053081</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928268476291239</v>
+        <v>0.79283346621953</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915049595109545</v>
+        <v>0.7915117742406023</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900544774355986</v>
+        <v>0.7900613990515527</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884762556973324</v>
+        <v>0.7884831444603371</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873910892686276</v>
+        <v>0.7873978511103178</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789424204412487</v>
+        <v>0.7894321282765695</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.79458657804218</v>
+        <v>0.7945902703904054</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970082038532253</v>
+        <v>0.7970121265150782</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994380562865472</v>
+        <v>0.7994420736240421</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002150807877506</v>
+        <v>0.8002169282553153</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986373316818196</v>
+        <v>0.7986359704692452</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992089491050455</v>
+        <v>0.7992064080232694</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039989722383433</v>
+        <v>0.8040001700638646</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097354961857264</v>
+        <v>0.8097405254908877</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159465137701338</v>
+        <v>0.8159532523531148</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223077666824559</v>
+        <v>0.8223130619366353</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229638109541749</v>
+        <v>0.8229645865364806</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186485092180622</v>
+        <v>0.8186421307202014</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151433707775504</v>
+        <v>0.8151347435367954</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136280253170741</v>
+        <v>0.8136126020720307</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.811805958473282</v>
+        <v>0.8117814557506883</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8115234467036956</v>
+        <v>0.8114923307392214</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.816580808093271</v>
+        <v>0.8165427632125153</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8221839965336328</v>
+        <v>0.8221417400585527</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8289644510836878</v>
+        <v>0.8289176758857351</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.833548968744387</v>
+        <v>0.8334987179258283</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8185205591063121</v>
+        <v>0.8184618514412911</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8203480248342414</v>
+        <v>0.8202896268459677</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8076671254412329</v>
+        <v>0.8076030235961942</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7996349300284228</v>
+        <v>0.7995747051534899</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7922352487477582</v>
+        <v>0.7921661946412063</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7825517632801549</v>
+        <v>0.7824785399896619</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7680597716396678</v>
+        <v>0.7680319668545839</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660329522715621</v>
+        <v>0.7660148491678436</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583636598005126</v>
+        <v>0.758365979742684</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7483440469523568</v>
+        <v>0.7483759532911581</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7398190305143668</v>
+        <v>0.7398686909736528</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7306465542203907</v>
+        <v>0.730715113198364</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7356416887718206</v>
+        <v>0.735749775339845</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7411845598123766</v>
+        <v>0.7412988189918915</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7505198453277844</v>
+        <v>0.7506223839919326</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.759201691197833</v>
+        <v>0.7592995635730345</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7739785536468804</v>
+        <v>0.7740212586995211</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7779764207601751</v>
+        <v>0.7780036499401526</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7786597102725442</v>
+        <v>0.7786929966884681</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7837285125605626</v>
+        <v>0.7837473637249928</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886783602754849</v>
+        <v>0.7886838179498037</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923247477323482</v>
+        <v>0.7923248867649864</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896807739190651</v>
+        <v>0.7896955668274106</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792515754245285</v>
+        <v>0.7925392267586696</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.798240492665471</v>
+        <v>0.7982792351106462</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.803577389422474</v>
+        <v>0.8020623165049359</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.806187473700184</v>
+        <v>0.8053880852464239</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8079713928273621</v>
+        <v>0.8073058940470659</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8105112569078801</v>
+        <v>0.8098088706014086</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8127886675713046</v>
+        <v>0.8125388757609112</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8153670045545428</v>
+        <v>0.8155218082428792</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8162289609907096</v>
+        <v>0.8167039360913071</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8168527055653499</v>
+        <v>0.8176438048282949</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.82176522059295</v>
+        <v>0.8227961806357664</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8304695949073411</v>
+        <v>0.8320901809022507</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8354316086503719</v>
+        <v>0.8377601709026137</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8376087705994509</v>
+        <v>0.8399296733625339</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8419566126498803</v>
+        <v>0.8443027348547374</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8561643081103343</v>
+        <v>0.8610559843553094</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8687268081103343</v>
+        <v>0.8742551619628083</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886800993646919</v>
+        <v>0.7886758796747461</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920374136345063</v>
+        <v>0.7920292732025744</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7914010993053081</v>
+        <v>0.7913929089381841</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.79283346621953</v>
+        <v>0.7928204407632886</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7915117742406023</v>
+        <v>0.791498362865987</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900613990515527</v>
+        <v>0.7900477774503369</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884831444603371</v>
+        <v>0.7884695875811866</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873978511103178</v>
+        <v>0.7873845440086545</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894321282765695</v>
+        <v>0.789416533489873</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945902703904054</v>
+        <v>0.7945830046694534</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970121265150782</v>
+        <v>0.7970044077575411</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994420736240421</v>
+        <v>0.7994341687313441</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002169282553153</v>
+        <v>0.8002132904930297</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986359704692452</v>
+        <v>0.7986386460313254</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992064080232694</v>
+        <v>0.7992114073253063</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8040001700638646</v>
+        <v>0.8039978103459852</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097405254908877</v>
+        <v>0.8097306218341154</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159532523531148</v>
+        <v>0.8159399744391203</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223130619366353</v>
+        <v>0.8223026234166074</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229645865364806</v>
+        <v>0.8229630405987897</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186421307202014</v>
+        <v>0.8186546576908019</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151347435367954</v>
+        <v>0.8151516951509935</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136126020720307</v>
+        <v>0.8136429295695139</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8117814557506883</v>
+        <v>0.8118296481593116</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8114923307392214</v>
+        <v>0.8115535405317877</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8165427632125153</v>
+        <v>0.8166176115417324</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8221417400585527</v>
+        <v>0.8222248838793768</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8289176758857351</v>
+        <v>0.8290097192996565</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8334987179258283</v>
+        <v>0.8335976546383305</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8184618514412911</v>
+        <v>0.8185773994893829</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8202896268459677</v>
+        <v>0.8204045719977076</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8076030235961942</v>
+        <v>0.8077291858343358</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7995747051534899</v>
+        <v>0.7996932460891257</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7921661946412063</v>
+        <v>0.7923021313966742</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7824785399896619</v>
+        <v>0.7826227213643113</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7680319668545839</v>
+        <v>0.7680867598532686</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660148491678436</v>
+        <v>0.7660505784653332</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758365979742684</v>
+        <v>0.7583615365145659</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7483759532911581</v>
+        <v>0.7483132783436319</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7398686909736528</v>
+        <v>0.739771091797224</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.730715113198364</v>
+        <v>0.7305802950129661</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.735749775339845</v>
+        <v>0.7355370304255131</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7412988189918915</v>
+        <v>0.7410738853887958</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7506223839919326</v>
+        <v>0.7504204615983123</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7592995635730345</v>
+        <v>0.7591067613570116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7740212586995211</v>
+        <v>0.7739371244572751</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7780036499401526</v>
+        <v>0.777949976961519</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7786929966884681</v>
+        <v>0.7786273990951895</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7837473637249928</v>
+        <v>0.7837102237200055</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886838179498037</v>
+        <v>0.7886731050767238</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923248867649864</v>
+        <v>0.7923246951968492</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896955668274106</v>
+        <v>0.7896664991065063</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7925392267586696</v>
+        <v>0.7924930744585332</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7982792351106462</v>
+        <v>0.7982029592580209</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8020623165049359</v>
+        <v>0.8035286861836899</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8053880852464239</v>
+        <v>0.8061250645890616</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073058940470659</v>
+        <v>0.8078219195277307</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098088706014086</v>
+        <v>0.8102188155251078</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8125388757609112</v>
+        <v>0.8124139668126589</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8155218082428792</v>
+        <v>0.8148445779465414</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8167039360913071</v>
+        <v>0.8156463876884816</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8176438048282949</v>
+        <v>0.8163297845773458</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8227961806357664</v>
+        <v>0.8211615493314326</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8320901809022507</v>
+        <v>0.8295844261359127</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8377601709026137</v>
+        <v>0.8348234734210169</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8399296733625339</v>
+        <v>0.8373810462263931</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8443027348547374</v>
+        <v>0.8419911698189657</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8610559843553094</v>
+        <v>0.8531295396188867</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8742551619628083</v>
+        <v>0.8631124258426235</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886758796747461</v>
+        <v>0.7886738702727121</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920292732025744</v>
+        <v>0.7920253961897314</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913929089381841</v>
+        <v>0.7913890062508078</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928204407632886</v>
+        <v>0.7928142356266604</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791498362865987</v>
+        <v>0.7914919740061399</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900477774503369</v>
+        <v>0.7900412886228794</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884695875811866</v>
+        <v>0.7884631296822939</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873845440086545</v>
+        <v>0.7873782050929247</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789416533489873</v>
+        <v>0.78940910359531</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945830046694534</v>
+        <v>0.7945795446153724</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970044077575411</v>
+        <v>0.7970007322023025</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994341687313441</v>
+        <v>0.7994304047720311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002132904930297</v>
+        <v>0.8002115547651159</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986386460313254</v>
+        <v>0.7986399158842126</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992114073253063</v>
+        <v>0.7992137866669691</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039978103459852</v>
+        <v>0.803996682806681</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097306218341154</v>
+        <v>0.8097258954126931</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159399744391203</v>
+        <v>0.8159336257437522</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8223026234166074</v>
+        <v>0.8222976257983867</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229630405987897</v>
+        <v>0.8229622761493958</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186546576908019</v>
+        <v>0.8186605881899853</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151516951509935</v>
+        <v>0.8151597321643695</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136429295695139</v>
+        <v>0.8136573404401732</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8118296481593116</v>
+        <v>0.8118525644135217</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8115535405317877</v>
+        <v>0.8115826615225992</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8166176115417324</v>
+        <v>0.8166532330314255</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8222248838793768</v>
+        <v>0.8222644672019584</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8290097192996565</v>
+        <v>0.8290535517713433</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8335976546383305</v>
+        <v>0.8336448473525883</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8185773994893829</v>
+        <v>0.8186324600667041</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8204045719977076</v>
+        <v>0.8204593547252377</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8077291858343358</v>
+        <v>0.807789300453162</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7996932460891257</v>
+        <v>0.7997497423376447</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7923021313966742</v>
+        <v>0.7923669429540012</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7826227213643113</v>
+        <v>0.7826915170613026</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7680867598532686</v>
+        <v>0.7681129664231995</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660505784653332</v>
+        <v>0.7660677453185547</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583615365145659</v>
+        <v>0.7583595948665501</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7483132783436319</v>
+        <v>0.7482835884842951</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739771091797224</v>
+        <v>0.7397247877069741</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7305802950129661</v>
+        <v>0.7305162224510707</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7355370304255131</v>
+        <v>0.7354356404278507</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7410738853887958</v>
+        <v>0.7409666305042613</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7504204615983123</v>
+        <v>0.7503240902960194</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7591067613570116</v>
+        <v>0.7590146443304064</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7739371244572751</v>
+        <v>0.773896915229412</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.777949976961519</v>
+        <v>0.7779242854716478</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7786273990951895</v>
+        <v>0.7785960213019057</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7837102237200055</v>
+        <v>0.783692472497844</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886731050767238</v>
+        <v>0.7886680414511877</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923246951968492</v>
+        <v>0.7923247213063238</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896664991065063</v>
+        <v>0.7896527159040709</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7924930744585332</v>
+        <v>0.7924711482299849</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7982029592580209</v>
+        <v>0.7981665798091925</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8035286861836899</v>
+        <v>0.8034814274731337</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8061250645890616</v>
+        <v>0.8060909620176031</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078219195277307</v>
+        <v>0.8077090400420129</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8102188155251078</v>
+        <v>0.8099780138548478</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8124139668126589</v>
+        <v>0.8121030446479204</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8148445779465414</v>
+        <v>0.8144102783711095</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8156463876884816</v>
+        <v>0.8151625438267456</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8163297845773458</v>
+        <v>0.8158990589125634</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8211615493314326</v>
+        <v>0.8206629767269985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8295844261359127</v>
+        <v>0.8288486980165055</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8348234734210169</v>
+        <v>0.8343443080850558</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8373810462263931</v>
+        <v>0.8372447732113197</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8419911698189657</v>
+        <v>0.8420923514937204</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8531295396188867</v>
+        <v>0.8508405309158216</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8631124258426235</v>
+        <v>0.8561986556293963</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8034814274731337</v>
+        <v>0.8019277515413443</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8060909620176031</v>
+        <v>0.8053321740596477</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077090400420129</v>
+        <v>0.8073367276449748</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099780138548478</v>
+        <v>0.8095317898740497</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8121030446479204</v>
+        <v>0.8119586213892855</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8144102783711095</v>
+        <v>0.8143518995332192</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8151625438267456</v>
+        <v>0.8153136196372207</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8158990589125634</v>
+        <v>0.8162503080716366</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8206629767269985</v>
+        <v>0.8209353820415926</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8288486980165055</v>
+        <v>0.8290588306668848</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8343443080850558</v>
+        <v>0.8348364342866457</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8372447732113197</v>
+        <v>0.8376535388992472</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8420923514937204</v>
+        <v>0.8421000049838003</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8508405309158216</v>
+        <v>0.8540148258255853</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,15 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8561986556293963</v>
+        <v>0.8521027383207861</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B76">
+        <v>0.8378827383207861</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886738702727121</v>
+        <v>0.7886719236489165</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920253961897314</v>
+        <v>0.7920216399554325</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913890062508078</v>
+        <v>0.7913852239787245</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928142356266604</v>
+        <v>0.7928082228430432</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914919740061399</v>
+        <v>0.7914857832701028</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900412886228794</v>
+        <v>0.7900350011296883</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884631296822939</v>
+        <v>0.7884568722179126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873782050929247</v>
+        <v>0.7873720629189139</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.78940910359531</v>
+        <v>0.7894019035515002</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945795446153724</v>
+        <v>0.7945761925759577</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7970007322023025</v>
+        <v>0.7969971715381613</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994304047720311</v>
+        <v>0.7994267586090827</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002115547651159</v>
+        <v>0.8002098711535122</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986399158842126</v>
+        <v>0.7986411434509546</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992137866669691</v>
+        <v>0.7992160908620174</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803996682806681</v>
+        <v>0.803995588130773</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097258954126931</v>
+        <v>0.8097213103143728</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159336257437522</v>
+        <v>0.8159274595513315</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222976257983867</v>
+        <v>0.8222927678274238</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229622761493958</v>
+        <v>0.8229615181855809</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186605881899853</v>
+        <v>0.8186663119489198</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151597321643695</v>
+        <v>0.815167496293145</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136573404401732</v>
+        <v>0.8136712818906693</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8118525644135217</v>
+        <v>0.8118747443210861</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8115826615225992</v>
+        <v>0.811610855869726</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8166532330314255</v>
+        <v>0.8166877283150968</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8222644672019584</v>
+        <v>0.8223028075660641</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8290535517713433</v>
+        <v>0.8290960153418611</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8336448473525883</v>
+        <v>0.8336906143270435</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8186324600667041</v>
+        <v>0.8186858229476599</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8204593547252377</v>
+        <v>0.8205124541254933</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.807789300453162</v>
+        <v>0.8078475591075007</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7997497423376447</v>
+        <v>0.7998045023477861</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7923669429540012</v>
+        <v>0.7924297777234086</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7826915170613026</v>
+        <v>0.7827582471035974</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7681129664231995</v>
+        <v>0.7681384243480229</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660677453185547</v>
+        <v>0.7660844696244329</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583595948665501</v>
+        <v>0.7583578211193422</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7482835884842951</v>
+        <v>0.7482549223570932</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7397247877069741</v>
+        <v>0.7396800368575089</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7305162224510707</v>
+        <v>0.7304542306697994</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7354356404278507</v>
+        <v>0.7353373686527759</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7409666305042613</v>
+        <v>0.7408626398871153</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7503240902960194</v>
+        <v>0.750230597313162</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7590146443304064</v>
+        <v>0.7589252178486905</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.773896915229412</v>
+        <v>0.7738578732535231</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7779242854716478</v>
+        <v>0.7778993150221136</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7785960213019057</v>
+        <v>0.7785655373755177</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.783692472497844</v>
+        <v>0.7836752356101659</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886680414511877</v>
+        <v>0.7886631592561641</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923247213063238</v>
+        <v>0.792324818921014</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896527159040709</v>
+        <v>0.7896393995862254</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7924711482299849</v>
+        <v>0.7924499389111022</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7981665798091925</v>
+        <v>0.7981313024956602</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8019277515413443</v>
+        <v>0.8034355509760556</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8053321740596477</v>
+        <v>0.8060468622758187</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073367276449748</v>
+        <v>0.8077839976398458</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095317898740497</v>
+        <v>0.8099053987241377</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8119586213892855</v>
+        <v>0.811826754105365</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8143518995332192</v>
+        <v>0.8138512395476628</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8153136196372207</v>
+        <v>0.8145971142412515</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8162503080716366</v>
+        <v>0.8153527960712724</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8209353820415926</v>
+        <v>0.8199802749339081</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8290588306668848</v>
+        <v>0.8278330918802482</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8348364342866457</v>
+        <v>0.833218544206738</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8376535388992472</v>
+        <v>0.8363162031291207</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8421000049838003</v>
+        <v>0.8411009082565251</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8540148258255853</v>
+        <v>0.8489779690686059</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8521027383207861</v>
+        <v>0.8518494435662116</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8378827383207861</v>
+        <v>0.8376294435662116</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8034355509760556</v>
+        <v>0.8018855431015012</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8060468622758187</v>
+        <v>0.8052898381072455</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077839976398458</v>
+        <v>0.8074322297111751</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099053987241377</v>
+        <v>0.8094805044583772</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.811826754105365</v>
+        <v>0.8116940388486569</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8138512395476628</v>
+        <v>0.8138165897651127</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8145971142412515</v>
+        <v>0.8147423056754614</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8153527960712724</v>
+        <v>0.8156493417332423</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8199802749339081</v>
+        <v>0.8201604790765364</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8278330918802482</v>
+        <v>0.8278995077264258</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.833218544206738</v>
+        <v>0.8335024759176173</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8363162031291207</v>
+        <v>0.836443067820382</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8411009082565251</v>
+        <v>0.8408006752529812</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8489779690686059</v>
+        <v>0.8513426325574909</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8518494435662116</v>
+        <v>0.8488067351742827</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8376294435662116</v>
+        <v>0.8345867351742827</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886719236489165</v>
+        <v>0.7886700369068385</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920216399554325</v>
+        <v>0.7920179989433374</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913852239787245</v>
+        <v>0.7913815566358841</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928082228430432</v>
+        <v>0.7928023936082174</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914857832701028</v>
+        <v>0.7914797815861507</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900350011296883</v>
+        <v>0.7900289057470377</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884568722179126</v>
+        <v>0.7884508060028029</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873720629189139</v>
+        <v>0.7873661084705943</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7894019035515002</v>
+        <v>0.7893949228613124</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945761925759577</v>
+        <v>0.7945729435730224</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969971715381613</v>
+        <v>0.7969937204632215</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994267586090827</v>
+        <v>0.7994232248000849</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002098711535122</v>
+        <v>0.8002082373518641</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986411434509546</v>
+        <v>0.7986423307986408</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992160908620174</v>
+        <v>0.7992183234109331</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803995588130773</v>
+        <v>0.8039945249127443</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097213103143728</v>
+        <v>0.8097168603180986</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159274595513315</v>
+        <v>0.8159214681798234</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222927678274238</v>
+        <v>0.8222880438217914</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229615181855809</v>
+        <v>0.8229607671994119</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186663119489198</v>
+        <v>0.818671839450326</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815167496293145</v>
+        <v>0.8151750010647929</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136712818906693</v>
+        <v>0.8136847763634516</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8118747443210861</v>
+        <v>0.8118962226439973</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.811610855869726</v>
+        <v>0.8116381669009385</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8166877283150968</v>
+        <v>0.8167211497098642</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8223028075660641</v>
+        <v>0.8223399623020774</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8290960153418611</v>
+        <v>0.8291371727915615</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8336906143270435</v>
+        <v>0.8337350190135659</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8186858229476599</v>
+        <v>0.8187375652791962</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8205124541254933</v>
+        <v>0.8205639464232362</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8078475591075007</v>
+        <v>0.8079040461808982</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7998045023477861</v>
+        <v>0.7998576046712065</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7924297777234086</v>
+        <v>0.7924907243948998</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7827582471035974</v>
+        <v>0.7828230025774525</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7681384243480229</v>
+        <v>0.7681631648255611</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7660844696244329</v>
+        <v>0.7661007674350256</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583578211193422</v>
+        <v>0.7583562026930336</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7482549223570932</v>
+        <v>0.7482272285837968</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7396800368575089</v>
+        <v>0.7396367631320322</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7304542306697994</v>
+        <v>0.7303942204939879</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7353373686527759</v>
+        <v>0.735242073992723</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7408626398871153</v>
+        <v>0.7407617674778111</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.750230597313162</v>
+        <v>0.7501398563361417</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7589252178486905</v>
+        <v>0.7588383665709307</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7738578732535231</v>
+        <v>0.7738199487889137</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7778993150221136</v>
+        <v>0.7778750360293561</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7785655373755177</v>
+        <v>0.7785359099770996</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7836752356101659</v>
+        <v>0.7836584910941518</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886631592561641</v>
+        <v>0.7886584490442075</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792324818921014</v>
+        <v>0.7923249815426779</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896393995862254</v>
+        <v>0.7896265270447924</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7924499389111022</v>
+        <v>0.7924294121751453</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7981313024956602</v>
+        <v>0.7980970785158533</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8018855431015012</v>
+        <v>0.8033909978496362</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052898381072455</v>
+        <v>0.8060039742024916</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074322297111751</v>
+        <v>0.8078547114355799</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8094805044583772</v>
+        <v>0.8098402943438441</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8116940388486569</v>
+        <v>0.8115758792640608</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8138165897651127</v>
+        <v>0.8133462008958858</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8147423056754614</v>
+        <v>0.8140957237818837</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8156493417332423</v>
+        <v>0.8148650639163106</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8201604790765364</v>
+        <v>0.8193662642515864</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8278995077264258</v>
+        <v>0.8269202003542531</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8335024759176173</v>
+        <v>0.8322038405551313</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.836443067820382</v>
+        <v>0.835473269883753</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8408006752529812</v>
+        <v>0.8402023727258314</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8513426325574909</v>
+        <v>0.847389569013979</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8488067351742827</v>
+        <v>0.8488637456553908</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8345867351742827</v>
+        <v>0.8369983244831689</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8033909978496362</v>
+        <v>0.8018445630506938</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8060039742024916</v>
+        <v>0.8052486710530427</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078547114355799</v>
+        <v>0.8073586084631208</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098402943438441</v>
+        <v>0.8092377601760861</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8115758792640608</v>
+        <v>0.8112598465540766</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8133462008958858</v>
+        <v>0.8130816032014347</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8140957237818837</v>
+        <v>0.813958130497634</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8148650639163106</v>
+        <v>0.8148268223917758</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8193662642515864</v>
+        <v>0.8191552253960082</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8269202003542531</v>
+        <v>0.8265035363023985</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8322038405551313</v>
+        <v>0.8319181212538826</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.835473269883753</v>
+        <v>0.8349275762530299</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8402023727258314</v>
+        <v>0.8391635397943741</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.847389569013979</v>
+        <v>0.8484253747892415</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8488637456553908</v>
+        <v>0.8453160235863658</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8369983244831689</v>
+        <v>0.8296682471705065</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886700369068385</v>
+        <v>0.7886682073254341</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920179989433374</v>
+        <v>0.792014467932725</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913815566358841</v>
+        <v>0.7913779990643695</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7928023936082174</v>
+        <v>0.7927967396469944</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914797815861507</v>
+        <v>0.7914739604278611</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900289057470377</v>
+        <v>0.7900229938059381</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884508060028029</v>
+        <v>0.7884449224043111</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873661084705943</v>
+        <v>0.7873603332743457</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893949228613124</v>
+        <v>0.7893881516568506</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945729435730224</v>
+        <v>0.7945697929295453</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969937204632215</v>
+        <v>0.7969903739967434</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994232248000849</v>
+        <v>0.7994197982326765</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002082373518641</v>
+        <v>0.8002066511875473</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986423307986408</v>
+        <v>0.7986434798623718</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992183234109331</v>
+        <v>0.7992204876003538</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039945249127443</v>
+        <v>0.8039934918254215</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097168603180986</v>
+        <v>0.8097125395611857</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159214681798234</v>
+        <v>0.8159156443675084</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222880438217914</v>
+        <v>0.8222834483977186</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229607671994119</v>
+        <v>0.8229600236059271</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818671839450326</v>
+        <v>0.8186771804874522</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151750010647929</v>
+        <v>0.8151822591345943</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136847763634516</v>
+        <v>0.8136978448997818</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8118962226439973</v>
+        <v>0.8119170319994445</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8116381669009385</v>
+        <v>0.8116646352960901</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8167211497098642</v>
+        <v>0.8167535463566542</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8223399623020774</v>
+        <v>0.822375985285806</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8291371727915615</v>
+        <v>0.8291770831404084</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8337350190135659</v>
+        <v>0.8337781211655366</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8187375652791962</v>
+        <v>0.8187877596142669</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8205639464232362</v>
+        <v>0.8206139033205656</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8079040461808982</v>
+        <v>0.8079588410331171</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7998576046712065</v>
+        <v>0.7999091232077244</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7924907243948998</v>
+        <v>0.7925498664544519</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7828230025774525</v>
+        <v>0.7828858693260028</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7681631648255611</v>
+        <v>0.7681872173715553</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661007674350256</v>
+        <v>0.7661166540953235</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583562026930336</v>
+        <v>0.7583547280544565</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7482272285837968</v>
+        <v>0.7482004591318943</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7396367631320322</v>
+        <v>0.7395948952665238</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7303942204939879</v>
+        <v>0.7303360989205354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.735242073992723</v>
+        <v>0.7351496236941956</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7407617674778111</v>
+        <v>0.7406638757593307</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7501398563361417</v>
+        <v>0.7500517482911575</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7588383665709307</v>
+        <v>0.7587539816050396</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7738199487889137</v>
+        <v>0.7737830948596696</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7778750360293561</v>
+        <v>0.7778514204846237</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7785359099770996</v>
+        <v>0.7785071037995512</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7836584910941518</v>
+        <v>0.7836422182159796</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886584490442075</v>
+        <v>0.7886539020051575</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923249815426779</v>
+        <v>0.792325203251512</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896265270447924</v>
+        <v>0.7896140766597621</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7924294121751453</v>
+        <v>0.7924095358373597</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7980970785158533</v>
+        <v>0.798063861875556</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8018445630506938</v>
+        <v>0.8033477124891564</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052486710530427</v>
+        <v>0.8059622498444421</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073586084631208</v>
+        <v>0.8077623678315764</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8092377601760861</v>
+        <v>0.8095878023100542</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8112598465540766</v>
+        <v>0.8111502673964589</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8130816032014347</v>
+        <v>0.8126154732654317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.813958130497634</v>
+        <v>0.8133441562637259</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8148268223917758</v>
+        <v>0.8141095951608477</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8191552253960082</v>
+        <v>0.8184710467984482</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8265035363023985</v>
+        <v>0.8257094699147862</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8319181212538826</v>
+        <v>0.8308690734145394</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8349275762530299</v>
+        <v>0.8342363180835811</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8391635397943741</v>
+        <v>0.8388581390197154</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8484253747892415</v>
+        <v>0.8452752224882113</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8453160235863658</v>
+        <v>0.84534171586308</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8296682471705065</v>
+        <v>0.8336692243119661</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8033477124891564</v>
+        <v>0.8018047592178736</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8059622498444421</v>
+        <v>0.8052086263333726</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077623678315764</v>
+        <v>0.807580055079576</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095878023100542</v>
+        <v>0.809359058432354</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8111502673964589</v>
+        <v>0.8112057982878236</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8126154732654317</v>
+        <v>0.812858775375521</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8133441562637259</v>
+        <v>0.8137314091857137</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8141095951608477</v>
+        <v>0.8145910759887059</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8184710467984482</v>
+        <v>0.8188019366799768</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8257094699147862</v>
+        <v>0.8258981788105877</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8308690734145394</v>
+        <v>0.8312170972681603</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8342363180835811</v>
+        <v>0.8343987327524063</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8388581390197154</v>
+        <v>0.8386588347552423</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8452752224882113</v>
+        <v>0.8473185866512158</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.84534171586308</v>
+        <v>0.8445511494833744</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8336692243119661</v>
+        <v>0.8326161480042534</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886682073254341</v>
+        <v>0.7886647095604797</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.792014467932725</v>
+        <v>0.7920077165635998</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913779990643695</v>
+        <v>0.7913711941014484</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927967396469944</v>
+        <v>0.7927859268583823</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914739604278611</v>
+        <v>0.7914628280705154</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900229938059381</v>
+        <v>0.7900116881032893</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884449224043111</v>
+        <v>0.7884336710475355</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873603332743457</v>
+        <v>0.7873492892181179</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893881516568506</v>
+        <v>0.7893752011051935</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945697929295453</v>
+        <v>0.7945637693861245</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969903739967434</v>
+        <v>0.7969839764304272</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994197982326765</v>
+        <v>0.7994132478777942</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002066511875473</v>
+        <v>0.8002036136927101</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986434798623718</v>
+        <v>0.7986456702794527</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992204876003538</v>
+        <v>0.799224623073009</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039934918254215</v>
+        <v>0.8039915110943675</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097125395611857</v>
+        <v>0.8097042639567134</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159156443675084</v>
+        <v>0.8159044723094924</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222834483977186</v>
+        <v>0.8222746231384217</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229600236059271</v>
+        <v>0.8229585599261751</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186771804874522</v>
+        <v>0.8186873392209884</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151822591345943</v>
+        <v>0.8151960818345989</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8136978448997818</v>
+        <v>0.8137227819557077</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119170319994445</v>
+        <v>0.8119567645117334</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8116646352960901</v>
+        <v>0.8117151948309577</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8167535463566542</v>
+        <v>0.8168154474866249</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.822375985285806</v>
+        <v>0.8224448357350568</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8291770831404084</v>
+        <v>0.8292533814450984</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8337781211655366</v>
+        <v>0.8338606399530302</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8187877596142669</v>
+        <v>0.818883773524884</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8206139033205656</v>
+        <v>0.8207094770590392</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8079588410331171</v>
+        <v>0.8080636485661263</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7999091232077244</v>
+        <v>0.8000076832599943</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7925498664544519</v>
+        <v>0.792663046876533</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7828858693260028</v>
+        <v>0.7830062559894255</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7681872173715553</v>
+        <v>0.7682333689710956</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661166540953235</v>
+        <v>0.766147252006394</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583547280544565</v>
+        <v>0.7583521686602629</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7482004591318943</v>
+        <v>0.7481495162219155</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7395948952665238</v>
+        <v>0.7395151140903835</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7303360989205354</v>
+        <v>0.7302251776475355</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7351496236941956</v>
+        <v>0.7349727633493169</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7406638757593307</v>
+        <v>0.7404765234170376</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7500517482911575</v>
+        <v>0.7498829878947368</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7587539816050396</v>
+        <v>0.7585922046761161</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7737830948596696</v>
+        <v>0.7737124234155284</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7778514204846237</v>
+        <v>0.7778060749754783</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7785071037995512</v>
+        <v>0.7784518232387803</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7836422182159796</v>
+        <v>0.7836110100825985</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886539020051575</v>
+        <v>0.788645265082657</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792325203251512</v>
+        <v>0.7923258028124468</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896140766597621</v>
+        <v>0.7895903626280729</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7924095358373597</v>
+        <v>0.7923716153611284</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.798063861875556</v>
+        <v>0.7980002795096444</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8018047592178736</v>
+        <v>0.8032647375606421</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052086263333726</v>
+        <v>0.8058821124015493</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.807580055079576</v>
+        <v>0.8081432086618836</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809359058432354</v>
+        <v>0.8097971127694036</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8112057982878236</v>
+        <v>0.8110850843913182</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.812858775375521</v>
+        <v>0.8123847040309504</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8137314091857137</v>
+        <v>0.8131801842004873</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8145910759887059</v>
+        <v>0.8140006527007433</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8188019366799768</v>
+        <v>0.8181890252280226</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8258981788105877</v>
+        <v>0.8250471670169796</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8312170972681603</v>
+        <v>0.8301292311901105</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8343987327524063</v>
+        <v>0.8339580246343141</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8386588347552423</v>
+        <v>0.8386849075372566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8473185866512158</v>
+        <v>0.8447516173317164</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8445511494833744</v>
+        <v>0.8451011980337733</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8326161480042534</v>
+        <v>0.8386943813599234</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886647095604797</v>
+        <v>0.7886664323460487</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920077165635998</v>
+        <v>0.7920110420135349</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913711941014484</v>
+        <v>0.791374546410235</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927859268583823</v>
+        <v>0.7927912531740836</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914628280705154</v>
+        <v>0.7914683117737628</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900116881032893</v>
+        <v>0.7900172571510664</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884336710475355</v>
+        <v>0.7884392133014452</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873492892181179</v>
+        <v>0.7873547293587861</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893752011051935</v>
+        <v>0.7893815806530283</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945637693861245</v>
+        <v>0.7945667362472444</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969839764304272</v>
+        <v>0.7969871274551967</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994132478777942</v>
+        <v>0.7994164740999108</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002036136927101</v>
+        <v>0.8002051106121425</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986456702794527</v>
+        <v>0.7986445924555891</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799224623073009</v>
+        <v>0.7992225865191384</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039915110943675</v>
+        <v>0.8039924876146459</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097042639567134</v>
+        <v>0.8097083425139947</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159044723094924</v>
+        <v>0.8159099812450104</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222746231384217</v>
+        <v>0.8222789764507755</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229585599261751</v>
+        <v>0.8229592877523468</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186873392209884</v>
+        <v>0.8186823442193556</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151960818345989</v>
+        <v>0.8151892823543265</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137227819557077</v>
+        <v>0.8137105072469279</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119567645117334</v>
+        <v>0.8119372030220637</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117151948309577</v>
+        <v>0.8116902992855214</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8168154474866249</v>
+        <v>0.8167849644565834</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8224448357350568</v>
+        <v>0.8224109271935586</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8292533814450984</v>
+        <v>0.8292158019238869</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8338606399530302</v>
+        <v>0.8338199771025931</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.818883773524884</v>
+        <v>0.8188364742480079</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8207094770590392</v>
+        <v>0.8206623923266406</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8080636485661263</v>
+        <v>0.808012018367409</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8000076832599943</v>
+        <v>0.7999591275434577</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.792663046876533</v>
+        <v>0.7926072825584725</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7830062559894255</v>
+        <v>0.7829469283185705</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682333689710956</v>
+        <v>0.768210609929312</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.766147252006394</v>
+        <v>0.7661321442762348</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583521686602629</v>
+        <v>0.7583533866185662</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7481495162219155</v>
+        <v>0.748174569048989</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7395151140903835</v>
+        <v>0.7395543664718436</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7302251776475355</v>
+        <v>0.7302797786478542</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7349727633493169</v>
+        <v>0.7350598927509865</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7404765234170376</v>
+        <v>0.7405688351448476</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7498829878947368</v>
+        <v>0.7499661608361663</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7585922046761161</v>
+        <v>0.7586719600671212</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7737124234155284</v>
+        <v>0.7737472670668308</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7778060749754783</v>
+        <v>0.7778284418522361</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7784518232387803</v>
+        <v>0.7784790854326826</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7836110100825985</v>
+        <v>0.7836263973863042</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788645265082657</v>
+        <v>0.7886495099138169</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923258028124468</v>
+        <v>0.7923254786499401</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895903626280729</v>
+        <v>0.7896020281822179</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923716153611284</v>
+        <v>0.7923902796915197</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7980002795096444</v>
+        <v>0.798031609191266</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8032647375606421</v>
+        <v>0.801766082304824</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8058821124015493</v>
+        <v>0.8051696597522517</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8081432086618836</v>
+        <v>0.8077859879577212</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097971127694036</v>
+        <v>0.8094703021850411</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8110850843913182</v>
+        <v>0.8111532375349451</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8123847040309504</v>
+        <v>0.8126844878694213</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8131801842004873</v>
+        <v>0.8135453749824307</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8140006527007433</v>
+        <v>0.8143909896793911</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8181890252280226</v>
+        <v>0.8184904550312333</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8250471670169796</v>
+        <v>0.8253575183670281</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8301292311901105</v>
+        <v>0.8305891129210559</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8339580246343141</v>
+        <v>0.8339266231323554</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8386849075372566</v>
+        <v>0.8382103193458746</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8447516173317164</v>
+        <v>0.8463748235758422</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8451011980337733</v>
+        <v>0.8439375218037817</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8386943813599234</v>
+        <v>0.8343708262996332</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886664323460487</v>
+        <v>0.7886630367000811</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920110420135349</v>
+        <v>0.7920044872278562</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791374546410235</v>
+        <v>0.7913679378277246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927912531740836</v>
+        <v>0.7927807537903402</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914683117737628</v>
+        <v>0.7914575021992614</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900172571510664</v>
+        <v>0.7900062794254188</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884392133014452</v>
+        <v>0.788428288436114</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873547293587861</v>
+        <v>0.7873440057786369</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893815806530283</v>
+        <v>0.7893690047703934</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945667362472444</v>
+        <v>0.7945608884457983</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969871274551967</v>
+        <v>0.7969809167697175</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994164740999108</v>
+        <v>0.7994101153047749</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002051106121425</v>
+        <v>0.8002021586037882</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986445924555891</v>
+        <v>0.7986467149313681</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992225865191384</v>
+        <v>0.7992265999979119</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039924876146459</v>
+        <v>0.803990561142124</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097083425139947</v>
+        <v>0.8097002989580452</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8159099812450104</v>
+        <v>0.8158991114008314</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222789764507755</v>
+        <v>0.8222703838637995</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229592877523468</v>
+        <v>0.822957840362326</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186823442193556</v>
+        <v>0.8186921735286417</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8151892823543265</v>
+        <v>0.8152026680015085</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137105072469279</v>
+        <v>0.8137346864693721</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119372030220637</v>
+        <v>0.8119757435683916</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8116902992855214</v>
+        <v>0.8117393557906692</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8167849644565834</v>
+        <v>0.8168450363966425</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8224109271935586</v>
+        <v>0.8224777558663874</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8292158019238869</v>
+        <v>0.8292898710053894</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8338199771025931</v>
+        <v>0.8339001598760178</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8188364742480079</v>
+        <v>0.8189297181196811</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8206623923266406</v>
+        <v>0.8207552175195554</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808012018367409</v>
+        <v>0.8081137979978026</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.7999591275434577</v>
+        <v>0.8000548522174379</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7926072825584725</v>
+        <v>0.7927172294054542</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7829469283185705</v>
+        <v>0.7830639245488763</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.768210609929312</v>
+        <v>0.7682555195919569</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661321442762348</v>
+        <v>0.7661619907027355</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583533866185662</v>
+        <v>0.7583510652354282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.748174569048989</v>
+        <v>0.7481252611579461</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7395543664718436</v>
+        <v>0.7394770792836579</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7302797786478542</v>
+        <v>0.7301722187738972</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7350598927509865</v>
+        <v>0.7348881243598031</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7405688351448476</v>
+        <v>0.7403868252140537</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7499661608361663</v>
+        <v>0.7498021292278523</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7586719600671212</v>
+        <v>0.758514623380531</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7737472670668308</v>
+        <v>0.7736785241557227</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7778284418522361</v>
+        <v>0.7777842959894832</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7784790854326826</v>
+        <v>0.7784252872377322</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7836263973863042</v>
+        <v>0.7835960387777141</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886495099138169</v>
+        <v>0.7886411603190004</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923254786499401</v>
+        <v>0.7923261712407361</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7896020281822179</v>
+        <v>0.7895790621814829</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923902796915197</v>
+        <v>0.7923535161637711</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.798031609191266</v>
+        <v>0.7979698341415594</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.801766082304824</v>
+        <v>0.8032249511149532</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051696597522517</v>
+        <v>0.8058436149277513</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077859879577212</v>
+        <v>0.808314820065598</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8094703021850411</v>
+        <v>0.8098923512194033</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8111532375349451</v>
+        <v>0.8110686277025563</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8126844878694213</v>
+        <v>0.8123159636966817</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8135453749824307</v>
+        <v>0.8131577858057646</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8143909896793911</v>
+        <v>0.8140053447216906</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8184904550312333</v>
+        <v>0.8181060879538471</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8253575183670281</v>
+        <v>0.8247876441551345</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8305891129210559</v>
+        <v>0.8298372330024955</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8339266231323554</v>
+        <v>0.8338933530590802</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8382103193458746</v>
+        <v>0.8386851228484093</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8463748235758422</v>
+        <v>0.8446270011422845</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8439375218037817</v>
+        <v>0.8451019720573073</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8343708262996332</v>
+        <v>0.840004263572135</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886630367000811</v>
+        <v>0.7886614116257972</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920044872278562</v>
+        <v>0.7920013498993248</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913679378277246</v>
+        <v>0.7913647735220661</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927807537903402</v>
+        <v>0.7927757274520998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914575021992614</v>
+        <v>0.7914523274448392</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900062794254188</v>
+        <v>0.7900010242908807</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788428288436114</v>
+        <v>0.7884230586696978</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873440057786369</v>
+        <v>0.7873388723680905</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893690047703934</v>
+        <v>0.7893629838719227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945608884457983</v>
+        <v>0.7945580897484049</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969809167697175</v>
+        <v>0.7969779445575553</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994101153047749</v>
+        <v>0.7994070723629906</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002021586037882</v>
+        <v>0.8002007436200436</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986467149313681</v>
+        <v>0.7986477279127484</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992265999979119</v>
+        <v>0.7992285198722252</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803990561142124</v>
+        <v>0.8039896366948753</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097002989580452</v>
+        <v>0.8096964428556233</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158991114008314</v>
+        <v>0.815893892679599</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222703838637995</v>
+        <v>0.8222662542606838</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822957840362326</v>
+        <v>0.8229571292494072</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186921735286417</v>
+        <v>0.818696854681244</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152026680015085</v>
+        <v>0.815209050648207</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137346864693721</v>
+        <v>0.8137462372047114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119757435683916</v>
+        <v>0.8119941657151774</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117393557906692</v>
+        <v>0.8117628140704635</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8168450363966425</v>
+        <v>0.8168737697896336</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8224777558663874</v>
+        <v>0.8225097299849498</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8292898710053894</v>
+        <v>0.8293253171156113</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8339001598760178</v>
+        <v>0.8339385842655604</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8189297181196811</v>
+        <v>0.8189743652949049</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8207552175195554</v>
+        <v>0.8207996703469226</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8081137979978026</v>
+        <v>0.8081625292984853</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8000548522174379</v>
+        <v>0.8001006928138585</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7927172294054542</v>
+        <v>0.7927698962574861</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7830639245488763</v>
+        <v>0.7831200022692786</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682555195919569</v>
+        <v>0.7682770855966334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661619907027355</v>
+        <v>0.7661763731998086</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583510652354282</v>
+        <v>0.7583500681101041</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7481252611579461</v>
+        <v>0.7481017667857792</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7394770792836579</v>
+        <v>0.7394402067476451</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7301722187738972</v>
+        <v>0.7301208294075741</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7348881243598031</v>
+        <v>0.7348058708717217</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7403868252140537</v>
+        <v>0.7402996315577188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7498021292278523</v>
+        <v>0.7497234900401297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.758514623380531</v>
+        <v>0.7584391290143556</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7736785241557227</v>
+        <v>0.7736455316353257</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777842959894832</v>
+        <v>0.7777630822405215</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7784252872377322</v>
+        <v>0.7783994490008749</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835960387777141</v>
+        <v>0.7835814668740927</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886411603190004</v>
+        <v>0.7886371888861993</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923261712407361</v>
+        <v>0.7923265798235943</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895790621814829</v>
+        <v>0.7895681101069225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923535161637711</v>
+        <v>0.7923359569872914</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7979698341415594</v>
+        <v>0.7979402365093922</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8032249511149532</v>
+        <v>0.8031862383262289</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8058436149277513</v>
+        <v>0.8058061121312414</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.808314820065598</v>
+        <v>0.8082833014623938</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098923512194033</v>
+        <v>0.8098943736146305</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8110686277025563</v>
+        <v>0.8110507546012521</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8123159636966817</v>
+        <v>0.8122066471813405</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8131577858057646</v>
+        <v>0.8129723749686733</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8140053447216906</v>
+        <v>0.8138556387292533</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8181060879538471</v>
+        <v>0.8178768717084282</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8247876441551345</v>
+        <v>0.8243479160507658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8298372330024955</v>
+        <v>0.8293001578853553</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8338933530590802</v>
+        <v>0.833315628106573</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8386851228484093</v>
+        <v>0.8381915873858024</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8446270011422845</v>
+        <v>0.8438263845016793</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8451019720573073</v>
+        <v>0.8440514826063257</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,15 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.840004263572135</v>
+        <v>0.8393419747328059</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B77">
+        <v>0.8369574651402758</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886614116257972</v>
+        <v>0.7886630367000811</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920013498993248</v>
+        <v>0.7920044872278562</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913647735220661</v>
+        <v>0.7913679378277246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927757274520998</v>
+        <v>0.7927807537903402</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914523274448392</v>
+        <v>0.7914575021992614</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900010242908807</v>
+        <v>0.7900062794254188</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884230586696978</v>
+        <v>0.788428288436114</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873388723680905</v>
+        <v>0.7873440057786369</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893629838719227</v>
+        <v>0.7893690047703934</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945580897484049</v>
+        <v>0.7945608884457983</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969779445575553</v>
+        <v>0.7969809167697175</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994070723629906</v>
+        <v>0.7994101153047749</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002007436200436</v>
+        <v>0.8002021586037882</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986477279127484</v>
+        <v>0.7986467149313681</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992285198722252</v>
+        <v>0.7992265999979119</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039896366948753</v>
+        <v>0.803990561142124</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096964428556233</v>
+        <v>0.8097002989580452</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815893892679599</v>
+        <v>0.8158991114008314</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222662542606838</v>
+        <v>0.8222703838637995</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229571292494072</v>
+        <v>0.822957840362326</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818696854681244</v>
+        <v>0.8186921735286417</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815209050648207</v>
+        <v>0.8152026680015085</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137462372047114</v>
+        <v>0.8137346864693721</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119941657151774</v>
+        <v>0.8119757435683916</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117628140704635</v>
+        <v>0.8117393557906692</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8168737697896336</v>
+        <v>0.8168450363966425</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8225097299849498</v>
+        <v>0.8224777558663874</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8293253171156113</v>
+        <v>0.8292898710053894</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8339385842655604</v>
+        <v>0.8339001598760178</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8189743652949049</v>
+        <v>0.8189297181196811</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8207996703469226</v>
+        <v>0.8207552175195554</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8081625292984853</v>
+        <v>0.8081137979978026</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8001006928138585</v>
+        <v>0.8000548522174379</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7927698962574861</v>
+        <v>0.7927172294054542</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7831200022692786</v>
+        <v>0.7830639245488763</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682770855966334</v>
+        <v>0.7682555195919569</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661763731998086</v>
+        <v>0.7661619907027355</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583500681101041</v>
+        <v>0.7583510652354282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7481017667857792</v>
+        <v>0.7481252611579461</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7394402067476451</v>
+        <v>0.7394770792836579</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7301208294075741</v>
+        <v>0.7301722187738972</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7348058708717217</v>
+        <v>0.7348881243598031</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7402996315577188</v>
+        <v>0.7403868252140537</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7497234900401297</v>
+        <v>0.7498021292278523</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7584391290143556</v>
+        <v>0.758514623380531</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7736455316353257</v>
+        <v>0.7736785241557227</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777630822405215</v>
+        <v>0.7777842959894832</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783994490008749</v>
+        <v>0.7784252872377322</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835814668740927</v>
+        <v>0.7835960387777141</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886371888861993</v>
+        <v>0.7886411603190004</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923265798235943</v>
+        <v>0.7923261712407361</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895681101069225</v>
+        <v>0.7895790621814829</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923359569872914</v>
+        <v>0.7923535161637711</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7979402365093922</v>
+        <v>0.7979698341415594</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8031862383262289</v>
+        <v>0.8016919252716288</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8058061121312414</v>
+        <v>0.8050947952122282</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8082833014623938</v>
+        <v>0.8077201289468494</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098943736146305</v>
+        <v>0.8095630789117698</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8110507546012521</v>
+        <v>0.8111082004690542</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8122066471813405</v>
+        <v>0.8123257226335325</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8129723749686733</v>
+        <v>0.812819072658779</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8138556387292533</v>
+        <v>0.813611483304998</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8178768717084282</v>
+        <v>0.8176086135028351</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8243479160507658</v>
+        <v>0.8240362192084641</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8293001578853553</v>
+        <v>0.8290531100763983</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.833315628106573</v>
+        <v>0.8323741936804314</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8381915873858024</v>
+        <v>0.8367685500745927</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8438263845016793</v>
+        <v>0.8439080919010196</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8440514826063257</v>
+        <v>0.8416869458214068</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8393419747328059</v>
+        <v>0.8339821789277189</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8369574651402758</v>
+        <v>0.8338143573280319</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886630367000811</v>
+        <v>0.7886598323190425</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920044872278562</v>
+        <v>0.7919983007016986</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913679378277246</v>
+        <v>0.7913616973438425</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927807537903402</v>
+        <v>0.7927708416901379</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914575021992614</v>
+        <v>0.7914472974675777</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900062794254188</v>
+        <v>0.7899959162550112</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788428288436114</v>
+        <v>0.7884179753311905</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873440057786369</v>
+        <v>0.7873338826876054</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893690047703934</v>
+        <v>0.789357131066836</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945608884457983</v>
+        <v>0.7945553698229695</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969809167697175</v>
+        <v>0.7969750560989415</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994101153047749</v>
+        <v>0.7994041152611024</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002021586037882</v>
+        <v>0.8001993671095184</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986467149313681</v>
+        <v>0.7986487106360947</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992265999979119</v>
+        <v>0.7992303851279314</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803990561142124</v>
+        <v>0.8039887367451517</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8097002989580452</v>
+        <v>0.8096926912379965</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158991114008314</v>
+        <v>0.8158888106066955</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222703838637995</v>
+        <v>0.8222622301794908</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822957840362326</v>
+        <v>0.8229564267352607</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8186921735286417</v>
+        <v>0.8187013897579415</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152026680015085</v>
+        <v>0.8152152389819022</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137346864693721</v>
+        <v>0.8137574496261627</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119757435683916</v>
+        <v>0.8120120550110591</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117393557906692</v>
+        <v>0.8117855997619013</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8168450363966425</v>
+        <v>0.8169016840868235</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8224777558663874</v>
+        <v>0.8225407981081494</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8292898710053894</v>
+        <v>0.8293597636898682</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8339001598760178</v>
+        <v>0.8339759579379238</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8189297181196811</v>
+        <v>0.8190177691368563</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8207552175195554</v>
+        <v>0.8208428890486781</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8081137979978026</v>
+        <v>0.8082099016297954</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8000548522174379</v>
+        <v>0.8001452602234076</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7927172294054542</v>
+        <v>0.7928211099250324</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7830639245488763</v>
+        <v>0.7831745537482655</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682555195919569</v>
+        <v>0.7682980895800872</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661619907027355</v>
+        <v>0.76619041177782</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583510652354282</v>
+        <v>0.7583491696968832</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7481252611579461</v>
+        <v>0.7480789982742649</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7394770792836579</v>
+        <v>0.7394044444530661</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7301722187738972</v>
+        <v>0.7300709411297551</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7348881243598031</v>
+        <v>0.7347259037655429</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7403868252140537</v>
+        <v>0.7402148394199709</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7498021292278523</v>
+        <v>0.7496469806172958</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.758514623380531</v>
+        <v>0.7583656389795662</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7736785241557227</v>
+        <v>0.7736134101646092</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777842959894832</v>
+        <v>0.7777424122111632</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7784252872377322</v>
+        <v>0.7783742815528107</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835960387777141</v>
+        <v>0.7835672786431125</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886411603190004</v>
+        <v>0.7886333444683805</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923261712407361</v>
+        <v>0.7923270248009144</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895790621814829</v>
+        <v>0.789557490669041</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923535161637711</v>
+        <v>0.7923189141766136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7979698341415594</v>
+        <v>0.79791145200639</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8016919252716288</v>
+        <v>0.8031485568580523</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050947952122282</v>
+        <v>0.8057695667947149</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077201289468494</v>
+        <v>0.8082525177727551</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095630789117698</v>
+        <v>0.8099462602021743</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8111082004690542</v>
+        <v>0.8110978118289784</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8123257226335325</v>
+        <v>0.8121741848292165</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.812819072658779</v>
+        <v>0.8128854131138292</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.813611483304998</v>
+        <v>0.8138144558401839</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8176086135028351</v>
+        <v>0.8177625608880043</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8240362192084641</v>
+        <v>0.8240519642385832</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8290531100763983</v>
+        <v>0.8289247698960659</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8323741936804314</v>
+        <v>0.8329148877771652</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8367685500745927</v>
+        <v>0.8378951172833358</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8439080919010196</v>
+        <v>0.8433184338140883</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8416869458214068</v>
+        <v>0.843473921283471</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8339821789277189</v>
+        <v>0.8392897159653276</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8338143573280319</v>
+        <v>0.8386961343749847</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886598323190425</v>
+        <v>0.7886614116257972</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919983007016986</v>
+        <v>0.7920013498993248</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913616973438425</v>
+        <v>0.7913647735220661</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927708416901379</v>
+        <v>0.7927757274520998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914472974675777</v>
+        <v>0.7914523274448392</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899959162550112</v>
+        <v>0.7900010242908807</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884179753311905</v>
+        <v>0.7884230586696978</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873338826876054</v>
+        <v>0.7873388723680905</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789357131066836</v>
+        <v>0.7893629838719227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945553698229695</v>
+        <v>0.7945580897484049</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969750560989415</v>
+        <v>0.7969779445575553</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994041152611024</v>
+        <v>0.7994070723629906</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001993671095184</v>
+        <v>0.8002007436200436</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986487106360947</v>
+        <v>0.7986477279127484</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992303851279314</v>
+        <v>0.7992285198722252</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039887367451517</v>
+        <v>0.8039896366948753</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096926912379965</v>
+        <v>0.8096964428556233</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158888106066955</v>
+        <v>0.815893892679599</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222622301794908</v>
+        <v>0.8222662542606838</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229564267352607</v>
+        <v>0.8229571292494072</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187013897579415</v>
+        <v>0.818696854681244</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152152389819022</v>
+        <v>0.815209050648207</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137574496261627</v>
+        <v>0.8137462372047114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120120550110591</v>
+        <v>0.8119941657151774</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117855997619013</v>
+        <v>0.8117628140704635</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169016840868235</v>
+        <v>0.8168737697896336</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8225407981081494</v>
+        <v>0.8225097299849498</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8293597636898682</v>
+        <v>0.8293253171156113</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8339759579379238</v>
+        <v>0.8339385842655604</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8190177691368563</v>
+        <v>0.8189743652949049</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8208428890486781</v>
+        <v>0.8207996703469226</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8082099016297954</v>
+        <v>0.8081625292984853</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8001452602234076</v>
+        <v>0.8001006928138585</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7928211099250324</v>
+        <v>0.7927698962574861</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7831745537482655</v>
+        <v>0.7831200022692786</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682980895800872</v>
+        <v>0.7682770855966334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.76619041177782</v>
+        <v>0.7661763731998086</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583491696968832</v>
+        <v>0.7583500681101041</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480789982742649</v>
+        <v>0.7481017667857792</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7394044444530661</v>
+        <v>0.7394402067476451</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7300709411297551</v>
+        <v>0.7301208294075741</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7347259037655429</v>
+        <v>0.7348058708717217</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7402148394199709</v>
+        <v>0.7402996315577188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7496469806172958</v>
+        <v>0.7497234900401297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7583656389795662</v>
+        <v>0.7584391290143556</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7736134101646092</v>
+        <v>0.7736455316353257</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777424122111632</v>
+        <v>0.7777630822405215</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783742815528107</v>
+        <v>0.7783994490008749</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835672786431125</v>
+        <v>0.7835814668740927</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886333444683805</v>
+        <v>0.7886371888861993</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923270248009144</v>
+        <v>0.7923265798235943</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789557490669041</v>
+        <v>0.7895681101069225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923189141766136</v>
+        <v>0.7923359569872914</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.79791145200639</v>
+        <v>0.7979402365093922</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8031485568580523</v>
+        <v>0.8016563592636854</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8057695667947149</v>
+        <v>0.8050588194611477</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8082525177727551</v>
+        <v>0.8076883889168688</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099462602021743</v>
+        <v>0.8096970818900223</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8110978118289784</v>
+        <v>0.81120135177507</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8121741848292165</v>
+        <v>0.8122949111522266</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8128854131138292</v>
+        <v>0.8126454891336772</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8138144558401839</v>
+        <v>0.8134075507523472</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8177625608880043</v>
+        <v>0.8173881128366653</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8240519642385832</v>
+        <v>0.823643689842444</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8289247698960659</v>
+        <v>0.8285795252582345</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8329148877771652</v>
+        <v>0.8319084013762552</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8378951172833358</v>
+        <v>0.8363821973900127</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8433184338140883</v>
+        <v>0.8432045706558828</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.843473921283471</v>
+        <v>0.84122359897841</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8392897159653276</v>
+        <v>0.8345023345279916</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8386961343749847</v>
+        <v>0.8355214289431629</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886614116257972</v>
+        <v>0.7886582968733375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7920013498993248</v>
+        <v>0.7919953359733729</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913647735220661</v>
+        <v>0.7913587056632632</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927757274520998</v>
+        <v>0.7927660906901662</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914523274448392</v>
+        <v>0.7914424062774191</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7900010242908807</v>
+        <v>0.7899909492287247</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884230586696978</v>
+        <v>0.7884130323576496</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873388723680905</v>
+        <v>0.7873290307859385</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893629838719227</v>
+        <v>0.7893514394161352</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945580897484049</v>
+        <v>0.7945527253910617</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969779445575553</v>
+        <v>0.7969722479040862</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994070723629906</v>
+        <v>0.7994012404185564</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8002007436200436</v>
+        <v>0.8001980275274121</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986477279127484</v>
+        <v>0.7986496644314576</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992285198722252</v>
+        <v>0.7992321980608519</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039896366948753</v>
+        <v>0.8039878603375017</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096964428556233</v>
+        <v>0.8096890399280324</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815893892679599</v>
+        <v>0.8158838599244942</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222662542606838</v>
+        <v>0.8222583076742681</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229571292494072</v>
+        <v>0.8229557329318546</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818696854681244</v>
+        <v>0.8187057854123461</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815209050648207</v>
+        <v>0.8152212416667559</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137462372047114</v>
+        <v>0.8137683383136134</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8119941657151774</v>
+        <v>0.8120294341539738</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8117628140704635</v>
+        <v>0.8118077412689781</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8168737697896336</v>
+        <v>0.8169288136790668</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8225097299849498</v>
+        <v>0.8225709980373794</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8293253171156113</v>
+        <v>0.8293932522234182</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8339385842655604</v>
+        <v>0.8340123233040622</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8189743652949049</v>
+        <v>0.8190599807724155</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8207996703469226</v>
+        <v>0.8208849242141474</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8081625292984853</v>
+        <v>0.808255970915926</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8001006928138585</v>
+        <v>0.800188606615104</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7927698962574861</v>
+        <v>0.7928709295241032</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7831200022692786</v>
+        <v>0.7832276401512788</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7682770855966334</v>
+        <v>0.7683185530022055</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7661763731998086</v>
+        <v>0.7662041181894172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583500681101041</v>
+        <v>0.758348362997695</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7481017667857792</v>
+        <v>0.7480569228670594</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7394402067476451</v>
+        <v>0.7393697434080958</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7301208294075741</v>
+        <v>0.730022489424044</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7348058708717217</v>
+        <v>0.7346481293201166</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7402996315577188</v>
+        <v>0.7401323513240029</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7497234900401297</v>
+        <v>0.7495725159920814</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7584391290143556</v>
+        <v>0.7582940749528706</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7736455316353257</v>
+        <v>0.7735821258909077</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777630822405215</v>
+        <v>0.7777222654508327</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783994490008749</v>
+        <v>0.7783497592805118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835814668740927</v>
+        <v>0.7835534591691085</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886371888861993</v>
+        <v>0.7886296211383894</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923265798235943</v>
+        <v>0.7923275027314043</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895681101069225</v>
+        <v>0.7895471890595078</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923359569872914</v>
+        <v>0.7923023654301634</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7979402365093922</v>
+        <v>0.7978834478669969</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8016563592636854</v>
+        <v>0.8031118665411452</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050588194611477</v>
+        <v>0.8057339434866864</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076883889168688</v>
+        <v>0.8082224448083167</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096970818900223</v>
+        <v>0.8100590028297521</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.81120135177507</v>
+        <v>0.8112235981563346</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8122949111522266</v>
+        <v>0.8122332184127042</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8126454891336772</v>
+        <v>0.8129107494000987</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8134075507523472</v>
+        <v>0.8138923550307526</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8173881128366653</v>
+        <v>0.81778112486013</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.823643689842444</v>
+        <v>0.8239189732533083</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8285795252582345</v>
+        <v>0.828730838231687</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8319084013762552</v>
+        <v>0.8327103973729066</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8363821973900127</v>
+        <v>0.8378149737546301</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8432045706558828</v>
+        <v>0.8431124503776414</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.84122359897841</v>
+        <v>0.8433426695270687</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8345023345279916</v>
+        <v>0.8397700045304762</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8355214289431629</v>
+        <v>0.840814494402067</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886582968733375</v>
+        <v>0.7886568034866341</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919953359733729</v>
+        <v>0.7919924522527857</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913587056632632</v>
+        <v>0.7913557950471102</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927660906901662</v>
+        <v>0.7927614689540812</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914424062774191</v>
+        <v>0.7914376482101564</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899909492287247</v>
+        <v>0.7899861174543332</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884130323576496</v>
+        <v>0.7884082240161955</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873290307859385</v>
+        <v>0.7873243110358293</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893514394161352</v>
+        <v>0.7893459023573836</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945527253910617</v>
+        <v>0.794550153353632</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969722479040862</v>
+        <v>0.7969695166743638</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994012404185564</v>
+        <v>0.7993984444511416</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001980275274121</v>
+        <v>0.8001967234103545</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986496644314576</v>
+        <v>0.7986505905523484</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992321980608519</v>
+        <v>0.7992339608400361</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039878603375017</v>
+        <v>0.8039870065652013</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096890399280324</v>
+        <v>0.8096854849676214</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158838599244942</v>
+        <v>0.8158790356393717</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222583076742681</v>
+        <v>0.8222544829905853</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229557329318546</v>
+        <v>0.8229550479196081</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187057854123461</v>
+        <v>0.8187100479037858</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152212416667559</v>
+        <v>0.8152270668630868</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137683383136134</v>
+        <v>0.8137789170245111</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120294341539738</v>
+        <v>0.8120463245754028</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118077412689781</v>
+        <v>0.8118292654243705</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169288136790668</v>
+        <v>0.8169551910658615</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8225709980373794</v>
+        <v>0.8226003655086902</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8293932522234182</v>
+        <v>0.8294258219562143</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340123233040622</v>
+        <v>0.8340477205284275</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8190599807724155</v>
+        <v>0.8191010485683414</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8208849242141474</v>
+        <v>0.8209258237103119</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808255970915926</v>
+        <v>0.8083007900615512</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800188606615104</v>
+        <v>0.8002307813540981</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7928709295241032</v>
+        <v>0.7929194110184593</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7832276401512788</v>
+        <v>0.7832793194352576</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683185530022055</v>
+        <v>0.7683384962571411</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662041181894172</v>
+        <v>0.7662175036852261</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758348362997695</v>
+        <v>0.758347641552271</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480569228670594</v>
+        <v>0.7480355097316138</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7393697434080958</v>
+        <v>0.739336057441297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.730022489424044</v>
+        <v>0.7299754134032614</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7346481293201166</v>
+        <v>0.7345724588512984</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7401323513240029</v>
+        <v>0.7400520749769212</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7495725159920814</v>
+        <v>0.7495000156359837</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7582940749528706</v>
+        <v>0.7582243626145841</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735821258909077</v>
+        <v>0.7735516466827288</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777222654508327</v>
+        <v>0.7777026225113166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783497592805118</v>
+        <v>0.7783258578490981</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835534591691085</v>
+        <v>0.7835399942976579</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886296211383894</v>
+        <v>0.7886260133285935</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923275027314043</v>
+        <v>0.7923280104635674</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895471890595078</v>
+        <v>0.789537191330151</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923023654301634</v>
+        <v>0.7922862897049537</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7978834478669969</v>
+        <v>0.797856193047177</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8031118665411452</v>
+        <v>0.8030761292384904</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8057339434866864</v>
+        <v>0.8056992084590974</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8082224448083167</v>
+        <v>0.8081930593583274</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100590028297521</v>
+        <v>0.8101007965781286</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8112235981563346</v>
+        <v>0.811268349932145</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8122332184127042</v>
+        <v>0.8122080116455526</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8129107494000987</v>
+        <v>0.8129186238389652</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8138923550307526</v>
+        <v>0.8139179827972853</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.81778112486013</v>
+        <v>0.817726280739099</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8239189732533083</v>
+        <v>0.8236984109730832</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.828730838231687</v>
+        <v>0.8284332484240613</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8327103973729066</v>
+        <v>0.8323840565908415</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8378149737546301</v>
+        <v>0.8375770197968044</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8431124503776414</v>
+        <v>0.8427094851983575</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8433426695270687</v>
+        <v>0.8429176624250968</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8397700045304762</v>
+        <v>0.8397082379673531</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.840814494402067</v>
+        <v>0.8407813137040381</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886568034866341</v>
+        <v>0.7886553504542614</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919924522527857</v>
+        <v>0.7919896462649422</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913557950471102</v>
+        <v>0.7913529622456126</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927614689540812</v>
+        <v>0.7927569712787645</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914376482101564</v>
+        <v>0.7914330179055779</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899861174543332</v>
+        <v>0.7899814154833095</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884082240161955</v>
+        <v>0.7884035448818578</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873243110358293</v>
+        <v>0.7873197181122544</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893459023573836</v>
+        <v>0.7893405136795153</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794550153353632</v>
+        <v>0.7945476507789122</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969695166743638</v>
+        <v>0.7969668592894026</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993984444511416</v>
+        <v>0.7993957241577168</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001967234103545</v>
+        <v>0.8001954533711219</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986505905523484</v>
+        <v>0.7986514901811477</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992339608400361</v>
+        <v>0.7992356755163842</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039870065652013</v>
+        <v>0.8039861745672096</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096854849676214</v>
+        <v>0.809682022603553</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158790356393717</v>
+        <v>0.8158743330055072</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222544829905853</v>
+        <v>0.8222507525542597</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229550479196081</v>
+        <v>0.8229543717512131</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187100479037858</v>
+        <v>0.8187141831258604</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152270668630868</v>
+        <v>0.8152327222632472</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137789170245111</v>
+        <v>0.8137891987508333</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120463245754028</v>
+        <v>0.8120627465271887</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118292654243705</v>
+        <v>0.8118501975962396</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169551910658615</v>
+        <v>0.8169808469831349</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226003655086902</v>
+        <v>0.8226289343313752</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8294258219562143</v>
+        <v>0.829457510023409</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340477205284275</v>
+        <v>0.8340821876753928</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8191010485683414</v>
+        <v>0.8191410183147116</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8209258237103119</v>
+        <v>0.8209656328621422</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8083007900615512</v>
+        <v>0.8083444091524116</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8002307813540981</v>
+        <v>0.8002718311870189</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7929194110184593</v>
+        <v>0.792966607426201</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7832793194352576</v>
+        <v>0.7833296465551642</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683384962571411</v>
+        <v>0.7683579387377187</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662175036852261</v>
+        <v>0.7662305790381758</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758347641552271</v>
+        <v>0.7583469993916672</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480355097316138</v>
+        <v>0.7480147298210735</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739336057441297</v>
+        <v>0.7393033430027998</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7299754134032614</v>
+        <v>0.7299296555587949</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7345724588512984</v>
+        <v>0.7344988083791228</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7400520749769212</v>
+        <v>0.7399739229310651</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7495000156359837</v>
+        <v>0.7494294031746069</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7582243626145841</v>
+        <v>0.758156431397728</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735516466827288</v>
+        <v>0.7735219420224575</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777026225113166</v>
+        <v>0.7776834648868256</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783258578490981</v>
+        <v>0.778302554123729</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835399942976579</v>
+        <v>0.7835268705877487</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886260133285935</v>
+        <v>0.788622515804263</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923280104635674</v>
+        <v>0.7923285451095882</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789537191330151</v>
+        <v>0.7895274843317679</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922862897049537</v>
+        <v>0.7922706671295069</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797856193047177</v>
+        <v>0.7978296581138624</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8030761292384904</v>
+        <v>0.8030413087202404</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8056992084590974</v>
+        <v>0.805665329551587</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8081930593583274</v>
+        <v>0.8081643391462916</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8101007965781286</v>
+        <v>0.8101406023853894</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.811268349932145</v>
+        <v>0.8112994831834025</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8122080116455526</v>
+        <v>0.8121481017231178</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8129186238389652</v>
+        <v>0.8128439897785237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8139179827972853</v>
+        <v>0.8138361615236447</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.817726280739099</v>
+        <v>0.8175691457204952</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8236984109730832</v>
+        <v>0.8233935944321378</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8284332484240613</v>
+        <v>0.8280640952824783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8323840565908415</v>
+        <v>0.8319978655567526</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8375770197968044</v>
+        <v>0.8372640190531664</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8427094851983575</v>
+        <v>0.8422410050325942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8429176624250968</v>
+        <v>0.8423749158477648</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8397082379673531</v>
+        <v>0.8392792400242863</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8407813137040381</v>
+        <v>0.8394715630491451</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886553504542614</v>
+        <v>0.7886539361624364</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919896462649422</v>
+        <v>0.7919869149090146</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913529622456126</v>
+        <v>0.7913502041803601</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927569712787645</v>
+        <v>0.792752592736568</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914330179055779</v>
+        <v>0.7914285102873506</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899814154833095</v>
+        <v>0.7899768381558177</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884035448818578</v>
+        <v>0.7883989898171845</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873197181122544</v>
+        <v>0.7873152469724125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893405136795153</v>
+        <v>0.7893352674996408</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945476507789122</v>
+        <v>0.7945452148912823</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969668592894026</v>
+        <v>0.7969642727952101</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993957241577168</v>
+        <v>0.7993930765080015</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001954533711219</v>
+        <v>0.8001942160937592</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986514901811477</v>
+        <v>0.7986523644340648</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992356755163842</v>
+        <v>0.799237344030578</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039861745672096</v>
+        <v>0.8039853635253492</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809682022603553</v>
+        <v>0.8096786492744734</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158743330055072</v>
+        <v>0.8158697475098453</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222507525542597</v>
+        <v>0.8222471129608498</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229543717512131</v>
+        <v>0.8229537044550219</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187141831258604</v>
+        <v>0.8187181966325671</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152327222632472</v>
+        <v>0.8152382151244898</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137891987508333</v>
+        <v>0.8137991957714008</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120627465271887</v>
+        <v>0.8120787191613332</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118501975962396</v>
+        <v>0.8118705617864655</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169808469831349</v>
+        <v>0.8170058105208455</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226289343313752</v>
+        <v>0.8226567365155935</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.829457510023409</v>
+        <v>0.8294883515940179</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340821876753928</v>
+        <v>0.8341157608444016</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8191410183147116</v>
+        <v>0.8191799333939505</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8209656328621422</v>
+        <v>0.8210043946188122</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8083444091524116</v>
+        <v>0.8083868756401573</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8002718311870189</v>
+        <v>0.8003118004128533</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.792966607426201</v>
+        <v>0.7930125690103811</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7833296465551642</v>
+        <v>0.783378673654849</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683579387377187</v>
+        <v>0.7683768988953117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662305790381758</v>
+        <v>0.7662433545666401</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583469993916672</v>
+        <v>0.7583464309962886</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480147298210735</v>
+        <v>0.7479945557478257</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7393033430027998</v>
+        <v>0.7392715589819735</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7299296555587949</v>
+        <v>0.7298851615303628</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7344988083791228</v>
+        <v>0.7344270983209393</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7399739229310651</v>
+        <v>0.7398978122714259</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7494294031746069</v>
+        <v>0.7493606061245153</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.758156431397728</v>
+        <v>0.7580902142556254</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735219420224575</v>
+        <v>0.7734929829069324</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776834648868256</v>
+        <v>0.7776647749582464</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778302554123729</v>
+        <v>0.7782798260971008</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835268705877487</v>
+        <v>0.7835140752675067</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788622515804263</v>
+        <v>0.7886191236392621</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923285451095882</v>
+        <v>0.7923291040218033</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895274843317679</v>
+        <v>0.789518055658061</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922706671295069</v>
+        <v>0.7922554789238727</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7978296581138624</v>
+        <v>0.7978038151427254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8030413087202404</v>
+        <v>0.8030073705476046</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.805665329551587</v>
+        <v>0.8056322761019569</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8081643391462916</v>
+        <v>0.8081362627883584</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8101406023853894</v>
+        <v>0.8102495694067863</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8112994831834025</v>
+        <v>0.8114181908143251</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8121481017231178</v>
+        <v>0.8121950049424052</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8128439897785237</v>
+        <v>0.8128862971241053</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8138361615236447</v>
+        <v>0.8138927004275824</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8175691457204952</v>
+        <v>0.8175697442597458</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8233935944321378</v>
+        <v>0.8232775967219984</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8280640952824783</v>
+        <v>0.8279031052025357</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8319978655567526</v>
+        <v>0.8318358647478047</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8372640190531664</v>
+        <v>0.8372025860356108</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8422410050325942</v>
+        <v>0.8420977837221275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8423749158477648</v>
+        <v>0.8422732123654835</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8392792400242863</v>
+        <v>0.8394101329899001</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8394715630491451</v>
+        <v>0.8395356187849966</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886539361624364</v>
+        <v>0.7886582968733375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919869149090146</v>
+        <v>0.7919953359733729</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913502041803601</v>
+        <v>0.7913587056632632</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.792752592736568</v>
+        <v>0.7927660906901662</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914285102873506</v>
+        <v>0.7914424062774191</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899768381558177</v>
+        <v>0.7899909492287247</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883989898171845</v>
+        <v>0.7884130323576496</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873152469724125</v>
+        <v>0.7873290307859385</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893352674996408</v>
+        <v>0.7893514394161352</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945452148912823</v>
+        <v>0.7945527253910617</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969642727952101</v>
+        <v>0.7969722479040862</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993930765080015</v>
+        <v>0.7994012404185564</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001942160937592</v>
+        <v>0.8001980275274121</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986523644340648</v>
+        <v>0.7986496644314576</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799237344030578</v>
+        <v>0.7992321980608519</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039853635253492</v>
+        <v>0.8039878603375017</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096786492744734</v>
+        <v>0.8096890399280324</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158697475098453</v>
+        <v>0.8158838599244942</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222471129608498</v>
+        <v>0.8222583076742681</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229537044550219</v>
+        <v>0.8229557329318546</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187181966325671</v>
+        <v>0.8187057854123461</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152382151244898</v>
+        <v>0.8152212416667559</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137991957714008</v>
+        <v>0.8137683383136134</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120787191613332</v>
+        <v>0.8120294341539738</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118705617864655</v>
+        <v>0.8118077412689781</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170058105208455</v>
+        <v>0.8169288136790668</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226567365155935</v>
+        <v>0.8225709980373794</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8294883515940179</v>
+        <v>0.8293932522234182</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8341157608444016</v>
+        <v>0.8340123233040622</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8191799333939505</v>
+        <v>0.8190599807724155</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8210043946188122</v>
+        <v>0.8208849242141474</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8083868756401573</v>
+        <v>0.808255970915926</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8003118004128533</v>
+        <v>0.800188606615104</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7930125690103811</v>
+        <v>0.7928709295241032</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.783378673654849</v>
+        <v>0.7832276401512788</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683768988953117</v>
+        <v>0.7683185530022055</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662433545666401</v>
+        <v>0.7662041181894172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583464309962886</v>
+        <v>0.758348362997695</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479945557478257</v>
+        <v>0.7480569228670594</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7392715589819735</v>
+        <v>0.7393697434080958</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7298851615303628</v>
+        <v>0.730022489424044</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7344270983209393</v>
+        <v>0.7346481293201166</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7398978122714259</v>
+        <v>0.7401323513240029</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7493606061245153</v>
+        <v>0.7495725159920814</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7580902142556254</v>
+        <v>0.7582940749528706</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734929829069324</v>
+        <v>0.7735821258909077</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776647749582464</v>
+        <v>0.7777222654508327</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7782798260971008</v>
+        <v>0.7783497592805118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835140752675067</v>
+        <v>0.7835534591691085</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886191236392621</v>
+        <v>0.7886296211383894</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923291040218033</v>
+        <v>0.7923275027314043</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789518055658061</v>
+        <v>0.7895471890595078</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922554789238727</v>
+        <v>0.7923023654301634</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7978038151427254</v>
+        <v>0.7978834478669969</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8030073705476046</v>
+        <v>0.8015880542010211</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8056322761019569</v>
+        <v>0.8049896005833391</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8081362627883584</v>
+        <v>0.8076271535639874</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8102495694067863</v>
+        <v>0.809731066254885</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8114181908143251</v>
+        <v>0.8112525066513329</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8121950049424052</v>
+        <v>0.8121768291823637</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8128862971241053</v>
+        <v>0.8124679999926182</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8138927004275824</v>
+        <v>0.8130636387607693</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8175697442597458</v>
+        <v>0.8168351967344365</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8232775967219984</v>
+        <v>0.8227282700878972</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8279031052025357</v>
+        <v>0.8274809445473972</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8318358647478047</v>
+        <v>0.8307886335628072</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8372025860356108</v>
+        <v>0.8352232481703177</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8420977837221275</v>
+        <v>0.8415813868350341</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8422732123654835</v>
+        <v>0.8398718481012237</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8394101329899001</v>
+        <v>0.8342769396315368</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,15 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8395356187849966</v>
+        <v>0.8350068154244441</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B78">
+        <v>0.8265915928234833</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886582968733375</v>
+        <v>0.7886525590822877</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919953359733729</v>
+        <v>0.7919842552469178</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913587056632632</v>
+        <v>0.7913475179331588</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927660906901662</v>
+        <v>0.7927483286573256</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914424062774191</v>
+        <v>0.7914241205444772</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899909492287247</v>
+        <v>0.7899723805818482</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884130323576496</v>
+        <v>0.7883945539534473</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873290307859385</v>
+        <v>0.7873108928372754</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893514394161352</v>
+        <v>0.7893301582416636</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945527253910617</v>
+        <v>0.794542843061014</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969722479040862</v>
+        <v>0.7969617543932308</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7994012404185564</v>
+        <v>0.7993904986313287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001980275274121</v>
+        <v>0.8001930103290704</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986496644314576</v>
+        <v>0.7986532143656877</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992321980608519</v>
+        <v>0.7992389682203789</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039878603375017</v>
+        <v>0.8039845726616881</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096890399280324</v>
+        <v>0.8096753615988174</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158838599244942</v>
+        <v>0.8158652748581295</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222583076742681</v>
+        <v>0.8222435609658605</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229557329318546</v>
+        <v>0.8229530460380439</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187057854123461</v>
+        <v>0.8187220936622304</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152212416667559</v>
+        <v>0.8152435522991197</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137683383136134</v>
+        <v>0.813808919699973</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120294341539738</v>
+        <v>0.812094260603422</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118077412689781</v>
+        <v>0.8118903807211058</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169288136790668</v>
+        <v>0.8170301092313283</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8225709980373794</v>
+        <v>0.8226838023900136</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8293932522234182</v>
+        <v>0.8295183799988093</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340123233040622</v>
+        <v>0.8341484742948387</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8190599807724155</v>
+        <v>0.819217834936746</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8208849242141474</v>
+        <v>0.8210421497070637</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808255970915926</v>
+        <v>0.8084282345128705</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800188606615104</v>
+        <v>0.8003507310406516</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7928709295241032</v>
+        <v>0.7930573434550583</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7832276401512788</v>
+        <v>0.7834264502436177</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683185530022055</v>
+        <v>0.7683953942955399</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662041181894172</v>
+        <v>0.7662558401564379</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758348362997695</v>
+        <v>0.7583459312579334</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480569228670594</v>
+        <v>0.7479749616675728</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7393697434080958</v>
+        <v>0.7392406665400255</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.730022489424044</v>
+        <v>0.7298418798942869</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7346481293201166</v>
+        <v>0.7343572532081833</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7401323513240029</v>
+        <v>0.7398236643268563</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7495725159920814</v>
+        <v>0.7492935556497329</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7582940749528706</v>
+        <v>0.7580256474464384</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735821258909077</v>
+        <v>0.7734647417552297</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777222654508327</v>
+        <v>0.7776465359412497</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783497592805118</v>
+        <v>0.7782576528220961</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835534591691085</v>
+        <v>0.7835015961931663</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886296211383894</v>
+        <v>0.7886158321938235</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923275027314043</v>
+        <v>0.7923296847714785</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895471890595078</v>
+        <v>0.7895088935942027</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7923023654301634</v>
+        <v>0.792240707326078</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7978834478669969</v>
+        <v>0.7977786376235655</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8015880542010211</v>
+        <v>0.8029742819649883</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049896005833391</v>
+        <v>0.8056000188623983</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076271535639874</v>
+        <v>0.8081088097534488</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809731066254885</v>
+        <v>0.8102284403499072</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8112525066513329</v>
+        <v>0.8114488219746523</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8121768291823637</v>
+        <v>0.812172338310357</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8124679999926182</v>
+        <v>0.8128605965463183</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8130636387607693</v>
+        <v>0.8137802887821999</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8168351967344365</v>
+        <v>0.8173108429930626</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8227282700878972</v>
+        <v>0.8228204373132302</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8274809445473972</v>
+        <v>0.8273053284772784</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8307886335628072</v>
+        <v>0.8311315250956216</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8352232481703177</v>
+        <v>0.8363187500935427</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8415813868350341</v>
+        <v>0.8410517816760182</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8398718481012237</v>
+        <v>0.8410393207821173</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8342769396315368</v>
+        <v>0.8381607950689568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8350068154244441</v>
+        <v>0.8373731996953915</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8265915928234833</v>
+        <v>0.825967219678662</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886525590822877</v>
+        <v>0.7886568034866341</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919842552469178</v>
+        <v>0.7919924522527857</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913475179331588</v>
+        <v>0.7913557950471102</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927483286573256</v>
+        <v>0.7927614689540812</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914241205444772</v>
+        <v>0.7914376482101564</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899723805818482</v>
+        <v>0.7899861174543332</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883945539534473</v>
+        <v>0.7884082240161955</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873108928372754</v>
+        <v>0.7873243110358293</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893301582416636</v>
+        <v>0.7893459023573836</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794542843061014</v>
+        <v>0.794550153353632</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969617543932308</v>
+        <v>0.7969695166743638</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993904986313287</v>
+        <v>0.7993984444511416</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001930103290704</v>
+        <v>0.8001967234103545</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986532143656877</v>
+        <v>0.7986505905523484</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992389682203789</v>
+        <v>0.7992339608400361</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039845726616881</v>
+        <v>0.8039870065652013</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096753615988174</v>
+        <v>0.8096854849676214</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158652748581295</v>
+        <v>0.8158790356393717</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222435609658605</v>
+        <v>0.8222544829905853</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229530460380439</v>
+        <v>0.8229550479196081</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187220936622304</v>
+        <v>0.8187100479037858</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152435522991197</v>
+        <v>0.8152270668630868</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813808919699973</v>
+        <v>0.8137789170245111</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.812094260603422</v>
+        <v>0.8120463245754028</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118903807211058</v>
+        <v>0.8118292654243705</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170301092313283</v>
+        <v>0.8169551910658615</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226838023900136</v>
+        <v>0.8226003655086902</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8295183799988093</v>
+        <v>0.8294258219562143</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8341484742948387</v>
+        <v>0.8340477205284275</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.819217834936746</v>
+        <v>0.8191010485683414</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8210421497070637</v>
+        <v>0.8209258237103119</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8084282345128705</v>
+        <v>0.8083007900615512</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8003507310406516</v>
+        <v>0.8002307813540981</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7930573434550583</v>
+        <v>0.7929194110184593</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7834264502436177</v>
+        <v>0.7832793194352576</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683953942955399</v>
+        <v>0.7683384962571411</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662558401564379</v>
+        <v>0.7662175036852261</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583459312579334</v>
+        <v>0.758347641552271</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479749616675728</v>
+        <v>0.7480355097316138</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7392406665400255</v>
+        <v>0.739336057441297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7298418798942869</v>
+        <v>0.7299754134032614</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7343572532081833</v>
+        <v>0.7345724588512984</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7398236643268563</v>
+        <v>0.7400520749769212</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7492935556497329</v>
+        <v>0.7495000156359837</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7580256474464384</v>
+        <v>0.7582243626145841</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734647417552297</v>
+        <v>0.7735516466827288</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776465359412497</v>
+        <v>0.7777026225113166</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7782576528220961</v>
+        <v>0.7783258578490981</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835015961931663</v>
+        <v>0.7835399942976579</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886158321938235</v>
+        <v>0.7886260133285935</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923296847714785</v>
+        <v>0.7923280104635674</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895088935942027</v>
+        <v>0.789537191330151</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792240707326078</v>
+        <v>0.7922862897049537</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7977786376235655</v>
+        <v>0.797856193047177</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8029742819649883</v>
+        <v>0.8015552419951935</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8056000188623983</v>
+        <v>0.8049562904632019</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8081088097534488</v>
+        <v>0.8075976079412401</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8102284403499072</v>
+        <v>0.809707031923079</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8114488219746523</v>
+        <v>0.8111866586138698</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.812172338310357</v>
+        <v>0.8120528000400555</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8128605965463183</v>
+        <v>0.8123354696601464</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8137802887821999</v>
+        <v>0.8127846443970227</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8173108429930626</v>
+        <v>0.8164188803052073</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8228204373132302</v>
+        <v>0.8221482273932132</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8273053284772784</v>
+        <v>0.8268103625176881</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8311315250956216</v>
+        <v>0.830100854303749</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8363187500935427</v>
+        <v>0.8344442116438475</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8410517816760182</v>
+        <v>0.8406486285602893</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8410393207821173</v>
+        <v>0.8390035910520209</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8381607950689568</v>
+        <v>0.8337235114299906</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8373731996953915</v>
+        <v>0.8323830494133088</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.825967219678662</v>
+        <v>0.8237278425778529</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886568034866341</v>
+        <v>0.7886512177643419</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919924522527857</v>
+        <v>0.7919816644927713</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913557950471102</v>
+        <v>0.7913449007357447</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927614689540812</v>
+        <v>0.7927441746117592</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914376482101564</v>
+        <v>0.7914198441141894</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899861174543332</v>
+        <v>0.7899680381238123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884082240161955</v>
+        <v>0.7883902326733042</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873243110358293</v>
+        <v>0.7873066511745703</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893459023573836</v>
+        <v>0.789325180616548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794550153353632</v>
+        <v>0.794540532794813</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969695166743638</v>
+        <v>0.7969593014302596</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993984444511416</v>
+        <v>0.7993879878062762</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001967234103545</v>
+        <v>0.8001918348904484</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986505905523484</v>
+        <v>0.7986540409731649</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992339608400361</v>
+        <v>0.7992405498273573</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039870065652013</v>
+        <v>0.8039838012361127</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096854849676214</v>
+        <v>0.8096721563636399</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158790356393717</v>
+        <v>0.8158609109619187</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222544829905853</v>
+        <v>0.8222400934756033</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229550479196081</v>
+        <v>0.8229523964886012</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187100479037858</v>
+        <v>0.8187258791594516</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152270668630868</v>
+        <v>0.8152487402621857</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137789170245111</v>
+        <v>0.813818381529517</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120463245754028</v>
+        <v>0.8121093880202626</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118292654243705</v>
+        <v>0.8119096759337836</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169551910658615</v>
+        <v>0.8170537692292212</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226003655086902</v>
+        <v>0.8227101607103866</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8294258219562143</v>
+        <v>0.8295476268483777</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340477205284275</v>
+        <v>0.8341803605615217</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8191010485683414</v>
+        <v>0.8192547619660271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8209258237103119</v>
+        <v>0.8210789367728639</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8083007900615512</v>
+        <v>0.8084685284525384</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8002307813540981</v>
+        <v>0.8003886629352281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7929194110184593</v>
+        <v>0.793100976028067</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7832793194352576</v>
+        <v>0.7834730233597277</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683384962571411</v>
+        <v>0.7684134416701236</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662175036852261</v>
+        <v>0.7662680452817342</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758347641552271</v>
+        <v>0.7583454954454305</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480355097316138</v>
+        <v>0.7479559231729305</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739336057441297</v>
+        <v>0.7392106289561248</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7299754134032614</v>
+        <v>0.7297997619685637</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7345724588512984</v>
+        <v>0.7342892014246958</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7400520749769212</v>
+        <v>0.739751404402997</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7495000156359837</v>
+        <v>0.7492281863362147</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7582243626145841</v>
+        <v>0.7579626703332327</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735516466827288</v>
+        <v>0.7734371923230609</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7777026225113166</v>
+        <v>0.777628731837954</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7783258578490981</v>
+        <v>0.7782360143491602</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835399942976579</v>
+        <v>0.7834894218110197</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886260133285935</v>
+        <v>0.7886126370942049</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923280104635674</v>
+        <v>0.7923302851296403</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789537191330151</v>
+        <v>0.7894999870695933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922862897049537</v>
+        <v>0.7922263355244179</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797856193047177</v>
+        <v>0.7977541003726651</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8015552419951935</v>
+        <v>0.8029420117997192</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049562904632019</v>
+        <v>0.8055685299210719</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075976079412401</v>
+        <v>0.8080819603250926</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809707031923079</v>
+        <v>0.8102077261788695</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8111866586138698</v>
+        <v>0.8113813655015301</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8120528000400555</v>
+        <v>0.8120407216316626</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8123354696601464</v>
+        <v>0.8127326127375649</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8127846443970227</v>
+        <v>0.813577346407904</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8164188803052073</v>
+        <v>0.8169673037434015</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8221482273932132</v>
+        <v>0.8222756525999434</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8268103625176881</v>
+        <v>0.82662626677285</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.830100854303749</v>
+        <v>0.8303510812194911</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8344442116438475</v>
+        <v>0.8353697059378287</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8406486285602893</v>
+        <v>0.8399541709694875</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8390035910520209</v>
+        <v>0.839759869435603</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8337235114299906</v>
+        <v>0.8368496151670077</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8323830494133088</v>
+        <v>0.8353318867438493</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8237278425778529</v>
+        <v>0.8243059548788865</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886512177643419</v>
+        <v>0.7886553504542614</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919816644927713</v>
+        <v>0.7919896462649422</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913449007357447</v>
+        <v>0.7913529622456126</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927441746117592</v>
+        <v>0.7927569712787645</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914198441141894</v>
+        <v>0.7914330179055779</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899680381238123</v>
+        <v>0.7899814154833095</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883902326733042</v>
+        <v>0.7884035448818578</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873066511745703</v>
+        <v>0.7873197181122544</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789325180616548</v>
+        <v>0.7893405136795153</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794540532794813</v>
+        <v>0.7945476507789122</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969593014302596</v>
+        <v>0.7969668592894026</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993879878062762</v>
+        <v>0.7993957241577168</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001918348904484</v>
+        <v>0.8001954533711219</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986540409731649</v>
+        <v>0.7986514901811477</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992405498273573</v>
+        <v>0.7992356755163842</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039838012361127</v>
+        <v>0.8039861745672096</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096721563636399</v>
+        <v>0.809682022603553</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158609109619187</v>
+        <v>0.8158743330055072</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222400934756033</v>
+        <v>0.8222507525542597</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229523964886012</v>
+        <v>0.8229543717512131</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187258791594516</v>
+        <v>0.8187141831258604</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152487402621857</v>
+        <v>0.8152327222632472</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813818381529517</v>
+        <v>0.8137891987508333</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121093880202626</v>
+        <v>0.8120627465271887</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119096759337836</v>
+        <v>0.8118501975962396</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170537692292212</v>
+        <v>0.8169808469831349</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227101607103866</v>
+        <v>0.8226289343313752</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8295476268483777</v>
+        <v>0.829457510023409</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8341803605615217</v>
+        <v>0.8340821876753928</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8192547619660271</v>
+        <v>0.8191410183147116</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8210789367728639</v>
+        <v>0.8209656328621422</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8084685284525384</v>
+        <v>0.8083444091524116</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8003886629352281</v>
+        <v>0.8002718311870189</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793100976028067</v>
+        <v>0.792966607426201</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7834730233597277</v>
+        <v>0.7833296465551642</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684134416701236</v>
+        <v>0.7683579387377187</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662680452817342</v>
+        <v>0.7662305790381758</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583454954454305</v>
+        <v>0.7583469993916672</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479559231729305</v>
+        <v>0.7480147298210735</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7392106289561248</v>
+        <v>0.7393033430027998</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7297997619685637</v>
+        <v>0.7299296555587949</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7342892014246958</v>
+        <v>0.7344988083791228</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.739751404402997</v>
+        <v>0.7399739229310651</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7492281863362147</v>
+        <v>0.7494294031746069</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7579626703332327</v>
+        <v>0.758156431397728</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734371923230609</v>
+        <v>0.7735219420224575</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.777628731837954</v>
+        <v>0.7776834648868256</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7782360143491602</v>
+        <v>0.778302554123729</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834894218110197</v>
+        <v>0.7835268705877487</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886126370942049</v>
+        <v>0.788622515804263</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923302851296403</v>
+        <v>0.7923285451095882</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894999870695933</v>
+        <v>0.7895274843317679</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922263355244179</v>
+        <v>0.7922706671295069</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7977541003726651</v>
+        <v>0.7978296581138624</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8029420117997192</v>
+        <v>0.8015232776526136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8055685299210719</v>
+        <v>0.804923804536126</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8080819603250926</v>
+        <v>0.8075687452490199</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8102077261788695</v>
+        <v>0.8096835074935049</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8113813655015301</v>
+        <v>0.8106392252145787</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8120407216316626</v>
+        <v>0.8113443461734868</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8127326127375649</v>
+        <v>0.8115692641848828</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.813577346407904</v>
+        <v>0.8117722623380075</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8169673037434015</v>
+        <v>0.8152446987489763</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8222756525999434</v>
+        <v>0.8207619646878217</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.82662626677285</v>
+        <v>0.8253035460649512</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8303510812194911</v>
+        <v>0.8285340728592752</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8353697059378287</v>
+        <v>0.8327177595166469</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8399541709694875</v>
+        <v>0.8379119822905454</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.839759869435603</v>
+        <v>0.8358667656288341</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8368496151670077</v>
+        <v>0.8299460340947293</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8353318867438493</v>
+        <v>0.8263659653364159</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8243059548788865</v>
+        <v>0.8131462210961503</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886553504542614</v>
+        <v>0.7886499108334373</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919896462649422</v>
+        <v>0.7919791400031709</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913529622456126</v>
+        <v>0.79134234996028</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927569712787645</v>
+        <v>0.7927401263961473</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914330179055779</v>
+        <v>0.791415676666146</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899814154833095</v>
+        <v>0.789963806380467</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7884035448818578</v>
+        <v>0.788386021594786</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873197181122544</v>
+        <v>0.7873025176830608</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893405136795153</v>
+        <v>0.7893203296040887</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945476507789122</v>
+        <v>0.7945382817270867</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969668592894026</v>
+        <v>0.7969569113891289</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993957241577168</v>
+        <v>0.7993855414510942</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001954533711219</v>
+        <v>0.8001906886500108</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986514901811477</v>
+        <v>0.7986548452000523</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992356755163842</v>
+        <v>0.7992420905030988</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039861745672096</v>
+        <v>0.8039830485440712</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809682022603553</v>
+        <v>0.8096690305142678</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158743330055072</v>
+        <v>0.8158566519265071</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222507525542597</v>
+        <v>0.8222367075386665</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229543717512131</v>
+        <v>0.822951755778689</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187141831258604</v>
+        <v>0.8187295577952627</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152327222632472</v>
+        <v>0.8152537851369409</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8137891987508333</v>
+        <v>0.8138275916729965</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8120627465271887</v>
+        <v>0.8121241176822588</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8118501975962396</v>
+        <v>0.8119284678426391</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8169808469831349</v>
+        <v>0.8170768152837252</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8226289343313752</v>
+        <v>0.8227358387598378</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.829457510023409</v>
+        <v>0.8295761221422695</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8340821876753928</v>
+        <v>0.8342114505616205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8191410183147116</v>
+        <v>0.8192907515300514</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8209656328621422</v>
+        <v>0.8211147925123856</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8083444091524116</v>
+        <v>0.808507797980627</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8002718311870189</v>
+        <v>0.8004256339519049</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.792966607426201</v>
+        <v>0.793143509731655</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7833296465551642</v>
+        <v>0.7835184377219189</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7683579387377187</v>
+        <v>0.76843105696519</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662305790381758</v>
+        <v>0.7662799790248824</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583469993916672</v>
+        <v>0.7583451191734898</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7480147298210735</v>
+        <v>0.7479374171956508</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7393033430027998</v>
+        <v>0.7391814114857999</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7299296555587949</v>
+        <v>0.7297587616332069</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7344988083791228</v>
+        <v>0.7342228749647033</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7399739229310651</v>
+        <v>0.7396809615350416</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7494294031746069</v>
+        <v>0.7491644359827656</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.758156431397728</v>
+        <v>0.7579012251982891</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7735219420224575</v>
+        <v>0.7734103096232352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776834648868256</v>
+        <v>0.7776113473918695</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778302554123729</v>
+        <v>0.778214891668032</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7835268705877487</v>
+        <v>0.7834775411220911</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788622515804263</v>
+        <v>0.788609534214043</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923285451095882</v>
+        <v>0.7923309030497477</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7895274843317679</v>
+        <v>0.7894913256144225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922706671295069</v>
+        <v>0.7922123475950541</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7978296581138624</v>
+        <v>0.797730179451522</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8015232776526136</v>
+        <v>0.8029105303687545</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.804923804536126</v>
+        <v>0.8055377826286679</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075687452490199</v>
+        <v>0.8080556955649394</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096835074935049</v>
+        <v>0.810187415860916</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8106392252145787</v>
+        <v>0.8108688228056085</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8113443461734868</v>
+        <v>0.8113532712148475</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8115692641848828</v>
+        <v>0.8119818738918132</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8117722623380075</v>
+        <v>0.8126613995353399</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8152446987489763</v>
+        <v>0.815860271350497</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8207619646878217</v>
+        <v>0.8208996078818186</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8253035460649512</v>
+        <v>0.8250674810229692</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285340728592752</v>
+        <v>0.8286368344199022</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8327177595166469</v>
+        <v>0.83341025477918</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8379119822905454</v>
+        <v>0.837559940966679</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8358667656288341</v>
+        <v>0.8368180954850943</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8299460340947293</v>
+        <v>0.8334185911143979</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8263659653364159</v>
+        <v>0.8299916056725509</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8131462210961503</v>
+        <v>0.8127048932702852</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886499108334373</v>
+        <v>0.7886486369840211</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919791400031709</v>
+        <v>0.7919766792681967</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.79134234996028</v>
+        <v>0.7913398631105625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927401263961473</v>
+        <v>0.7927361800181523</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791415676666146</v>
+        <v>0.7914116140878227</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789963806380467</v>
+        <v>0.7899596811720523</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788386021594786</v>
+        <v>0.7883819165564895</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873025176830608</v>
+        <v>0.7872984882780135</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893203296040887</v>
+        <v>0.7893156004360511</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945382817270867</v>
+        <v>0.7945360876118731</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969569113891289</v>
+        <v>0.7969545818801009</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993855414510942</v>
+        <v>0.7993831571148609</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001906886500108</v>
+        <v>0.8001895705350179</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986548452000523</v>
+        <v>0.7986556279398538</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992420905030988</v>
+        <v>0.7992435918149374</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039830485440712</v>
+        <v>0.8039823139144766</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096690305142678</v>
+        <v>0.8096659811446998</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158566519265071</v>
+        <v>0.8158524940396761</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222367075386665</v>
+        <v>0.8222334003379432</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822951755778689</v>
+        <v>0.8229511238660618</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187295577952627</v>
+        <v>0.8187331339856521</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152537851369409</v>
+        <v>0.8152586927182801</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138275916729965</v>
+        <v>0.8138365600009974</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121241176822588</v>
+        <v>0.8121384650209915</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119284678426391</v>
+        <v>0.8119467758214151</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170768152837252</v>
+        <v>0.8170992709038718</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227358387598378</v>
+        <v>0.8227608624416127</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8295761221422695</v>
+        <v>0.8296038943699364</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8342114505616205</v>
+        <v>0.8342417736937418</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8192907515300514</v>
+        <v>0.8193258388255515</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8211147925123856</v>
+        <v>0.8211497517932308</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808507797980627</v>
+        <v>0.80854608159279</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8004256339519049</v>
+        <v>0.8004616800612466</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793143509731655</v>
+        <v>0.7931849854420276</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7835184377219189</v>
+        <v>0.7835627358699866</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.76843105696519</v>
+        <v>0.7684482553863107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662799790248824</v>
+        <v>0.7662916500952588</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583451191734898</v>
+        <v>0.7583447983744347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479374171956508</v>
+        <v>0.7479194219166746</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7391814114857999</v>
+        <v>0.7391529812304908</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7297587616332069</v>
+        <v>0.7297188351644871</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7342228749647033</v>
+        <v>0.7341582092087681</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7396809615350416</v>
+        <v>0.7396122682586534</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7491644359827656</v>
+        <v>0.7491022454070311</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7579012251982891</v>
+        <v>0.7578412570704994</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734103096232352</v>
+        <v>0.7733840698517047</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776113473918695</v>
+        <v>0.7775943680458649</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778214891668032</v>
+        <v>0.7781942666534788</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834775411220911</v>
+        <v>0.7834659436493143</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788609534214043</v>
+        <v>0.7886065196572402</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923309030497477</v>
+        <v>0.7923315366520055</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894913256144225</v>
+        <v>0.7894828993196779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922123475950541</v>
+        <v>0.7921987284444449</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797730179451522</v>
+        <v>0.7977068520914365</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8029105303687545</v>
+        <v>0.8028798093918224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8055377826286679</v>
+        <v>0.8055077515295993</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8080556955649394</v>
+        <v>0.8080299972778958</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.810187415860916</v>
+        <v>0.8101674986892266</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8108688228056085</v>
+        <v>0.8104160293265845</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8113532712148475</v>
+        <v>0.8107331984580701</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8119818738918132</v>
+        <v>0.8112934617015694</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8126613995353399</v>
+        <v>0.811806901268784</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.815860271350497</v>
+        <v>0.8148145551859041</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8208996078818186</v>
+        <v>0.8195914236681003</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8250674810229692</v>
+        <v>0.8235784136601088</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8286368344199022</v>
+        <v>0.8269945056705879</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.83341025477918</v>
+        <v>0.831534560484506</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.837559940966679</v>
+        <v>0.8352649292116874</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8368180954850943</v>
+        <v>0.8340468006195758</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8334185911143979</v>
+        <v>0.8302438672578381</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8299916056725509</v>
+        <v>0.8254198863126514</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8127048932702852</v>
+        <v>0.8061071339875963</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886486369840211</v>
+        <v>0.7886473949758011</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919766792681967</v>
+        <v>0.7919742799030929</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913398631105625</v>
+        <v>0.7913374378138882</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927361800181523</v>
+        <v>0.7927323316837015</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914116140878227</v>
+        <v>0.791407652470991</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899596811720523</v>
+        <v>0.7899556585265344</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883819165564895</v>
+        <v>0.7883779136038772</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872984882780135</v>
+        <v>0.7872945590777499</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893156004360511</v>
+        <v>0.789310988580567</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945360876118731</v>
+        <v>0.7945339483153764</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969545818801009</v>
+        <v>0.7969523106329089</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993831571148609</v>
+        <v>0.7993808324693011</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001895705350179</v>
+        <v>0.800188479524552</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986556279398538</v>
+        <v>0.7986563900392888</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992435918149374</v>
+        <v>0.799245055251257</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039823139144766</v>
+        <v>0.803981596707754</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096659811446998</v>
+        <v>0.8096630054886963</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158524940396761</v>
+        <v>0.8158484337612157</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222334003379432</v>
+        <v>0.8222301691831847</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229511238660618</v>
+        <v>0.8229505006960939</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187331339856521</v>
+        <v>0.8187366119086164</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152586927182801</v>
+        <v>0.8152634684943362</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138365600009974</v>
+        <v>0.8138452958764706</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121384650209915</v>
+        <v>0.8121524446824315</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119467758214151</v>
+        <v>0.8119646182651918</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170992709038718</v>
+        <v>0.8171211584174061</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227608624416127</v>
+        <v>0.8227852563649222</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8296038943699364</v>
+        <v>0.8296309706042198</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8342417736937418</v>
+        <v>0.8342713579298313</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8193258388255515</v>
+        <v>0.8193600573117923</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8211497517932308</v>
+        <v>0.8211838477667392</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.80854608159279</v>
+        <v>0.808583415883642</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8004616800612466</v>
+        <v>0.8004968354646415</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7931849854420276</v>
+        <v>0.7932254420387359</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7835627358699866</v>
+        <v>0.7836059582953039</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684482553863107</v>
+        <v>0.7684650514405165</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662916500952588</v>
+        <v>0.7663030668471287</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583447983744347</v>
+        <v>0.7583445292725186</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479194219166746</v>
+        <v>0.7479019166832922</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7391529812304908</v>
+        <v>0.7391253070172448</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7297188351644871</v>
+        <v>0.7296799410818341</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7341582092087681</v>
+        <v>0.7340951427161695</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7396122682586534</v>
+        <v>0.7395452603974995</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7491022454070311</v>
+        <v>0.7490415582653154</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7578412570704994</v>
+        <v>0.7577827135647932</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7733840698517047</v>
+        <v>0.7733584503187322</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7775943680458649</v>
+        <v>0.77757777990293</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7781942666534788</v>
+        <v>0.7781741220147222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834659436493143</v>
+        <v>0.7834546194070069</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886065196572402</v>
+        <v>0.7886035897422476</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923315366520055</v>
+        <v>0.7923321842091531</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894828993196779</v>
+        <v>0.7894746988002956</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921987284444449</v>
+        <v>0.7921854637561774</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7977068520914365</v>
+        <v>0.7976840966234658</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8028798093918224</v>
+        <v>0.8028498219104857</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8055077515295993</v>
+        <v>0.8054784122975039</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8080299972778958</v>
+        <v>0.8080048479788478</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8101674986892266</v>
+        <v>0.8101479642757823</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8104160293265845</v>
+        <v>0.8099908008065781</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8107331984580701</v>
+        <v>0.8101777328446884</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8112934617015694</v>
+        <v>0.8107599291039369</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.811806901268784</v>
+        <v>0.8112309753046908</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8148145551859041</v>
+        <v>0.8141261419197023</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8195914236681003</v>
+        <v>0.8187513246672929</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8235784136601088</v>
+        <v>0.822640845785799</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8269945056705879</v>
+        <v>0.82597418204222</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.831534560484506</v>
+        <v>0.8303551773244452</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8352649292116874</v>
+        <v>0.8334109231974554</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8340468006195758</v>
+        <v>0.8318000343569911</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8302438672578381</v>
+        <v>0.8276956245111273</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8254198863126514</v>
+        <v>0.8219928986647278</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8061071339875963</v>
+        <v>0.8027592717052474</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886473949758011</v>
+        <v>0.7886461836297179</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919742799030929</v>
+        <v>0.7919719396405631</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913374378138882</v>
+        <v>0.7913350718135085</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927323316837015</v>
+        <v>0.7927285777848346</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791407652470991</v>
+        <v>0.7914037880991913</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899556585265344</v>
+        <v>0.7899517346668652</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883779136038772</v>
+        <v>0.7883740089765839</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872945590777499</v>
+        <v>0.7872907263911859</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789310988580567</v>
+        <v>0.7893064897276725</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945339483153764</v>
+        <v>0.7945318618090512</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969523106329089</v>
+        <v>0.7969500954893834</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993808324693011</v>
+        <v>0.7993785653012121</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800188479524552</v>
+        <v>0.800187414646429</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986563900392888</v>
+        <v>0.7986571323013048</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799245055251257</v>
+        <v>0.7992464822263955</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803981596707754</v>
+        <v>0.803980896314024</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096630054886963</v>
+        <v>0.8096601009114992</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158484337612157</v>
+        <v>0.8158444677131516</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222301691831847</v>
+        <v>0.8222270115040314</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229505006960939</v>
+        <v>0.822949886203422</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187366119086164</v>
+        <v>0.8187399955198678</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152634684943362</v>
+        <v>0.8152681176664029</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138452958764706</v>
+        <v>0.8138538081868469</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121524446824315</v>
+        <v>0.8121660705761611</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119646182651918</v>
+        <v>0.8119820126512322</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8171211584174061</v>
+        <v>0.8171424990438354</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227852563649222</v>
+        <v>0.8228090439244813</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8296309706042198</v>
+        <v>0.8296573765880004</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8342713579298313</v>
+        <v>0.8343002299004992</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8193600573117923</v>
+        <v>0.8193934388163138</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8211838477667392</v>
+        <v>0.821217111972132</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808583415883642</v>
+        <v>0.8086198356624419</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8004968354646415</v>
+        <v>0.8005311327014988</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7932254420387359</v>
+        <v>0.7932649165247575</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7836059582953039</v>
+        <v>0.7836481435621141</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684650514405165</v>
+        <v>0.7684814589755238</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663030668471287</v>
+        <v>0.7663142372965921</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583445292725186</v>
+        <v>0.7583443083605661</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479019166832922</v>
+        <v>0.7478848819327705</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7391253070172448</v>
+        <v>0.739098359287655</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7296799410818341</v>
+        <v>0.7296420400062922</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7340951427161695</v>
+        <v>0.7340336170323348</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7395452603974995</v>
+        <v>0.7394798768660219</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7490415582653154</v>
+        <v>0.748982320885097</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7577827135647932</v>
+        <v>0.7577255447326326</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7733584503187322</v>
+        <v>0.7733334293847857</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.77757777990293</v>
+        <v>0.7775615696895219</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7781741220147222</v>
+        <v>0.7781544412482696</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834546194070069</v>
+        <v>0.7834435588724592</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886035897422476</v>
+        <v>0.7886007409876064</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923321842091531</v>
+        <v>0.7923328441335731</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894746988002956</v>
+        <v>0.7894667151611603</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921854637561774</v>
+        <v>0.792172539941816</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7976840966234658</v>
+        <v>0.7976618924133125</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8028498219104857</v>
+        <v>0.802820542212678</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8054784122975039</v>
+        <v>0.805449741674759</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8080048479788478</v>
+        <v>0.8079802308609068</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8101479642757823</v>
+        <v>0.810128802543891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8099908008065781</v>
+        <v>0.8096845404840979</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8101777328446884</v>
+        <v>0.8097671199813384</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8107599291039369</v>
+        <v>0.8103824765867487</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8112309753046908</v>
+        <v>0.8108018087253031</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8141261419197023</v>
+        <v>0.8136266407395998</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8187513246672929</v>
+        <v>0.8181181235941308</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.822640845785799</v>
+        <v>0.8219190721849563</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.82597418204222</v>
+        <v>0.825177044716688</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8303551773244452</v>
+        <v>0.8294171850069827</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8334109231974554</v>
+        <v>0.8323931456331791</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8318000343569911</v>
+        <v>0.8300497443706569</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8276956245111273</v>
+        <v>0.825782651591477</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8219928986647278</v>
+        <v>0.8196459087929735</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8027592717052474</v>
+        <v>0.8015055054699857</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886461836297179</v>
+        <v>0.7886512177643419</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919719396405631</v>
+        <v>0.7919816644927713</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913350718135085</v>
+        <v>0.7913449007357447</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927285777848346</v>
+        <v>0.7927441746117592</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914037880991913</v>
+        <v>0.7914198441141894</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899517346668652</v>
+        <v>0.7899680381238123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883740089765839</v>
+        <v>0.7883902326733042</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872907263911859</v>
+        <v>0.7873066511745703</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893064897276725</v>
+        <v>0.789325180616548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945318618090512</v>
+        <v>0.794540532794813</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969500954893834</v>
+        <v>0.7969593014302596</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993785653012121</v>
+        <v>0.7993879878062762</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800187414646429</v>
+        <v>0.8001918348904484</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986571323013048</v>
+        <v>0.7986540409731649</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992464822263955</v>
+        <v>0.7992405498273573</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803980896314024</v>
+        <v>0.8039838012361127</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096601009114992</v>
+        <v>0.8096721563636399</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158444677131516</v>
+        <v>0.8158609109619187</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222270115040314</v>
+        <v>0.8222400934756033</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822949886203422</v>
+        <v>0.8229523964886012</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187399955198678</v>
+        <v>0.8187258791594516</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152681176664029</v>
+        <v>0.8152487402621857</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138538081868469</v>
+        <v>0.813818381529517</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121660705761611</v>
+        <v>0.8121093880202626</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119820126512322</v>
+        <v>0.8119096759337836</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8171424990438354</v>
+        <v>0.8170537692292212</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8228090439244813</v>
+        <v>0.8227101607103866</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8296573765880004</v>
+        <v>0.8295476268483777</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8343002299004992</v>
+        <v>0.8341803605615217</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8193934388163138</v>
+        <v>0.8192547619660271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.821217111972132</v>
+        <v>0.8210789367728639</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8086198356624419</v>
+        <v>0.8084685284525384</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8005311327014988</v>
+        <v>0.8003886629352281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7932649165247575</v>
+        <v>0.793100976028067</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7836481435621141</v>
+        <v>0.7834730233597277</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684814589755238</v>
+        <v>0.7684134416701236</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663142372965921</v>
+        <v>0.7662680452817342</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583443083605661</v>
+        <v>0.7583454954454305</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478848819327705</v>
+        <v>0.7479559231729305</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739098359287655</v>
+        <v>0.7392106289561248</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7296420400062922</v>
+        <v>0.7297997619685637</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7340336170323348</v>
+        <v>0.7342892014246958</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7394798768660219</v>
+        <v>0.739751404402997</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748982320885097</v>
+        <v>0.7492281863362147</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7577255447326326</v>
+        <v>0.7579626703332327</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7733334293847857</v>
+        <v>0.7734371923230609</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7775615696895219</v>
+        <v>0.777628731837954</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7781544412482696</v>
+        <v>0.7782360143491602</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834435588724592</v>
+        <v>0.7834894218110197</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886007409876064</v>
+        <v>0.7886126370942049</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923328441335731</v>
+        <v>0.7923302851296403</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894667151611603</v>
+        <v>0.7894999870695933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792172539941816</v>
+        <v>0.7922263355244179</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7976618924133125</v>
+        <v>0.7977541003726651</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802820542212678</v>
+        <v>0.8014321583804933</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.805449741674759</v>
+        <v>0.8048310020464339</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8079802308609068</v>
+        <v>0.8074860335644508</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.810128802543891</v>
+        <v>0.8096158467401644</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096845404840979</v>
+        <v>0.8098049877820556</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8097671199813384</v>
+        <v>0.809967212764352</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8103824765867487</v>
+        <v>0.8101105089484939</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8108018087253031</v>
+        <v>0.8100574298584027</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8136266407395998</v>
+        <v>0.81321261462614</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8181181235941308</v>
+        <v>0.81817839506714</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8219190721849563</v>
+        <v>0.8224574637955123</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.825177044716688</v>
+        <v>0.8256046108175693</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8294171850069827</v>
+        <v>0.8295087282557294</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8323931456331791</v>
+        <v>0.8335265454887227</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8300497443706569</v>
+        <v>0.8308853517423841</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.825782651591477</v>
+        <v>0.8249248068011961</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8196459087929735</v>
+        <v>0.8203651390450041</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,15 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8015055054699857</v>
+        <v>0.8106516128912777</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B79">
+        <v>0.8173897754954803</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886512177643419</v>
+        <v>0.7886450018242128</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919816644927713</v>
+        <v>0.7919696563236264</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913449007357447</v>
+        <v>0.7913327629616344</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927441746117592</v>
+        <v>0.7927249148884316</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914198441141894</v>
+        <v>0.7914000174361158</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899680381238123</v>
+        <v>0.7899479059991635</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883902326733042</v>
+        <v>0.7883701990966456</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873066511745703</v>
+        <v>0.7872869867062791</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789325180616548</v>
+        <v>0.7893020997758947</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794540532794813</v>
+        <v>0.7945298261631956</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969593014302596</v>
+        <v>0.7969479343966214</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993879878062762</v>
+        <v>0.7993763535054419</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001918348904484</v>
+        <v>0.8001863749743318</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986540409731649</v>
+        <v>0.7986578554878622</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992405498273573</v>
+        <v>0.7992478740851907</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039838012361127</v>
+        <v>0.8039802121514075</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096721563636399</v>
+        <v>0.8096572649021336</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158609109619187</v>
+        <v>0.8158405926706234</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222400934756033</v>
+        <v>0.822223924843493</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229523964886012</v>
+        <v>0.8229492803134129</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187258791594516</v>
+        <v>0.8187432885673231</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152487402621857</v>
+        <v>0.8152726451673327</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813818381529517</v>
+        <v>0.8138621053737501</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121093880202626</v>
+        <v>0.8121793559209518</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119096759337836</v>
+        <v>0.8119989755953554</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170537692292212</v>
+        <v>0.8171633129621423</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227101607103866</v>
+        <v>0.8228322473742699</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8295476268483777</v>
+        <v>0.8296831368145871</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8341803605615217</v>
+        <v>0.8343284149743047</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8192547619660271</v>
+        <v>0.819426013633056</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8210789367728639</v>
+        <v>0.8212495744331754</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8084685284525384</v>
+        <v>0.8086553740604474</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8003886629352281</v>
+        <v>0.8005646027487641</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793100976028067</v>
+        <v>0.7933034441380421</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7834730233597277</v>
+        <v>0.7836893284203492</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684134416701236</v>
+        <v>0.7684974912163789</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662680452817342</v>
+        <v>0.7663251691376549</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583454954454305</v>
+        <v>0.7583441323787012</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479559231729305</v>
+        <v>0.7478682991218686</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7392106289561248</v>
+        <v>0.739072109995224</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7297997619685637</v>
+        <v>0.7296050945295245</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7342892014246958</v>
+        <v>0.7339735765100646</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.739751404402997</v>
+        <v>0.7394160594861878</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7492281863362147</v>
+        <v>0.7489244821092106</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7579626703332327</v>
+        <v>0.7576697029227011</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734371923230609</v>
+        <v>0.7733089864007794</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.777628731837954</v>
+        <v>0.7775457247213018</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7782360143491602</v>
+        <v>0.7781352085938841</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834894218110197</v>
+        <v>0.7834327529594668</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7886126370942049</v>
+        <v>0.788597970098635</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923302851296403</v>
+        <v>0.7923335149655883</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894999870695933</v>
+        <v>0.7894589399657095</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922263355244179</v>
+        <v>0.7921599440954187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7977541003726651</v>
+        <v>0.7976402198007488</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8014321583804933</v>
+        <v>0.8027919457622847</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048310020464339</v>
+        <v>0.8054217174157303</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074860335644508</v>
+        <v>0.8079561297651325</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096158467401644</v>
+        <v>0.8101100037204638</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8098049877820556</v>
+        <v>0.8096808057849811</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.809967212764352</v>
+        <v>0.8095123330549274</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8101105089484939</v>
+        <v>0.8100803156859697</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8100574298584027</v>
+        <v>0.8105162807030938</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.81321261462614</v>
+        <v>0.8132633758325415</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.81817839506714</v>
+        <v>0.8176550959209825</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8224574637955123</v>
+        <v>0.8214218989302196</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8256046108175693</v>
+        <v>0.8246504665617352</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8295087282557294</v>
+        <v>0.8287816148618813</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8335265454887227</v>
+        <v>0.8315645237354106</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8308853517423841</v>
+        <v>0.829226679941345</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8249248068011961</v>
+        <v>0.8248568492318007</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8203651390450041</v>
+        <v>0.8185515987897725</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8106516128912777</v>
+        <v>0.8018078522658553</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8173897754954803</v>
+        <v>0.8013668842173487</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886450018242128</v>
+        <v>0.7886499108334373</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919696563236264</v>
+        <v>0.7919791400031709</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913327629616344</v>
+        <v>0.79134234996028</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927249148884316</v>
+        <v>0.7927401263961473</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7914000174361158</v>
+        <v>0.791415676666146</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899479059991635</v>
+        <v>0.789963806380467</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883701990966456</v>
+        <v>0.788386021594786</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872869867062791</v>
+        <v>0.7873025176830608</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893020997758947</v>
+        <v>0.7893203296040887</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945298261631956</v>
+        <v>0.7945382817270867</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969479343966214</v>
+        <v>0.7969569113891289</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993763535054419</v>
+        <v>0.7993855414510942</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001863749743318</v>
+        <v>0.8001906886500108</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986578554878622</v>
+        <v>0.7986548452000523</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992478740851907</v>
+        <v>0.7992420905030988</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039802121514075</v>
+        <v>0.8039830485440712</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096572649021336</v>
+        <v>0.8096690305142678</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158405926706234</v>
+        <v>0.8158566519265071</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822223924843493</v>
+        <v>0.8222367075386665</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229492803134129</v>
+        <v>0.822951755778689</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187432885673231</v>
+        <v>0.8187295577952627</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152726451673327</v>
+        <v>0.8152537851369409</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138621053737501</v>
+        <v>0.8138275916729965</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121793559209518</v>
+        <v>0.8121241176822588</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119989755953554</v>
+        <v>0.8119284678426391</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8171633129621423</v>
+        <v>0.8170768152837252</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8228322473742699</v>
+        <v>0.8227358387598378</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8296831368145871</v>
+        <v>0.8295761221422695</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8343284149743047</v>
+        <v>0.8342114505616205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.819426013633056</v>
+        <v>0.8192907515300514</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8212495744331754</v>
+        <v>0.8211147925123856</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8086553740604474</v>
+        <v>0.808507797980627</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8005646027487641</v>
+        <v>0.8004256339519049</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7933034441380421</v>
+        <v>0.793143509731655</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7836893284203492</v>
+        <v>0.7835184377219189</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7684974912163789</v>
+        <v>0.76843105696519</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663251691376549</v>
+        <v>0.7662799790248824</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583441323787012</v>
+        <v>0.7583451191734898</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478682991218686</v>
+        <v>0.7479374171956508</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739072109995224</v>
+        <v>0.7391814114857999</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7296050945295245</v>
+        <v>0.7297587616332069</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7339735765100646</v>
+        <v>0.7342228749647033</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7394160594861878</v>
+        <v>0.7396809615350416</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7489244821092106</v>
+        <v>0.7491644359827656</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7576697029227011</v>
+        <v>0.7579012251982891</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7733089864007794</v>
+        <v>0.7734103096232352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7775457247213018</v>
+        <v>0.7776113473918695</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7781352085938841</v>
+        <v>0.778214891668032</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834327529594668</v>
+        <v>0.7834775411220911</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788597970098635</v>
+        <v>0.788609534214043</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923335149655883</v>
+        <v>0.7923309030497477</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894589399657095</v>
+        <v>0.7894913256144225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921599440954187</v>
+        <v>0.7922123475950541</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7976402198007488</v>
+        <v>0.797730179451522</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8027919457622847</v>
+        <v>0.8014032796225995</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8054217174157303</v>
+        <v>0.8048015296090585</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8079561297651325</v>
+        <v>0.8074596859191696</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8101100037204638</v>
+        <v>0.8095942175358342</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096808057849811</v>
+        <v>0.8097976172470909</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8095123330549274</v>
+        <v>0.8097273372788616</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8100803156859697</v>
+        <v>0.8098452953292482</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105162807030938</v>
+        <v>0.8098537180710789</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8132633758325415</v>
+        <v>0.8129774636750822</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8176550959209825</v>
+        <v>0.8178222109519212</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8214218989302196</v>
+        <v>0.8220607306943283</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8246504665617352</v>
+        <v>0.8252296105865532</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8287816148618813</v>
+        <v>0.8291150987671252</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8315645237354106</v>
+        <v>0.8330191580212198</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.829226679941345</v>
+        <v>0.8307770211580666</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8248568492318007</v>
+        <v>0.8252310329643606</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8185515987897725</v>
+        <v>0.8212920485641795</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8018078522658553</v>
+        <v>0.8137354946397179</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8013668842173487</v>
+        <v>0.818450167913453</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886499108334373</v>
+        <v>0.7886438484917643</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919791400031709</v>
+        <v>0.791967427898991</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.79134234996028</v>
+        <v>0.7913305092129406</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927401263961473</v>
+        <v>0.792721339725752</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791415676666146</v>
+        <v>0.7913963371148259</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789963806380467</v>
+        <v>0.7899441691017486</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788386021594786</v>
+        <v>0.7883664805575759</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7873025176830608</v>
+        <v>0.7872833366793048</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7893203296040887</v>
+        <v>0.789297814819802</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945382817270867</v>
+        <v>0.7945278395410038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969569113891289</v>
+        <v>0.7969458254006454</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993855414510942</v>
+        <v>0.7993741950783768</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001906886500108</v>
+        <v>0.8001853596251405</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986548452000523</v>
+        <v>0.79865856032251</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992420905030988</v>
+        <v>0.7992492321071939</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039830485440712</v>
+        <v>0.803979543664446</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096690305142678</v>
+        <v>0.8096544950662403</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158566519265071</v>
+        <v>0.8158368055533708</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222367075386665</v>
+        <v>0.8222209068518421</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822951755778689</v>
+        <v>0.8229486829434611</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187295577952627</v>
+        <v>0.8187464946044796</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152537851369409</v>
+        <v>0.8152770556785424</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138275916729965</v>
+        <v>0.813870195460517</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121241176822588</v>
+        <v>0.8121923132870064</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8119284678426391</v>
+        <v>0.8120155229042175</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8170768152837252</v>
+        <v>0.8171836193736031</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8227358387598378</v>
+        <v>0.8228548878959996</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8295761221422695</v>
+        <v>0.8297082746023657</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8342114505616205</v>
+        <v>0.8343559373314948</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8192907515300514</v>
+        <v>0.8194578106134959</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8211147925123856</v>
+        <v>0.821281263747983</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808507797980627</v>
+        <v>0.8086900626306293</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8004256339519049</v>
+        <v>0.8005972751133846</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793143509731655</v>
+        <v>0.7933410584552156</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7835184377219189</v>
+        <v>0.7837295479106458</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.76843105696519</v>
+        <v>0.7685131607997155</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7662799790248824</v>
+        <v>0.7663358697574649</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583451191734898</v>
+        <v>0.7583439982949598</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7479374171956508</v>
+        <v>0.7478521506617204</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7391814114857999</v>
+        <v>0.739046532510423</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7297587616332069</v>
+        <v>0.7295690690924665</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7342228749647033</v>
+        <v>0.7339149681434166</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7396809615350416</v>
+        <v>0.7393537528170816</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7491644359827656</v>
+        <v>0.7488679931507682</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7579012251982891</v>
+        <v>0.7576151426509913</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7734103096232352</v>
+        <v>0.7732851016523286</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7776113473918695</v>
+        <v>0.77753023287108</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778214891668032</v>
+        <v>0.7781164089934598</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834775411220911</v>
+        <v>0.7834221929936535</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788609534214043</v>
+        <v>0.7885952739551605</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923309030497477</v>
+        <v>0.7923341953628235</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894913256144225</v>
+        <v>0.7894513652069087</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7922123475950541</v>
+        <v>0.7921476639514078</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797730179451522</v>
+        <v>0.7976190600432145</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8014032796225995</v>
+        <v>0.8027640091333896</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048015296090585</v>
+        <v>0.8053943182335006</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074596859191696</v>
+        <v>0.8079325291516708</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095942175358342</v>
+        <v>0.8100915583281252</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8097976172470909</v>
+        <v>0.8096770459645236</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8097273372788616</v>
+        <v>0.8093130008712857</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8098452953292482</v>
+        <v>0.8098478709235609</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8098537180710789</v>
+        <v>0.8103075616342198</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8129774636750822</v>
+        <v>0.8130249067878141</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8178222109519212</v>
+        <v>0.8173175201372909</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8220607306943283</v>
+        <v>0.8210489698186917</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8252296105865532</v>
+        <v>0.8242520457398838</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8291150987671252</v>
+        <v>0.8282932315805247</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8330191580212198</v>
+        <v>0.8309361760807049</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8307770211580666</v>
+        <v>0.8286977060023742</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8252310329643606</v>
+        <v>0.8243447901368206</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8212920485641795</v>
+        <v>0.8181301244288282</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8137354946397179</v>
+        <v>0.8030151983808423</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.818450167913453</v>
+        <v>0.8054992612438227</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886438484917643</v>
+        <v>0.7886427226156734</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791967427898991</v>
+        <v>0.7919652524108967</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913305092129406</v>
+        <v>0.7913283086185287</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.792721339725752</v>
+        <v>0.7927178491827147</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913963371148259</v>
+        <v>0.7913927439277348</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899441691017486</v>
+        <v>0.7899405207149501</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883664805575759</v>
+        <v>0.788362850114217</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872833366793048</v>
+        <v>0.7872797731248954</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789297814819802</v>
+        <v>0.7892936311384321</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945278395410038</v>
+        <v>0.7945259001930437</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969458254006454</v>
+        <v>0.7969437666405188</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993741950783768</v>
+        <v>0.7993720881118948</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001853596251405</v>
+        <v>0.8001843677564484</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.79865856032251</v>
+        <v>0.7986592474927698</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992492321071939</v>
+        <v>0.7992505575105818</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803979543664446</v>
+        <v>0.8039788903226273</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096544950662403</v>
+        <v>0.8096517891194016</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158368055533708</v>
+        <v>0.815833103417773</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222209068518421</v>
+        <v>0.8222179552808921</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229486829434611</v>
+        <v>0.8229480940041443</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187464946044796</v>
+        <v>0.8187496170027762</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152770556785424</v>
+        <v>0.8152813536457482</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813870195460517</v>
+        <v>0.8138780860777091</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8121923132870064</v>
+        <v>0.8122049546351481</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120155229042175</v>
+        <v>0.8120316696238411</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8171836193736031</v>
+        <v>0.8172034365601237</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8228548878959996</v>
+        <v>0.8228769856627254</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8297082746023657</v>
+        <v>0.829732812164176</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8343559373314948</v>
+        <v>0.8343828200326467</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8194578106134959</v>
+        <v>0.8194888572513719</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.821281263747983</v>
+        <v>0.8213122071725167</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8086900626306293</v>
+        <v>0.8087239314403726</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8005972751133846</v>
+        <v>0.8006291779182995</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7933410584552156</v>
+        <v>0.7933777914880799</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7837295479106458</v>
+        <v>0.7837688354621839</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685131607997155</v>
+        <v>0.7685284798058033</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663358697574649</v>
+        <v>0.7663463462507581</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583439982949598</v>
+        <v>0.7583439032875994</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478521506617204</v>
+        <v>0.7478364198576172</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.739046532510423</v>
+        <v>0.7390216015327824</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7295690690924665</v>
+        <v>0.7295339298728092</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7339149681434166</v>
+        <v>0.7338577414132172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7393537528170816</v>
+        <v>0.7392929039963041</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7488679931507682</v>
+        <v>0.7488128074579639</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7576151426509913</v>
+        <v>0.757561820479562</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7732851016523286</v>
+        <v>0.7732617563077074</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.77753023287108</v>
+        <v>0.7775150825388146</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7781164089934598</v>
+        <v>0.778098028052578</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834221929936535</v>
+        <v>0.7834118706894491</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885952739551605</v>
+        <v>0.7885926496001965</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923341953628235</v>
+        <v>0.7923348840905298</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894513652069087</v>
+        <v>0.7894439832803957</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921476639514078</v>
+        <v>0.792135687845509</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7976190600432145</v>
+        <v>0.7975983952632603</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8027640091333896</v>
+        <v>0.8027367099488318</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8053943182335006</v>
+        <v>0.8053675237498397</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8079325291516708</v>
+        <v>0.8079094140722507</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100915583281252</v>
+        <v>0.8100734571772201</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096770459645236</v>
+        <v>0.8096732655895564</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8093130008712857</v>
+        <v>0.8091661895637087</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8098478709235609</v>
+        <v>0.8096783002401826</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8103075616342198</v>
+        <v>0.8101624605927233</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8130249067878141</v>
+        <v>0.8128559416263459</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8173175201372909</v>
+        <v>0.8170654957847406</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8210489698186917</v>
+        <v>0.8207715403872918</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8242520457398838</v>
+        <v>0.8239586230108739</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8282932315805247</v>
+        <v>0.8279235200483647</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8309361760807049</v>
+        <v>0.8304522318751496</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8286977060023742</v>
+        <v>0.8283262521473851</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8243447901368206</v>
+        <v>0.8239972626664077</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8181301244288282</v>
+        <v>0.8178919806653698</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8030151983808423</v>
+        <v>0.8041147367462115</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8054992612438227</v>
+        <v>0.8072686934229736</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886427226156734</v>
+        <v>0.7886416232270743</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919652524108967</v>
+        <v>0.7919631279953929</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913283086185287</v>
+        <v>0.7913261593203127</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927178491827147</v>
+        <v>0.7927144402908606</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913927439277348</v>
+        <v>0.7913892348172927</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899405207149501</v>
+        <v>0.7899369577316342</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788362850114217</v>
+        <v>0.7883593046733024</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872797731248954</v>
+        <v>0.787276293006776</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892936311384321</v>
+        <v>0.7892895451845319</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945259001930437</v>
+        <v>0.7945240064521245</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969437666405188</v>
+        <v>0.7969417563428722</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993720881118948</v>
+        <v>0.7993700307877432</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001843677564484</v>
+        <v>0.8001833985642458</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986592474927698</v>
+        <v>0.7986599176523427</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992505575105818</v>
+        <v>0.7992518514557899</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039788903226273</v>
+        <v>0.8039782516190056</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096517891194016</v>
+        <v>0.8096491448809175</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815833103417773</v>
+        <v>0.8158294834494062</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222179552808921</v>
+        <v>0.822215067978634</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229480940041443</v>
+        <v>0.8229475134002487</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187496170027762</v>
+        <v>0.8187526589630298</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152813536457482</v>
+        <v>0.8152855432935397</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138780860777091</v>
+        <v>0.8138857844867855</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122049546351481</v>
+        <v>0.8122172913532081</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120316696238411</v>
+        <v>0.8120474300847023</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172034365601237</v>
+        <v>0.8172227819384623</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8228769856627254</v>
+        <v>0.8228985598979931</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.829732812164176</v>
+        <v>0.8297567706718473</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8343828200326467</v>
+        <v>0.8344090850826088</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8194888572513719</v>
+        <v>0.8195191797615144</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8213122071725167</v>
+        <v>0.8213424306982948</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8087239314403726</v>
+        <v>0.8087570091577321</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8006291779182995</v>
+        <v>0.8006603379824763</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7933777914880799</v>
+        <v>0.7934136737734794</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7837688354621839</v>
+        <v>0.7838072229839098</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685284798058033</v>
+        <v>0.7685434597885445</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663463462507581</v>
+        <v>0.7663566054335547</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583439032875994</v>
+        <v>0.7583438447289415</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478364198576172</v>
+        <v>0.7478210908532656</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7390216015327824</v>
+        <v>0.738997293009416</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7295339298728092</v>
+        <v>0.7294996446805742</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7338577414132172</v>
+        <v>0.7338018481432649</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7392929039963041</v>
+        <v>0.7392334625922398</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7488128074579639</v>
+        <v>0.7487588805879937</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.757561820479562</v>
+        <v>0.757509694903304</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7732617563077074</v>
+        <v>0.7732389323692269</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7775150825388146</v>
+        <v>0.777500262623508</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778098028052578</v>
+        <v>0.7780800520045462</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834118706894491</v>
+        <v>0.7834017781285894</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885926496001965</v>
+        <v>0.7885900942294874</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923348840905298</v>
+        <v>0.7923355800127739</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894439832803957</v>
+        <v>0.7894367869596042</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792135687845509</v>
+        <v>0.7921240046785072</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7975983952632603</v>
+        <v>0.7975782083995364</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8027367099488318</v>
+        <v>0.8027100268227544</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8053675237498397</v>
+        <v>0.805341314448194</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8079094140722507</v>
+        <v>0.8078867701439855</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100734571772201</v>
+        <v>0.8100556913577759</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096732655895564</v>
+        <v>0.8096694688627863</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8091661895637087</v>
+        <v>0.808986176641497</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096783002401826</v>
+        <v>0.8094714942506567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8101624605927233</v>
+        <v>0.8099785693081252</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8128559416263459</v>
+        <v>0.8126474007646063</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8170654957847406</v>
+        <v>0.8167668704984634</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8207715403872918</v>
+        <v>0.8204411343993108</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8239586230108739</v>
+        <v>0.8236059231711848</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8279235200483647</v>
+        <v>0.8274937101121219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8304522318751496</v>
+        <v>0.8299108459312449</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8283262521473851</v>
+        <v>0.8278921552294749</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8239972626664077</v>
+        <v>0.8235997293885178</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8178919806653698</v>
+        <v>0.8176095365429867</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8041147367462115</v>
+        <v>0.8049249158849957</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8072686934229736</v>
+        <v>0.8080738138291991</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886416232270743</v>
+        <v>0.7886405494021541</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919631279953929</v>
+        <v>0.7919610528750149</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913261593203127</v>
+        <v>0.7913240595457909</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927144402908606</v>
+        <v>0.7927111102189399</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913892348172927</v>
+        <v>0.7913858068673174</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899369577316342</v>
+        <v>0.7899334771883864</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883593046733024</v>
+        <v>0.7883558412846763</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.787276293006776</v>
+        <v>0.7872728934291457</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892895451845319</v>
+        <v>0.789285553574541</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945240064521245</v>
+        <v>0.7945221567285209</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969417563428722</v>
+        <v>0.7969397928168166</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993700307877432</v>
+        <v>0.7993680213723127</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001833985642458</v>
+        <v>0.8001824512807616</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986599176523427</v>
+        <v>0.7986605714231607</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992518514557899</v>
+        <v>0.7992531150488911</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039782516190056</v>
+        <v>0.8039776270689158</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096491448809175</v>
+        <v>0.8096465602679986</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158294834494062</v>
+        <v>0.8158259429560766</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822215067978634</v>
+        <v>0.8222122428842021</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229475134002487</v>
+        <v>0.8229469410316815</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187526589630298</v>
+        <v>0.8187556235260238</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152855432935397</v>
+        <v>0.8152896286388899</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138857844867855</v>
+        <v>0.8138932976020877</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122172913532081</v>
+        <v>0.8122293342898422</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120474300847023</v>
+        <v>0.8120628179436543</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172227819384623</v>
+        <v>0.8172416721106642</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8228985598979931</v>
+        <v>0.8229196289308862</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8297567706718473</v>
+        <v>0.82978017031628</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8344090850826088</v>
+        <v>0.8344347534901246</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8195191797615144</v>
+        <v>0.8195488031532544</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8213424306982948</v>
+        <v>0.8213719591247719</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8087570091577321</v>
+        <v>0.8087893231317568</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8006603379824763</v>
+        <v>0.8006907808954684</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7934136737734794</v>
+        <v>0.7934487344570652</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7838072229839098</v>
+        <v>0.7838447409496552</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685434597885445</v>
+        <v>0.7685581118035762</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663566054335547</v>
+        <v>0.7663666538561442</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583438447289415</v>
+        <v>0.7583438201705981</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478210908532656</v>
+        <v>0.7478061485791432</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738997293009416</v>
+        <v>0.7389735840594404</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7294996446805742</v>
+        <v>0.7294661828611122</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7338018481432649</v>
+        <v>0.7337472423663723</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7392334625922398</v>
+        <v>0.739175380466333</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7487588805879937</v>
+        <v>0.7487061700893809</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.757509694903304</v>
+        <v>0.7574587262441032</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7732389323692269</v>
+        <v>0.7732166126277754</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.777500262623508</v>
+        <v>0.7774857624968636</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7780800520045462</v>
+        <v>0.7780624676767366</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7834017781285894</v>
+        <v>0.7833919077400239</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885900942294874</v>
+        <v>0.788587605181839</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923355800127739</v>
+        <v>0.7923362820844091</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894367869596042</v>
+        <v>0.7894297693727007</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921240046785072</v>
+        <v>0.7921126038825772</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7975782083995364</v>
+        <v>0.797558483161054</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8027100268227544</v>
+        <v>0.802683939306847</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.805341314448194</v>
+        <v>0.8053156716294976</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078867701439855</v>
+        <v>0.8078645835244189</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100556913577759</v>
+        <v>0.8100382522314649</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096694688627863</v>
+        <v>0.8096656596511724</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.808986176641497</v>
+        <v>0.8088158596137187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094714942506567</v>
+        <v>0.80926887259235</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099785693081252</v>
+        <v>0.8097706288233487</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8126474007646063</v>
+        <v>0.8123818676851834</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8167668704984634</v>
+        <v>0.8164177854029149</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8204411343993108</v>
+        <v>0.8200779340870477</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8236059231711848</v>
+        <v>0.8232553937559893</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8274937101121219</v>
+        <v>0.8271177762172583</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8299108459312449</v>
+        <v>0.8294960862112493</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8278921552294749</v>
+        <v>0.8277036906009254</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8235997293885178</v>
+        <v>0.8236186381527449</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8176095365429867</v>
+        <v>0.8181366772313281</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8049249158849957</v>
+        <v>0.8072820176168962</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8080738138291991</v>
+        <v>0.8105290019867682</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886405494021541</v>
+        <v>0.7886395002595646</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919610528750149</v>
+        <v>0.7919590253538251</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913240595457909</v>
+        <v>0.7913220076031766</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927111102189399</v>
+        <v>0.7927078562650774</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913858068673174</v>
+        <v>0.7913824572949195</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899334771883864</v>
+        <v>0.7899300762572983</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883558412846763</v>
+        <v>0.7883524571331126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872728934291457</v>
+        <v>0.7872695716286475</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789285553574541</v>
+        <v>0.7892816530792613</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945221567285209</v>
+        <v>0.7945203495055266</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969397928168166</v>
+        <v>0.7969378744492015</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993680213723127</v>
+        <v>0.7993660582117675</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001824512807616</v>
+        <v>0.800181525172446</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986605714231607</v>
+        <v>0.7986612093972874</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992531150488911</v>
+        <v>0.7992543493447408</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039776270689158</v>
+        <v>0.8039770162087673</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096465602679986</v>
+        <v>0.8096440332903461</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158259429560766</v>
+        <v>0.8158224793612995</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222122428842021</v>
+        <v>0.8222094780231519</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229469410316815</v>
+        <v>0.8229463767942784</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187556235260238</v>
+        <v>0.8187585135823245</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152896286388899</v>
+        <v>0.8152936135036919</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8138932976020877</v>
+        <v>0.8139006320112769</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122293342898422</v>
+        <v>0.8122410937859889</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120628179436543</v>
+        <v>0.8120778462229493</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172416721106642</v>
+        <v>0.8172601229110241</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8229196289308862</v>
+        <v>0.8229402102472988</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.82978017031628</v>
+        <v>0.8298030303634278</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8344347534901246</v>
+        <v>0.8344598453234646</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8195488031532544</v>
+        <v>0.8195777512988394</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8213719591247719</v>
+        <v>0.8214008161268095</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8087893231317568</v>
+        <v>0.8088208994673565</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8006907808954684</v>
+        <v>0.800720531086925</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7934487344570652</v>
+        <v>0.7934830013714268</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7838447409496552</v>
+        <v>0.7838814184776238</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685581118035762</v>
+        <v>0.7685724464346065</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663666538561442</v>
+        <v>0.7663764978153971</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583438201705981</v>
+        <v>0.758343827329955</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7478061485791432</v>
+        <v>0.7477915787046017</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7389735840594404</v>
+        <v>0.7389504529037978</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7294661828611122</v>
+        <v>0.7294335152049187</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7337472423663723</v>
+        <v>0.7336938801994766</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.739175380466333</v>
+        <v>0.7391186116445978</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7487061700893809</v>
+        <v>0.748654635392065</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7574587262441032</v>
+        <v>0.7574088765518515</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7732166126277754</v>
+        <v>0.7731947806202879</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774857624968636</v>
+        <v>0.7774715719785829</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7780624676767366</v>
+        <v>0.778045262459054</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833919077400239</v>
+        <v>0.7833822522811276</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788587605181839</v>
+        <v>0.788585179930173</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923362820844091</v>
+        <v>0.7923369893437492</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894297693727007</v>
+        <v>0.7894229239811863</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921126038825772</v>
+        <v>0.7921014753899893</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797558483161054</v>
+        <v>0.7975392039844651</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802683939306847</v>
+        <v>0.8026584278400123</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8053156716294976</v>
+        <v>0.8052905773706085</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078645835244189</v>
+        <v>0.8078428408877631</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100382522314649</v>
+        <v>0.8100211314236097</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096656596511724</v>
+        <v>0.8096618415119514</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088158596137187</v>
+        <v>0.8088302467247386</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.80926887259235</v>
+        <v>0.8092948779404862</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8097706288233487</v>
+        <v>0.8098131746914454</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123818676851834</v>
+        <v>0.8123913785414381</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8164177854029149</v>
+        <v>0.8163779794028551</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8200779340870477</v>
+        <v>0.8200356100564121</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8232553937559893</v>
+        <v>0.8232357198648612</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8271177762172583</v>
+        <v>0.8270908885801076</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8294960862112493</v>
+        <v>0.8294800607993658</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8277036906009254</v>
+        <v>0.8279666777464643</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8236186381527449</v>
+        <v>0.824133243497469</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8181366772313281</v>
+        <v>0.8192330256518302</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8072820176168962</v>
+        <v>0.8101352908797863</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8105290019867682</v>
+        <v>0.8163366765283476</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886395002595646</v>
+        <v>0.7886384749580106</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919590253538251</v>
+        <v>0.7919570438127925</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913220076031766</v>
+        <v>0.7913200018768558</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927078562650774</v>
+        <v>0.7927046758494678</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913824572949195</v>
+        <v>0.7913791834429735</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899300762572983</v>
+        <v>0.789926752238312</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883524571331126</v>
+        <v>0.78834914953069</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872695716286475</v>
+        <v>0.7872663249668841</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892816530792613</v>
+        <v>0.7892778406151553</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945203495055266</v>
+        <v>0.7945185833353103</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969378744492015</v>
+        <v>0.7969359997002019</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993660582117675</v>
+        <v>0.7993641397275123</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800181525172446</v>
+        <v>0.8001806195380889</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986612093972874</v>
+        <v>0.7986618321386849</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992543493447408</v>
+        <v>0.7992555553499057</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039770162087673</v>
+        <v>0.8039764185949162</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096440332903461</v>
+        <v>0.809641562045085</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158224793612995</v>
+        <v>0.8158190901981847</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222094780231519</v>
+        <v>0.8222067715030221</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229463767942784</v>
+        <v>0.8229458205805233</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187585135823245</v>
+        <v>0.8187613318813838</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152936135036919</v>
+        <v>0.8152975015264006</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139006320112769</v>
+        <v>0.8139077939943472</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122410937859889</v>
+        <v>0.8122525797041518</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120778462229493</v>
+        <v>0.8120925273465811</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172601229110241</v>
+        <v>0.8172781494498403</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8229402102472988</v>
+        <v>0.8229603205377316</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8298030303634278</v>
+        <v>0.8298253692064982</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8344598453234646</v>
+        <v>0.834484379762378</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8195777512988394</v>
+        <v>0.8196060469972485</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8214008161268095</v>
+        <v>0.8214290243176219</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8088208994673565</v>
+        <v>0.8088517630951318</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800720531086925</v>
+        <v>0.800749611891448</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7934830013714268</v>
+        <v>0.793516501109031</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7838814184776238</v>
+        <v>0.7839172834046745</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685724464346065</v>
+        <v>0.7685864738181165</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663764978153971</v>
+        <v>0.7663861433664384</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758343827329955</v>
+        <v>0.758343864077788</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477915787046017</v>
+        <v>0.7477773675934092</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7389504529037978</v>
+        <v>0.7389278788000397</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7294335152049187</v>
+        <v>0.7294016138637135</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7336938801994766</v>
+        <v>0.7336417197271053</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7391186116445978</v>
+        <v>0.7390631121976436</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748654635392065</v>
+        <v>0.7486042377046642</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7574088765518515</v>
+        <v>0.7573601095117937</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731947806202879</v>
+        <v>0.7731734205899232</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774715719785829</v>
+        <v>0.7774576813131802</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.778045262459054</v>
+        <v>0.7780284242743801</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833822522811276</v>
+        <v>0.7833728048201167</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788585179930173</v>
+        <v>0.7885828160732378</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923369893437492</v>
+        <v>0.7923377009058834</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894229239811863</v>
+        <v>0.7894162445600188</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7921014753899893</v>
+        <v>0.7920906096039891</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7975392039844651</v>
+        <v>0.7975203559941382</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8026584278400123</v>
+        <v>0.8026334737012073</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052905773706085</v>
+        <v>0.8052660144851997</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078428408877631</v>
+        <v>0.8078215294022708</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100211314236097</v>
+        <v>0.8100043208152582</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096618415119514</v>
+        <v>0.8096580177165265</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088302467247386</v>
+        <v>0.8088381676242653</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8092948779404862</v>
+        <v>0.8093385710762391</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8098131746914454</v>
+        <v>0.8098509355464621</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123913785414381</v>
+        <v>0.8123933077453058</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8163779794028551</v>
+        <v>0.8163766216991143</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8200356100564121</v>
+        <v>0.8199502872406965</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8232357198648612</v>
+        <v>0.8231527482135648</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8270908885801076</v>
+        <v>0.8269990906401263</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8294800607993658</v>
+        <v>0.8294126234012107</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8279666777464643</v>
+        <v>0.8280155432427382</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.824133243497469</v>
+        <v>0.8246043419064784</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8192330256518302</v>
+        <v>0.8201925112308474</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8101352908797863</v>
+        <v>0.8124426488042862</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,15 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8163366765283476</v>
+        <v>0.8178709122849442</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B80">
+        <v>0.8296259986166361</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886384749580106</v>
+        <v>0.7886374726939988</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919570438127925</v>
+        <v>0.7919551067054822</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913200018768558</v>
+        <v>0.7913180408231485</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927046758494678</v>
+        <v>0.7927015665075595</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913791834429735</v>
+        <v>0.7913759827730956</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789926752238312</v>
+        <v>0.7899235025520766</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.78834914953069</v>
+        <v>0.788345915909678</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872663249668841</v>
+        <v>0.7872631509234344</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892778406151553</v>
+        <v>0.7892741132362279</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945185833353103</v>
+        <v>0.7945168568350514</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969359997002019</v>
+        <v>0.7969341670991973</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993641397275123</v>
+        <v>0.7993622644119602</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001806195380889</v>
+        <v>0.8001797337070597</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986618321386849</v>
+        <v>0.7986624401848588</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992555553499057</v>
+        <v>0.7992567340253924</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039764185949162</v>
+        <v>0.8039758338026088</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809641562045085</v>
+        <v>0.8096391447120258</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158190901981847</v>
+        <v>0.8158157731037061</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222067715030221</v>
+        <v>0.8222041215091642</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229458205805233</v>
+        <v>0.8229452722801858</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187613318813838</v>
+        <v>0.8187640810399939</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8152975015264006</v>
+        <v>0.815301296172855</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139077939943472</v>
+        <v>0.8139147895413287</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122525797041518</v>
+        <v>0.812263801455687</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8120925273465811</v>
+        <v>0.8121068731741672</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172781494498403</v>
+        <v>0.8172957661542219</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8229603205377316</v>
+        <v>0.8229799757418814</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8298253692064982</v>
+        <v>0.8298472044146699</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.834484379762378</v>
+        <v>0.8345083751466463</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8196060469972485</v>
+        <v>0.8196337120337636</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8214290243176219</v>
+        <v>0.8214566053075463</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8088517630951318</v>
+        <v>0.8088819378365628</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800749611891448</v>
+        <v>0.8007780456091522</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793516501109031</v>
+        <v>0.7935492590903663</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7839172834046745</v>
+        <v>0.7839523623557885</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7685864738181165</v>
+        <v>0.7686002036665405</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663861433664384</v>
+        <v>0.7663955963337195</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758343864077788</v>
+        <v>0.7583439284269109</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477773675934092</v>
+        <v>0.7477635022624474</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7389278788000397</v>
+        <v>0.7389058419816695</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7294016138637135</v>
+        <v>0.7293704522722863</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7336417197271053</v>
+        <v>0.7335907208925618</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7390631121976436</v>
+        <v>0.7390088401285739</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7486042377046642</v>
+        <v>0.748554939918375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7573601095117937</v>
+        <v>0.7573123903577442</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731734205899232</v>
+        <v>0.7731525174487541</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774576813131802</v>
+        <v>0.77744408114821</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7780284242743801</v>
+        <v>0.7780119415508499</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833728048201167</v>
+        <v>0.7833635587195791</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885828160732378</v>
+        <v>0.7885805113279251</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923377009058834</v>
+        <v>0.7923384159565658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894162445600188</v>
+        <v>0.7894097251791372</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920906096039891</v>
+        <v>0.7920799973716832</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7975203559941382</v>
+        <v>0.7975019249648155</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8026334737012073</v>
+        <v>0.8026090589652314</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052660144851997</v>
+        <v>0.8052419664869414</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078215294022708</v>
+        <v>0.8078006367086932</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8100043208152582</v>
+        <v>0.8099878125353654</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096580177165265</v>
+        <v>0.8096541912724063</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088381676242653</v>
+        <v>0.8088458564002283</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8093385710762391</v>
+        <v>0.8095064882503753</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8098509355464621</v>
+        <v>0.8100400212704559</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123933077453058</v>
+        <v>0.8125646047897013</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8163766216991143</v>
+        <v>0.8165784234049794</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8199502872406965</v>
+        <v>0.8200847259307081</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8231527482135648</v>
+        <v>0.8233024994564986</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8269990906401263</v>
+        <v>0.8271598477795493</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8294126234012107</v>
+        <v>0.8296383658784826</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8280155432427382</v>
+        <v>0.8284098982107031</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8246043419064784</v>
+        <v>0.8254659113965952</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8201925112308474</v>
+        <v>0.8216083895772881</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8124426488042862</v>
+        <v>0.8151966388345404</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8178709122849442</v>
+        <v>0.8223344318085783</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8296259986166361</v>
+        <v>0.8347714198192098</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886374726939988</v>
+        <v>0.78863649269974</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919551067054822</v>
+        <v>0.7919532125540325</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913180408231485</v>
+        <v>0.791316122966351</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7927015665075595</v>
+        <v>0.7926985258836916</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913759827730956</v>
+        <v>0.7913728528590842</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899235025520766</v>
+        <v>0.7899203247332797</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788345915909678</v>
+        <v>0.7883427538158948</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872631509234344</v>
+        <v>0.7872600470893338</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892741132362279</v>
+        <v>0.7892704681264442</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945168568350514</v>
+        <v>0.7945151686833311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969341670991973</v>
+        <v>0.7969323752409291</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993622644119602</v>
+        <v>0.799360430824587</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001797337070597</v>
+        <v>0.8001788670376606</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986624401848588</v>
+        <v>0.7986630340483859</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992567340253924</v>
+        <v>0.7992578862891973</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039758338026088</v>
+        <v>0.8039752614249908</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096391447120258</v>
+        <v>0.8096367795492319</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158157731037061</v>
+        <v>0.8158125258133223</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222041215091642</v>
+        <v>0.8222015263008238</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229452722801858</v>
+        <v>0.8229447317808859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187640810399939</v>
+        <v>0.8187667635501461</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815301296172855</v>
+        <v>0.815305000746347</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139147895413287</v>
+        <v>0.8139216243687881</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.812263801455687</v>
+        <v>0.8122747680262461</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121068731741672</v>
+        <v>0.8121208950325579</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8172957661542219</v>
+        <v>0.8173129868061697</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8229799757418814</v>
+        <v>0.8229991910902732</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8298472044146699</v>
+        <v>0.8298685527785932</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8345083751466463</v>
+        <v>0.8345318490214904</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8196337120337636</v>
+        <v>0.8196607672356204</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8214566053075463</v>
+        <v>0.8214835797589584</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8088819378365628</v>
+        <v>0.8089114464649103</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8007780456091522</v>
+        <v>0.8008058535622592</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7935492590903663</v>
+        <v>0.7935812996276502</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7839523623557885</v>
+        <v>0.7839866808090852</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686002036665405</v>
+        <v>0.7686136452900354</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7663955963337195</v>
+        <v>0.7664048623215191</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583439284269109</v>
+        <v>0.7583440185217574</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477635022624474</v>
+        <v>0.7477499703433055</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7389058419816695</v>
+        <v>0.7388843236016749</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7293704522722863</v>
+        <v>0.7293400050756502</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7335907208925618</v>
+        <v>0.7335408453962329</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7390088401285739</v>
+        <v>0.7389557552681569</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748554939918375</v>
+        <v>0.7485067065170127</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7573123903577442</v>
+        <v>0.7572656857907489</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731525174487541</v>
+        <v>0.7731320567427888</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.77744408114821</v>
+        <v>0.7774307625138099</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7780119415508499</v>
+        <v>0.7779958031958344</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833635587195791</v>
+        <v>0.78335450762104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885805113279251</v>
+        <v>0.7885782635221389</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923384159565658</v>
+        <v>0.792339133746629</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894097251791372</v>
+        <v>0.7894033601862714</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920799973716832</v>
+        <v>0.7920696299587678</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7975019249648155</v>
+        <v>0.7974838972866629</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8026090589652314</v>
+        <v>0.8025851664612501</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052419664869414</v>
+        <v>0.8052184175548216</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8078006367086932</v>
+        <v>0.8077801508997677</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099878125353654</v>
+        <v>0.8099715989530919</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096541912724063</v>
+        <v>0.8096503649433632</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088458564002283</v>
+        <v>0.8088533220889597</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095064882503753</v>
+        <v>0.8094882383830156</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8100400212704559</v>
+        <v>0.8100086124229073</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8125646047897013</v>
+        <v>0.8124935755059566</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8165784234049794</v>
+        <v>0.8165005756502978</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8200847259307081</v>
+        <v>0.8199201443468258</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8233024994564986</v>
+        <v>0.8231316178326236</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8271598477795493</v>
+        <v>0.8269699124032281</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8296383658784826</v>
+        <v>0.8294490673035051</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8284098982107031</v>
+        <v>0.8282929888595647</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8254659113965952</v>
+        <v>0.8256695274826644</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8216083895772881</v>
+        <v>0.8221286217339649</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8151966388345404</v>
+        <v>0.8165354080408586</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8223344318085783</v>
+        <v>0.8223492337155864</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8347714198192098</v>
+        <v>0.8316285808180188</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.78863649269974</v>
+        <v>0.7886355342411865</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919532125540325</v>
+        <v>0.7919513599453951</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791316122966351</v>
+        <v>0.7913142468950352</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926985258836916</v>
+        <v>0.7926955517251459</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913728528590842</v>
+        <v>0.791369791380792</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899203247332797</v>
+        <v>0.7899172164244137</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883427538158948</v>
+        <v>0.7883396609025</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872600470893338</v>
+        <v>0.7872570111609817</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892704681264442</v>
+        <v>0.7892669025926442</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945151686833311</v>
+        <v>0.794513517616764</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969323752409291</v>
+        <v>0.7969306227819104</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799360430824587</v>
+        <v>0.7993586375882435</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001788670376606</v>
+        <v>0.800178018915585</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986630340483859</v>
+        <v>0.798663614218341</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992578862891973</v>
+        <v>0.7992590130186823</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039752614249908</v>
+        <v>0.8039747010721785</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096367795492319</v>
+        <v>0.8096344648888677</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158125258133223</v>
+        <v>0.8158093461559284</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8222015263008238</v>
+        <v>0.8221989842074499</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229447317808859</v>
+        <v>0.8229441989685961</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187667635501461</v>
+        <v>0.8187693817863355</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815305000746347</v>
+        <v>0.8153086183969955</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139216243687881</v>
+        <v>0.8139283039352152</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122747680262461</v>
+        <v>0.8122854879995198</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121208950325579</v>
+        <v>0.8121346037453507</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173129868061697</v>
+        <v>0.8173298245781487</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8229991910902732</v>
+        <v>0.8230179811431593</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8298685527785932</v>
+        <v>0.8298894303529144</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8345318490214904</v>
+        <v>0.8345548181800706</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8196607672356204</v>
+        <v>0.8196872325240381</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8214835797589584</v>
+        <v>0.8215099674376207</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8089114464649103</v>
+        <v>0.808940310762153</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8008058535622592</v>
+        <v>0.800833056148022</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7935812996276502</v>
+        <v>0.7936126459844383</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7839866808090852</v>
+        <v>0.7840202631567086</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686136452900354</v>
+        <v>0.7686268076169318</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664048623215191</v>
+        <v>0.7664139467239031</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583440185217574</v>
+        <v>0.7583441326288152</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477499703433055</v>
+        <v>0.7477367600465399</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7388843236016749</v>
+        <v>0.7388633056799221</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7293400050756502</v>
+        <v>0.729310248061092</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7335408453962329</v>
+        <v>0.7334920566004903</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7389557552681569</v>
+        <v>0.7389038191767312</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7485067065170127</v>
+        <v>0.7484595034927451</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7572656857907489</v>
+        <v>0.7572199639027974</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731320567427888</v>
+        <v>0.7731120246191527</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774307625138099</v>
+        <v>0.7774177168034683</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779958031958344</v>
+        <v>0.7779799985715029</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.78335450762104</v>
+        <v>0.7833456454304879</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885782635221389</v>
+        <v>0.7885760705881701</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792339133746629</v>
+        <v>0.7923398535868712</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7894033601862714</v>
+        <v>0.7893971441909351</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920696299587678</v>
+        <v>0.7920594990259608</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7974838972866629</v>
+        <v>0.7974662599325352</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8025851664612501</v>
+        <v>0.8025617797338631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8052184175548216</v>
+        <v>0.8051953525004694</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077801508997677</v>
+        <v>0.8077600605006905</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099715989530919</v>
+        <v>0.8099556726702473</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096503649433632</v>
+        <v>0.8096465412679709</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088533220889597</v>
+        <v>0.8088605732943406</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094882383830156</v>
+        <v>0.8094840669347547</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8100086124229073</v>
+        <v>0.8099934705099282</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8124935755059566</v>
+        <v>0.81243867917366</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8165005756502978</v>
+        <v>0.8164465807401347</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8199201443468258</v>
+        <v>0.8197795687408023</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8231316178326236</v>
+        <v>0.8229855228157508</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8269699124032281</v>
+        <v>0.8268066404425756</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8294490673035051</v>
+        <v>0.8292892950601856</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8282929888595647</v>
+        <v>0.8282055945236353</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8256695274826644</v>
+        <v>0.8258828036549477</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8221286217339649</v>
+        <v>0.8226287908554637</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8165354080408586</v>
+        <v>0.8177373620017088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8223492337155864</v>
+        <v>0.8224640936146899</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8316285808180188</v>
+        <v>0.8303028263230476</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886355342411865</v>
+        <v>0.7886345966161996</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919513599453951</v>
+        <v>0.791949547527822</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913142468950352</v>
+        <v>0.7913124112585878</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926955517251459</v>
+        <v>0.7926926418765868</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791369791380792</v>
+        <v>0.7913667961183953</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899172164244137</v>
+        <v>0.7899141753699498</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883396609025</v>
+        <v>0.7883366349241911</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872570111609817</v>
+        <v>0.7872540409344451</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892669025926442</v>
+        <v>0.789263414057914</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794513517616764</v>
+        <v>0.7945119024268463</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969306227819104</v>
+        <v>0.7969289084370677</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993586375882435</v>
+        <v>0.799356883385708</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800178018915585</v>
+        <v>0.8001771887524736</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.798663614218341</v>
+        <v>0.7986641811616251</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992590130186823</v>
+        <v>0.7992601150527989</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039747010721785</v>
+        <v>0.8039741523703864</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096344648888677</v>
+        <v>0.8096321991333072</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158093461559284</v>
+        <v>0.81580623204911</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221989842074499</v>
+        <v>0.8221964936252236</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229441989685961</v>
+        <v>0.8229436737280842</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187693817863355</v>
+        <v>0.8187719380123669</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153086183969955</v>
+        <v>0.8153121521304817</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139283039352152</v>
+        <v>0.8139348334553864</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122854879995198</v>
+        <v>0.8122959695794154</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121346037453507</v>
+        <v>0.8121480096604675</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173298245781487</v>
+        <v>0.8173462920663334</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8230179811431593</v>
+        <v>0.8230363598268933</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8298894303529144</v>
+        <v>0.8299098524960544</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8345548181800706</v>
+        <v>0.8345772987032914</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8196872325240381</v>
+        <v>0.8197131269628973</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8215099674376207</v>
+        <v>0.8215357872607352</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.808940310762153</v>
+        <v>0.8089685515722608</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800833056148022</v>
+        <v>0.8008596728882568</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7936126459844383</v>
+        <v>0.7936433204314346</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7840202631567086</v>
+        <v>0.7840531327618918</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686268076169318</v>
+        <v>0.7686396992129645</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664139467239031</v>
+        <v>0.7664228547341768</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583441326288152</v>
+        <v>0.7583442691278304</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477367600465399</v>
+        <v>0.747723860128385</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7388633056799221</v>
+        <v>0.7388427710541048</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.729310248061092</v>
+        <v>0.7292811580947344</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7334920566004903</v>
+        <v>0.7334443194406881</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7389038191767312</v>
+        <v>0.7388529950523427</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7484595034927451</v>
+        <v>0.7484132982671028</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7572199639027974</v>
+        <v>0.757175194105226</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7731120246191527</v>
+        <v>0.7730924077952807</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774177168034683</v>
+        <v>0.7774049357559294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779799985715029</v>
+        <v>0.7779645174718592</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833456454304879</v>
+        <v>0.7833369663047888</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885760705881701</v>
+        <v>0.7885739305565403</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923398535868712</v>
+        <v>0.7923405748433728</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893971441909351</v>
+        <v>0.789391072049509</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920594990259608</v>
+        <v>0.792049596607001</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7974662599325352</v>
+        <v>0.7974490004272975</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8025617797338631</v>
+        <v>0.8025388830065348</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051953525004694</v>
+        <v>0.8051727567373457</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077600605006905</v>
+        <v>0.8077403544505222</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099556726702473</v>
+        <v>0.8099400265138872</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096465412679709</v>
+        <v>0.8096427225766581</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088605732943406</v>
+        <v>0.8088676182120849</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094840669347547</v>
+        <v>0.8094798499800153</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099934705099282</v>
+        <v>0.8099877430491782</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.81243867917366</v>
+        <v>0.8124276517190065</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8164465807401347</v>
+        <v>0.8166071193205156</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8197795687408023</v>
+        <v>0.8199082319075093</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8229855228157508</v>
+        <v>0.8232151496239926</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8268066404425756</v>
+        <v>0.8268153643627052</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8292892950601856</v>
+        <v>0.8293206255497861</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8282055945236353</v>
+        <v>0.82833478361708</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8258828036549477</v>
+        <v>0.8261468080150294</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8226287908554637</v>
+        <v>0.8231488997661842</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8177373620017088</v>
+        <v>0.8188124525154397</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8224640936146899</v>
+        <v>0.8238258573703869</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8303028263230476</v>
+        <v>0.8322826041044036</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886345966161996</v>
+        <v>0.7886336791528341</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791949547527822</v>
+        <v>0.7919477740075762</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913124112585878</v>
+        <v>0.7913106147639701</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926926418765868</v>
+        <v>0.7926897942748554</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913667961183953</v>
+        <v>0.79136386494703</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899141753699498</v>
+        <v>0.7899111994108823</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883366349241911</v>
+        <v>0.7883336737317718</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872540409344451</v>
+        <v>0.7872511343001255</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.789263414057914</v>
+        <v>0.7892600000553843</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945119024268463</v>
+        <v>0.7945103219570094</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969289084370677</v>
+        <v>0.7969272309766031</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799356883385708</v>
+        <v>0.7993551669564641</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001771887524736</v>
+        <v>0.8001763759845602</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986641811616251</v>
+        <v>0.7986647353242048</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992601150527989</v>
+        <v>0.7992611931941652</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039741523703864</v>
+        <v>0.8039736149611081</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096321991333072</v>
+        <v>0.8096299807514853</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.81580623204911</v>
+        <v>0.815803181494685</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221964936252236</v>
+        <v>0.8221940530137873</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229436737280842</v>
+        <v>0.8229431559433068</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187719380123669</v>
+        <v>0.8187744343876907</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153121521304817</v>
+        <v>0.8153156048161968</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139348334553864</v>
+        <v>0.8139412179137802</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8122959695794154</v>
+        <v>0.8123062206107836</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121480096604675</v>
+        <v>0.8121611226759422</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173462920663334</v>
+        <v>0.8173624013217091</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8230363598268933</v>
+        <v>0.823054340467966</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8299098524960544</v>
+        <v>0.8299298339074388</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8345772987032914</v>
+        <v>0.8345993059971084</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8197131269628973</v>
+        <v>0.8197384688043204</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8215357872607352</v>
+        <v>0.821561057341942</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8089685515722608</v>
+        <v>0.8089961888510718</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8008596728882568</v>
+        <v>0.8008857224757298</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7936433204314346</v>
+        <v>0.7936733442987838</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7840531327618918</v>
+        <v>0.7840853120124704</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686396992129645</v>
+        <v>0.7686523282993578</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664228547341768</v>
+        <v>0.7664315913538526</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583442691278304</v>
+        <v>0.758344426503717</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.747723860128385</v>
+        <v>0.7477112598597229</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7388427710541048</v>
+        <v>0.7388227033339727</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7292811580947344</v>
+        <v>0.7292527130622715</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7334443194406881</v>
+        <v>0.733397600341807</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7388529950523427</v>
+        <v>0.7388032476446635</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7484132982671028</v>
+        <v>0.7483680596168849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.757175194105226</v>
+        <v>0.7571313470614811</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7730924077952807</v>
+        <v>0.7730731935299782</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7774049357559294</v>
+        <v>0.7773924114381627</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779645174718592</v>
+        <v>0.7779493501011487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833369663047888</v>
+        <v>0.7833284646389292</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885739305565403</v>
+        <v>0.7885718415502719</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923405748433728</v>
+        <v>0.792341296933206</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789391072049509</v>
+        <v>0.7893851388513292</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.792049596607001</v>
+        <v>0.7920399150880973</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7974490004272975</v>
+        <v>0.797432106819053</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8025388830065348</v>
+        <v>0.802516461147226</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051727567373457</v>
+        <v>0.8051506162516848</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077403544505222</v>
+        <v>0.8077210220844842</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099400265138872</v>
+        <v>0.8099246535290764</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096427225766581</v>
+        <v>0.8096389110074076</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088676182120849</v>
+        <v>0.8088744646524717</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094798499800153</v>
+        <v>0.8094756040661576</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099877430491782</v>
+        <v>0.8099724661940074</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8124276517190065</v>
+        <v>0.812371918090002</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8166071193205156</v>
+        <v>0.8165061065394854</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8199082319075093</v>
+        <v>0.8198029520302624</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8232151496239926</v>
+        <v>0.8231199429262185</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8268153643627052</v>
+        <v>0.8267270476713755</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8293206255497861</v>
+        <v>0.8292402151821664</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.82833478361708</v>
+        <v>0.8283228351233115</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8261468080150294</v>
+        <v>0.8264095950748641</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8231488997661842</v>
+        <v>0.8236096266921744</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8188124525154397</v>
+        <v>0.8197234376438181</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8238258573703869</v>
+        <v>0.824890498768807</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8322826041044036</v>
+        <v>0.830914653534756</v>
       </c>
     </row>
   </sheetData>
